--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S411"/>
+  <dimension ref="A1:S415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,7 +570,7 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="b">
+      <c r="S2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -623,7 +623,7 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="b">
+      <c r="S3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -676,7 +676,7 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="b">
+      <c r="S4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -729,7 +729,7 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="b">
+      <c r="S5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -782,7 +782,7 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="b">
+      <c r="S6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -835,7 +835,7 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="b">
+      <c r="S7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -888,7 +888,7 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="b">
+      <c r="S8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -941,7 +941,7 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="b">
+      <c r="S9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -994,7 +994,7 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="b">
+      <c r="S10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="b">
+      <c r="S11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="b">
+      <c r="S12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="b">
+      <c r="S13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="b">
+      <c r="S14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="b">
+      <c r="S15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="b">
+      <c r="S16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="b">
+      <c r="S17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="b">
+      <c r="S18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="b">
+      <c r="S19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="b">
+      <c r="S20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="b">
+      <c r="S21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="b">
+      <c r="S22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="b">
+      <c r="S23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="b">
+      <c r="S24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="b">
+      <c r="S25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="b">
+      <c r="S26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="b">
+      <c r="S27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="b">
+      <c r="S28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="b">
+      <c r="S29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="b">
+      <c r="S30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="b">
+      <c r="S31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="b">
+      <c r="S32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="b">
+      <c r="S33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="b">
+      <c r="S34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="b">
+      <c r="S35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="b">
+      <c r="S36" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="b">
+      <c r="S37" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="b">
+      <c r="S38" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="b">
+      <c r="S39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="b">
+      <c r="S40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="b">
+      <c r="S41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="b">
+      <c r="S42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="b">
+      <c r="S43" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="b">
+      <c r="S44" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="b">
+      <c r="S45" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="b">
+      <c r="S46" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="b">
+      <c r="S47" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="b">
+      <c r="S48" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="b">
+      <c r="S49" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="b">
+      <c r="S50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="b">
+      <c r="S51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="b">
+      <c r="S52" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="b">
+      <c r="S53" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="b">
+      <c r="S54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="b">
+      <c r="S55" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="b">
+      <c r="S56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="b">
+      <c r="S57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="b">
+      <c r="S58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="b">
+      <c r="S59" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="b">
+      <c r="S60" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="b">
+      <c r="S61" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3730,7 +3730,7 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="b">
+      <c r="S62" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="b">
+      <c r="S63" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="S64" t="b">
+      <c r="S64" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="b">
+      <c r="S65" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="b">
+      <c r="S66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="b">
+      <c r="S67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="b">
+      <c r="S68" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4093,7 +4093,7 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="b">
+      <c r="S69" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="b">
+      <c r="S70" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="b">
+      <c r="S71" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="b">
+      <c r="S72" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="S73" t="b">
+      <c r="S73" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="b">
+      <c r="S74" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="b">
+      <c r="S75" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="b">
+      <c r="S76" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="b">
+      <c r="S77" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="b">
+      <c r="S78" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="b">
+      <c r="S79" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="b">
+      <c r="S80" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4725,7 +4725,7 @@
       <c r="R81" t="n">
         <v>0</v>
       </c>
-      <c r="S81" t="b">
+      <c r="S81" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="b">
+      <c r="S82" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="b">
+      <c r="S83" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="b">
+      <c r="S84" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
-      <c r="S85" t="b">
+      <c r="S85" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="b">
+      <c r="S86" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5035,7 +5035,7 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="b">
+      <c r="S87" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="b">
+      <c r="S88" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="b">
+      <c r="S89" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
-      <c r="S90" t="b">
+      <c r="S90" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="b">
+      <c r="S91" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="S92" t="b">
+      <c r="S92" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5349,7 +5349,7 @@
       <c r="R93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="b">
+      <c r="S93" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       <c r="R94" t="n">
         <v>0</v>
       </c>
-      <c r="S94" t="b">
+      <c r="S94" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       <c r="R95" t="n">
         <v>0</v>
       </c>
-      <c r="S95" t="b">
+      <c r="S95" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
-      <c r="S96" t="b">
+      <c r="S96" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5549,7 +5549,7 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
-      <c r="S97" t="b">
+      <c r="S97" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       <c r="R98" t="n">
         <v>0</v>
       </c>
-      <c r="S98" t="b">
+      <c r="S98" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       <c r="R99" t="n">
         <v>0</v>
       </c>
-      <c r="S99" t="b">
+      <c r="S99" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="b">
+      <c r="S100" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       <c r="R101" t="n">
         <v>0</v>
       </c>
-      <c r="S101" t="b">
+      <c r="S101" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
-      <c r="S102" t="b">
+      <c r="S102" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5819,7 +5819,7 @@
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="b">
+      <c r="S103" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5864,7 +5864,7 @@
       <c r="R104" t="n">
         <v>0</v>
       </c>
-      <c r="S104" t="b">
+      <c r="S104" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       <c r="R105" t="n">
         <v>0</v>
       </c>
-      <c r="S105" t="b">
+      <c r="S105" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
-      <c r="S106" t="b">
+      <c r="S106" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5999,7 +5999,7 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="b">
+      <c r="S107" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       <c r="R108" t="n">
         <v>0</v>
       </c>
-      <c r="S108" t="b">
+      <c r="S108" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
-      <c r="S109" t="b">
+      <c r="S109" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       <c r="R110" t="n">
         <v>0</v>
       </c>
-      <c r="S110" t="b">
+      <c r="S110" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="b">
+      <c r="S111" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       <c r="R112" t="n">
         <v>0</v>
       </c>
-      <c r="S112" t="b">
+      <c r="S112" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       <c r="R113" t="n">
         <v>0</v>
       </c>
-      <c r="S113" t="b">
+      <c r="S113" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       <c r="R114" t="n">
         <v>0</v>
       </c>
-      <c r="S114" t="b">
+      <c r="S114" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       <c r="R115" t="n">
         <v>0</v>
       </c>
-      <c r="S115" t="b">
+      <c r="S115" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="b">
+      <c r="S116" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6449,7 +6449,7 @@
       <c r="R117" t="n">
         <v>0</v>
       </c>
-      <c r="S117" t="b">
+      <c r="S117" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       <c r="R118" t="n">
         <v>0</v>
       </c>
-      <c r="S118" t="b">
+      <c r="S118" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       <c r="R119" t="n">
         <v>0</v>
       </c>
-      <c r="S119" t="b">
+      <c r="S119" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       <c r="R120" t="n">
         <v>0</v>
       </c>
-      <c r="S120" t="b">
+      <c r="S120" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6629,7 +6629,7 @@
       <c r="R121" t="n">
         <v>0</v>
       </c>
-      <c r="S121" t="b">
+      <c r="S121" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
-      <c r="S122" t="b">
+      <c r="S122" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       <c r="R123" t="n">
         <v>0</v>
       </c>
-      <c r="S123" t="b">
+      <c r="S123" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       <c r="R124" t="n">
         <v>0</v>
       </c>
-      <c r="S124" t="b">
+      <c r="S124" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       <c r="R125" t="n">
         <v>0</v>
       </c>
-      <c r="S125" t="b">
+      <c r="S125" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6854,7 +6854,7 @@
       <c r="R126" t="n">
         <v>0</v>
       </c>
-      <c r="S126" t="b">
+      <c r="S126" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       <c r="R127" t="n">
         <v>0</v>
       </c>
-      <c r="S127" t="b">
+      <c r="S127" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       <c r="R128" t="n">
         <v>0</v>
       </c>
-      <c r="S128" t="b">
+      <c r="S128" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
       <c r="R129" t="n">
         <v>0</v>
       </c>
-      <c r="S129" t="b">
+      <c r="S129" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       <c r="R130" t="n">
         <v>0</v>
       </c>
-      <c r="S130" t="b">
+      <c r="S130" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       <c r="R131" t="n">
         <v>0</v>
       </c>
-      <c r="S131" t="b">
+      <c r="S131" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7124,7 +7124,7 @@
       <c r="R132" t="n">
         <v>0</v>
       </c>
-      <c r="S132" t="b">
+      <c r="S132" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7169,7 +7169,7 @@
       <c r="R133" t="n">
         <v>0</v>
       </c>
-      <c r="S133" t="b">
+      <c r="S133" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       <c r="R134" t="n">
         <v>0</v>
       </c>
-      <c r="S134" t="b">
+      <c r="S134" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7259,7 +7259,7 @@
       <c r="R135" t="n">
         <v>0</v>
       </c>
-      <c r="S135" t="b">
+      <c r="S135" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       <c r="R136" t="n">
         <v>0</v>
       </c>
-      <c r="S136" t="b">
+      <c r="S136" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       <c r="R137" t="n">
         <v>0</v>
       </c>
-      <c r="S137" t="b">
+      <c r="S137" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7394,7 +7394,7 @@
       <c r="R138" t="n">
         <v>0</v>
       </c>
-      <c r="S138" t="b">
+      <c r="S138" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       <c r="R139" t="n">
         <v>0</v>
       </c>
-      <c r="S139" t="b">
+      <c r="S139" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       <c r="R140" t="n">
         <v>0</v>
       </c>
-      <c r="S140" t="b">
+      <c r="S140" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       <c r="R141" t="n">
         <v>0</v>
       </c>
-      <c r="S141" t="b">
+      <c r="S141" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       <c r="R142" t="n">
         <v>0</v>
       </c>
-      <c r="S142" t="b">
+      <c r="S142" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7619,7 +7619,7 @@
       <c r="R143" t="n">
         <v>0</v>
       </c>
-      <c r="S143" t="b">
+      <c r="S143" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       <c r="R144" t="n">
         <v>0</v>
       </c>
-      <c r="S144" t="b">
+      <c r="S144" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       <c r="R145" t="n">
         <v>0</v>
       </c>
-      <c r="S145" t="b">
+      <c r="S145" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       <c r="R146" t="n">
         <v>0</v>
       </c>
-      <c r="S146" t="b">
+      <c r="S146" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7799,7 +7799,7 @@
       <c r="R147" t="n">
         <v>0</v>
       </c>
-      <c r="S147" t="b">
+      <c r="S147" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7844,7 +7844,7 @@
       <c r="R148" t="n">
         <v>0</v>
       </c>
-      <c r="S148" t="b">
+      <c r="S148" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       <c r="R149" t="n">
         <v>0</v>
       </c>
-      <c r="S149" t="b">
+      <c r="S149" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
       <c r="R150" t="n">
         <v>0</v>
       </c>
-      <c r="S150" t="b">
+      <c r="S150" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7979,7 +7979,7 @@
       <c r="R151" t="n">
         <v>0</v>
       </c>
-      <c r="S151" t="b">
+      <c r="S151" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8024,7 +8024,7 @@
       <c r="R152" t="n">
         <v>0</v>
       </c>
-      <c r="S152" t="b">
+      <c r="S152" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
       <c r="R153" t="n">
         <v>0</v>
       </c>
-      <c r="S153" t="b">
+      <c r="S153" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
-      <c r="S154" t="b">
+      <c r="S154" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       <c r="R155" t="n">
         <v>0</v>
       </c>
-      <c r="S155" t="b">
+      <c r="S155" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       <c r="R156" t="n">
         <v>0</v>
       </c>
-      <c r="S156" t="b">
+      <c r="S156" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       <c r="R157" t="n">
         <v>0</v>
       </c>
-      <c r="S157" t="b">
+      <c r="S157" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       <c r="R158" t="n">
         <v>0</v>
       </c>
-      <c r="S158" t="b">
+      <c r="S158" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       <c r="R159" t="n">
         <v>0</v>
       </c>
-      <c r="S159" t="b">
+      <c r="S159" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       <c r="R160" t="n">
         <v>0</v>
       </c>
-      <c r="S160" t="b">
+      <c r="S160" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
       <c r="R161" t="n">
         <v>0</v>
       </c>
-      <c r="S161" t="b">
+      <c r="S161" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       <c r="R162" t="n">
         <v>0</v>
       </c>
-      <c r="S162" t="b">
+      <c r="S162" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       <c r="R163" t="n">
         <v>0</v>
       </c>
-      <c r="S163" t="b">
+      <c r="S163" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       <c r="R164" t="n">
         <v>0</v>
       </c>
-      <c r="S164" t="b">
+      <c r="S164" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8609,7 +8609,7 @@
       <c r="R165" t="n">
         <v>0</v>
       </c>
-      <c r="S165" t="b">
+      <c r="S165" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8654,7 +8654,7 @@
       <c r="R166" t="n">
         <v>0</v>
       </c>
-      <c r="S166" t="b">
+      <c r="S166" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       <c r="R167" t="n">
         <v>0</v>
       </c>
-      <c r="S167" t="b">
+      <c r="S167" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       <c r="R168" t="n">
         <v>0</v>
       </c>
-      <c r="S168" t="b">
+      <c r="S168" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8789,7 +8789,7 @@
       <c r="R169" t="n">
         <v>0</v>
       </c>
-      <c r="S169" t="b">
+      <c r="S169" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8834,7 +8834,7 @@
       <c r="R170" t="n">
         <v>0</v>
       </c>
-      <c r="S170" t="b">
+      <c r="S170" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8879,7 +8879,7 @@
       <c r="R171" t="n">
         <v>0</v>
       </c>
-      <c r="S171" t="b">
+      <c r="S171" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8924,7 +8924,7 @@
       <c r="R172" t="n">
         <v>0</v>
       </c>
-      <c r="S172" t="b">
+      <c r="S172" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8969,7 +8969,7 @@
       <c r="R173" t="n">
         <v>0</v>
       </c>
-      <c r="S173" t="b">
+      <c r="S173" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       <c r="R174" t="n">
         <v>0</v>
       </c>
-      <c r="S174" t="b">
+      <c r="S174" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       <c r="R175" t="n">
         <v>0</v>
       </c>
-      <c r="S175" t="b">
+      <c r="S175" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
       <c r="R176" t="n">
         <v>0</v>
       </c>
-      <c r="S176" t="b">
+      <c r="S176" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9169,7 +9169,7 @@
       <c r="R177" t="n">
         <v>0</v>
       </c>
-      <c r="S177" t="b">
+      <c r="S177" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9214,7 +9214,7 @@
       <c r="R178" t="n">
         <v>0</v>
       </c>
-      <c r="S178" t="b">
+      <c r="S178" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9259,7 +9259,7 @@
       <c r="R179" t="n">
         <v>0</v>
       </c>
-      <c r="S179" t="b">
+      <c r="S179" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       <c r="R180" t="n">
         <v>0</v>
       </c>
-      <c r="S180" t="b">
+      <c r="S180" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       <c r="R181" t="n">
         <v>0</v>
       </c>
-      <c r="S181" t="b">
+      <c r="S181" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9394,7 +9394,7 @@
       <c r="R182" t="n">
         <v>0</v>
       </c>
-      <c r="S182" t="b">
+      <c r="S182" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       <c r="R183" t="n">
         <v>0</v>
       </c>
-      <c r="S183" t="b">
+      <c r="S183" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9484,7 +9484,7 @@
       <c r="R184" t="n">
         <v>0</v>
       </c>
-      <c r="S184" t="b">
+      <c r="S184" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       <c r="R185" t="n">
         <v>0</v>
       </c>
-      <c r="S185" t="b">
+      <c r="S185" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9574,7 +9574,7 @@
       <c r="R186" t="n">
         <v>0</v>
       </c>
-      <c r="S186" t="b">
+      <c r="S186" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9619,7 +9619,7 @@
       <c r="R187" t="n">
         <v>0</v>
       </c>
-      <c r="S187" t="b">
+      <c r="S187" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9664,7 +9664,7 @@
       <c r="R188" t="n">
         <v>0</v>
       </c>
-      <c r="S188" t="b">
+      <c r="S188" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       <c r="R189" t="n">
         <v>0</v>
       </c>
-      <c r="S189" t="b">
+      <c r="S189" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9754,7 +9754,7 @@
       <c r="R190" t="n">
         <v>0</v>
       </c>
-      <c r="S190" t="b">
+      <c r="S190" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9799,7 +9799,7 @@
       <c r="R191" t="n">
         <v>0</v>
       </c>
-      <c r="S191" t="b">
+      <c r="S191" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       <c r="R192" t="n">
         <v>0</v>
       </c>
-      <c r="S192" t="b">
+      <c r="S192" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9889,7 +9889,7 @@
       <c r="R193" t="n">
         <v>0</v>
       </c>
-      <c r="S193" t="b">
+      <c r="S193" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       <c r="R194" t="n">
         <v>0</v>
       </c>
-      <c r="S194" t="b">
+      <c r="S194" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
       <c r="R195" t="n">
         <v>0</v>
       </c>
-      <c r="S195" t="b">
+      <c r="S195" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       <c r="R196" t="n">
         <v>0</v>
       </c>
-      <c r="S196" t="b">
+      <c r="S196" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
       <c r="R197" t="n">
         <v>0</v>
       </c>
-      <c r="S197" t="b">
+      <c r="S197" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       <c r="R198" t="n">
         <v>0</v>
       </c>
-      <c r="S198" t="b">
+      <c r="S198" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10159,7 +10159,7 @@
       <c r="R199" t="n">
         <v>0</v>
       </c>
-      <c r="S199" t="b">
+      <c r="S199" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10204,7 +10204,7 @@
       <c r="R200" t="n">
         <v>0</v>
       </c>
-      <c r="S200" t="b">
+      <c r="S200" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10249,7 +10249,7 @@
       <c r="R201" t="n">
         <v>0</v>
       </c>
-      <c r="S201" t="b">
+      <c r="S201" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       <c r="R202" t="n">
         <v>0</v>
       </c>
-      <c r="S202" t="b">
+      <c r="S202" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10339,7 +10339,7 @@
       <c r="R203" t="n">
         <v>0</v>
       </c>
-      <c r="S203" t="b">
+      <c r="S203" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10384,7 +10384,7 @@
       <c r="R204" t="n">
         <v>0</v>
       </c>
-      <c r="S204" t="b">
+      <c r="S204" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10429,7 +10429,7 @@
       <c r="R205" t="n">
         <v>0</v>
       </c>
-      <c r="S205" t="b">
+      <c r="S205" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10474,7 +10474,7 @@
       <c r="R206" t="n">
         <v>0</v>
       </c>
-      <c r="S206" t="b">
+      <c r="S206" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       <c r="R207" t="n">
         <v>0</v>
       </c>
-      <c r="S207" t="b">
+      <c r="S207" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       <c r="R208" t="n">
         <v>0</v>
       </c>
-      <c r="S208" t="b">
+      <c r="S208" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10609,7 +10609,7 @@
       <c r="R209" t="n">
         <v>0</v>
       </c>
-      <c r="S209" t="b">
+      <c r="S209" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10662,7 +10662,7 @@
       <c r="R210" t="n">
         <v>0</v>
       </c>
-      <c r="S210" t="b">
+      <c r="S210" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10715,7 +10715,7 @@
       <c r="R211" t="n">
         <v>0</v>
       </c>
-      <c r="S211" t="b">
+      <c r="S211" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10768,7 +10768,7 @@
       <c r="R212" t="n">
         <v>0</v>
       </c>
-      <c r="S212" t="b">
+      <c r="S212" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10821,7 +10821,7 @@
       <c r="R213" t="n">
         <v>0</v>
       </c>
-      <c r="S213" t="b">
+      <c r="S213" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10874,7 +10874,7 @@
       <c r="R214" t="n">
         <v>0</v>
       </c>
-      <c r="S214" t="b">
+      <c r="S214" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10927,7 +10927,7 @@
       <c r="R215" t="n">
         <v>0</v>
       </c>
-      <c r="S215" t="b">
+      <c r="S215" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10980,7 +10980,7 @@
       <c r="R216" t="n">
         <v>0</v>
       </c>
-      <c r="S216" t="b">
+      <c r="S216" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11033,7 +11033,7 @@
       <c r="R217" t="n">
         <v>0</v>
       </c>
-      <c r="S217" t="b">
+      <c r="S217" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11086,7 +11086,7 @@
       <c r="R218" t="n">
         <v>0</v>
       </c>
-      <c r="S218" t="b">
+      <c r="S218" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11139,7 +11139,7 @@
       <c r="R219" t="n">
         <v>0</v>
       </c>
-      <c r="S219" t="b">
+      <c r="S219" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11192,7 +11192,7 @@
       <c r="R220" t="n">
         <v>0</v>
       </c>
-      <c r="S220" t="b">
+      <c r="S220" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11245,7 +11245,7 @@
       <c r="R221" t="n">
         <v>0</v>
       </c>
-      <c r="S221" t="b">
+      <c r="S221" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       <c r="R222" t="n">
         <v>0</v>
       </c>
-      <c r="S222" t="b">
+      <c r="S222" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11351,7 +11351,7 @@
       <c r="R223" t="n">
         <v>0</v>
       </c>
-      <c r="S223" t="b">
+      <c r="S223" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11404,7 +11404,7 @@
       <c r="R224" t="n">
         <v>0</v>
       </c>
-      <c r="S224" t="b">
+      <c r="S224" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11457,7 +11457,7 @@
       <c r="R225" t="n">
         <v>0</v>
       </c>
-      <c r="S225" t="b">
+      <c r="S225" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       <c r="R226" t="n">
         <v>0</v>
       </c>
-      <c r="S226" t="b">
+      <c r="S226" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11563,7 +11563,7 @@
       <c r="R227" t="n">
         <v>0</v>
       </c>
-      <c r="S227" t="b">
+      <c r="S227" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       <c r="R228" t="n">
         <v>0</v>
       </c>
-      <c r="S228" t="b">
+      <c r="S228" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       <c r="R229" t="n">
         <v>0</v>
       </c>
-      <c r="S229" t="b">
+      <c r="S229" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       <c r="R230" t="n">
         <v>0</v>
       </c>
-      <c r="S230" t="b">
+      <c r="S230" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
       <c r="R231" t="n">
         <v>0</v>
       </c>
-      <c r="S231" t="b">
+      <c r="S231" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       <c r="R232" t="n">
         <v>0</v>
       </c>
-      <c r="S232" t="b">
+      <c r="S232" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11877,7 +11877,7 @@
       <c r="R233" t="n">
         <v>0</v>
       </c>
-      <c r="S233" t="b">
+      <c r="S233" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11930,7 +11930,7 @@
       <c r="R234" t="n">
         <v>0</v>
       </c>
-      <c r="S234" t="b">
+      <c r="S234" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11983,7 +11983,7 @@
       <c r="R235" t="n">
         <v>0</v>
       </c>
-      <c r="S235" t="b">
+      <c r="S235" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
       <c r="R236" t="n">
         <v>0</v>
       </c>
-      <c r="S236" t="b">
+      <c r="S236" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12089,7 +12089,7 @@
       <c r="R237" t="n">
         <v>0</v>
       </c>
-      <c r="S237" t="b">
+      <c r="S237" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12142,7 +12142,7 @@
       <c r="R238" t="n">
         <v>0</v>
       </c>
-      <c r="S238" t="b">
+      <c r="S238" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       <c r="R239" t="n">
         <v>0</v>
       </c>
-      <c r="S239" t="b">
+      <c r="S239" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12248,7 +12248,7 @@
       <c r="R240" t="n">
         <v>0</v>
       </c>
-      <c r="S240" t="b">
+      <c r="S240" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12301,7 +12301,7 @@
       <c r="R241" t="n">
         <v>0</v>
       </c>
-      <c r="S241" t="b">
+      <c r="S241" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       <c r="R242" t="n">
         <v>0</v>
       </c>
-      <c r="S242" t="b">
+      <c r="S242" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12407,7 +12407,7 @@
       <c r="R243" t="n">
         <v>0</v>
       </c>
-      <c r="S243" t="b">
+      <c r="S243" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12460,7 +12460,7 @@
       <c r="R244" t="n">
         <v>0</v>
       </c>
-      <c r="S244" t="b">
+      <c r="S244" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12509,7 +12509,7 @@
       <c r="R245" t="n">
         <v>0</v>
       </c>
-      <c r="S245" t="b">
+      <c r="S245" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12558,7 +12558,7 @@
       <c r="R246" t="n">
         <v>0</v>
       </c>
-      <c r="S246" t="b">
+      <c r="S246" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12607,7 +12607,7 @@
       <c r="R247" t="n">
         <v>0</v>
       </c>
-      <c r="S247" t="b">
+      <c r="S247" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12660,7 +12660,7 @@
       <c r="R248" t="n">
         <v>0</v>
       </c>
-      <c r="S248" t="b">
+      <c r="S248" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
       <c r="R249" t="n">
         <v>0</v>
       </c>
-      <c r="S249" t="b">
+      <c r="S249" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12762,7 +12762,7 @@
       <c r="R250" t="n">
         <v>0</v>
       </c>
-      <c r="S250" t="b">
+      <c r="S250" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       <c r="R251" t="n">
         <v>0</v>
       </c>
-      <c r="S251" t="b">
+      <c r="S251" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12864,7 +12864,7 @@
       <c r="R252" t="n">
         <v>0</v>
       </c>
-      <c r="S252" t="b">
+      <c r="S252" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12913,7 +12913,7 @@
       <c r="R253" t="n">
         <v>0</v>
       </c>
-      <c r="S253" t="b">
+      <c r="S253" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12966,7 +12966,7 @@
       <c r="R254" t="n">
         <v>0</v>
       </c>
-      <c r="S254" t="b">
+      <c r="S254" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13019,7 +13019,7 @@
       <c r="R255" t="n">
         <v>0</v>
       </c>
-      <c r="S255" t="b">
+      <c r="S255" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13072,7 +13072,7 @@
       <c r="R256" t="n">
         <v>0</v>
       </c>
-      <c r="S256" t="b">
+      <c r="S256" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       <c r="R257" t="n">
         <v>0</v>
       </c>
-      <c r="S257" t="b">
+      <c r="S257" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13178,7 +13178,7 @@
       <c r="R258" t="n">
         <v>0</v>
       </c>
-      <c r="S258" t="b">
+      <c r="S258" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13231,7 +13231,7 @@
       <c r="R259" t="n">
         <v>0</v>
       </c>
-      <c r="S259" t="b">
+      <c r="S259" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13284,7 +13284,7 @@
       <c r="R260" t="n">
         <v>0</v>
       </c>
-      <c r="S260" t="b">
+      <c r="S260" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13333,7 +13333,7 @@
       <c r="R261" t="n">
         <v>0</v>
       </c>
-      <c r="S261" t="b">
+      <c r="S261" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13386,7 +13386,7 @@
       <c r="R262" t="n">
         <v>0</v>
       </c>
-      <c r="S262" t="b">
+      <c r="S262" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13439,7 +13439,7 @@
       <c r="R263" t="n">
         <v>0</v>
       </c>
-      <c r="S263" t="b">
+      <c r="S263" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13492,7 +13492,7 @@
       <c r="R264" t="n">
         <v>0</v>
       </c>
-      <c r="S264" t="b">
+      <c r="S264" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13545,7 +13545,7 @@
       <c r="R265" t="n">
         <v>0</v>
       </c>
-      <c r="S265" t="b">
+      <c r="S265" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13598,7 +13598,7 @@
       <c r="R266" t="n">
         <v>0</v>
       </c>
-      <c r="S266" t="b">
+      <c r="S266" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13651,7 +13651,7 @@
       <c r="R267" t="n">
         <v>0</v>
       </c>
-      <c r="S267" t="b">
+      <c r="S267" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       <c r="R268" t="n">
         <v>0</v>
       </c>
-      <c r="S268" t="b">
+      <c r="S268" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13757,7 +13757,7 @@
       <c r="R269" t="n">
         <v>0</v>
       </c>
-      <c r="S269" t="b">
+      <c r="S269" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13810,7 +13810,7 @@
       <c r="R270" t="n">
         <v>0</v>
       </c>
-      <c r="S270" t="b">
+      <c r="S270" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       <c r="R271" t="n">
         <v>0</v>
       </c>
-      <c r="S271" t="b">
+      <c r="S271" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13916,7 +13916,7 @@
       <c r="R272" t="n">
         <v>0</v>
       </c>
-      <c r="S272" t="b">
+      <c r="S272" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13969,7 +13969,7 @@
       <c r="R273" t="n">
         <v>0</v>
       </c>
-      <c r="S273" t="b">
+      <c r="S273" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       <c r="R274" t="n">
         <v>0</v>
       </c>
-      <c r="S274" t="b">
+      <c r="S274" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
       <c r="R275" t="n">
         <v>0</v>
       </c>
-      <c r="S275" t="b">
+      <c r="S275" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14128,7 +14128,7 @@
       <c r="R276" t="n">
         <v>0</v>
       </c>
-      <c r="S276" t="b">
+      <c r="S276" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14181,7 +14181,7 @@
       <c r="R277" t="n">
         <v>0</v>
       </c>
-      <c r="S277" t="b">
+      <c r="S277" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14234,7 +14234,7 @@
       <c r="R278" t="n">
         <v>0</v>
       </c>
-      <c r="S278" t="b">
+      <c r="S278" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14287,7 +14287,7 @@
       <c r="R279" t="n">
         <v>0</v>
       </c>
-      <c r="S279" t="b">
+      <c r="S279" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       <c r="R280" t="n">
         <v>0</v>
       </c>
-      <c r="S280" t="b">
+      <c r="S280" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14393,7 +14393,7 @@
       <c r="R281" t="n">
         <v>0</v>
       </c>
-      <c r="S281" t="b">
+      <c r="S281" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14446,7 +14446,7 @@
       <c r="R282" t="n">
         <v>0</v>
       </c>
-      <c r="S282" t="b">
+      <c r="S282" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14499,7 +14499,7 @@
       <c r="R283" t="n">
         <v>0</v>
       </c>
-      <c r="S283" t="b">
+      <c r="S283" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14552,7 +14552,7 @@
       <c r="R284" t="n">
         <v>0</v>
       </c>
-      <c r="S284" t="b">
+      <c r="S284" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14605,7 +14605,7 @@
       <c r="R285" t="n">
         <v>0</v>
       </c>
-      <c r="S285" t="b">
+      <c r="S285" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14658,7 +14658,7 @@
       <c r="R286" t="n">
         <v>0</v>
       </c>
-      <c r="S286" t="b">
+      <c r="S286" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14711,7 +14711,7 @@
       <c r="R287" t="n">
         <v>0</v>
       </c>
-      <c r="S287" t="b">
+      <c r="S287" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14764,7 +14764,7 @@
       <c r="R288" t="n">
         <v>0</v>
       </c>
-      <c r="S288" t="b">
+      <c r="S288" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14817,7 +14817,7 @@
       <c r="R289" t="n">
         <v>0</v>
       </c>
-      <c r="S289" t="b">
+      <c r="S289" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14870,7 +14870,7 @@
       <c r="R290" t="n">
         <v>0</v>
       </c>
-      <c r="S290" t="b">
+      <c r="S290" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14923,7 +14923,7 @@
       <c r="R291" t="n">
         <v>0</v>
       </c>
-      <c r="S291" t="b">
+      <c r="S291" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14976,7 +14976,7 @@
       <c r="R292" t="n">
         <v>0</v>
       </c>
-      <c r="S292" t="b">
+      <c r="S292" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       <c r="R293" t="n">
         <v>0</v>
       </c>
-      <c r="S293" t="b">
+      <c r="S293" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       <c r="R294" t="n">
         <v>0</v>
       </c>
-      <c r="S294" t="b">
+      <c r="S294" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15135,7 +15135,7 @@
       <c r="R295" t="n">
         <v>0</v>
       </c>
-      <c r="S295" t="b">
+      <c r="S295" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15188,7 +15188,7 @@
       <c r="R296" t="n">
         <v>0</v>
       </c>
-      <c r="S296" t="b">
+      <c r="S296" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       <c r="R297" t="n">
         <v>0</v>
       </c>
-      <c r="S297" t="b">
+      <c r="S297" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       <c r="R298" t="n">
         <v>0</v>
       </c>
-      <c r="S298" t="b">
+      <c r="S298" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15347,7 +15347,7 @@
       <c r="R299" t="n">
         <v>0</v>
       </c>
-      <c r="S299" t="b">
+      <c r="S299" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15400,7 +15400,7 @@
       <c r="R300" t="n">
         <v>0</v>
       </c>
-      <c r="S300" t="b">
+      <c r="S300" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15453,7 +15453,7 @@
       <c r="R301" t="n">
         <v>0</v>
       </c>
-      <c r="S301" t="b">
+      <c r="S301" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15506,7 +15506,7 @@
       <c r="R302" t="n">
         <v>0</v>
       </c>
-      <c r="S302" t="b">
+      <c r="S302" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15559,7 +15559,7 @@
       <c r="R303" t="n">
         <v>0</v>
       </c>
-      <c r="S303" t="b">
+      <c r="S303" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15612,7 +15612,7 @@
       <c r="R304" t="n">
         <v>0</v>
       </c>
-      <c r="S304" t="b">
+      <c r="S304" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15665,7 +15665,7 @@
       <c r="R305" t="n">
         <v>0</v>
       </c>
-      <c r="S305" t="b">
+      <c r="S305" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15718,7 +15718,7 @@
       <c r="R306" t="n">
         <v>0</v>
       </c>
-      <c r="S306" t="b">
+      <c r="S306" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15771,7 +15771,7 @@
       <c r="R307" t="n">
         <v>0</v>
       </c>
-      <c r="S307" t="b">
+      <c r="S307" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15824,7 +15824,7 @@
       <c r="R308" t="n">
         <v>0</v>
       </c>
-      <c r="S308" t="b">
+      <c r="S308" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15877,7 +15877,7 @@
       <c r="R309" t="n">
         <v>0</v>
       </c>
-      <c r="S309" t="b">
+      <c r="S309" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15930,7 +15930,7 @@
       <c r="R310" t="n">
         <v>0</v>
       </c>
-      <c r="S310" t="b">
+      <c r="S310" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15983,7 +15983,7 @@
       <c r="R311" t="n">
         <v>0</v>
       </c>
-      <c r="S311" t="b">
+      <c r="S311" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16036,7 +16036,7 @@
       <c r="R312" t="n">
         <v>0</v>
       </c>
-      <c r="S312" t="b">
+      <c r="S312" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16089,7 +16089,7 @@
       <c r="R313" t="n">
         <v>0</v>
       </c>
-      <c r="S313" t="b">
+      <c r="S313" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16142,7 +16142,7 @@
       <c r="R314" t="n">
         <v>0</v>
       </c>
-      <c r="S314" t="b">
+      <c r="S314" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16195,7 +16195,7 @@
       <c r="R315" t="n">
         <v>0</v>
       </c>
-      <c r="S315" t="b">
+      <c r="S315" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16248,7 +16248,7 @@
       <c r="R316" t="n">
         <v>0</v>
       </c>
-      <c r="S316" t="b">
+      <c r="S316" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16301,7 +16301,7 @@
       <c r="R317" t="n">
         <v>0</v>
       </c>
-      <c r="S317" t="b">
+      <c r="S317" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16354,7 +16354,7 @@
       <c r="R318" t="n">
         <v>0</v>
       </c>
-      <c r="S318" t="b">
+      <c r="S318" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16407,7 +16407,7 @@
       <c r="R319" t="n">
         <v>0</v>
       </c>
-      <c r="S319" t="b">
+      <c r="S319" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16460,7 +16460,7 @@
       <c r="R320" t="n">
         <v>0</v>
       </c>
-      <c r="S320" t="b">
+      <c r="S320" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16513,7 +16513,7 @@
       <c r="R321" t="n">
         <v>0</v>
       </c>
-      <c r="S321" t="b">
+      <c r="S321" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16566,7 +16566,7 @@
       <c r="R322" t="n">
         <v>0</v>
       </c>
-      <c r="S322" t="b">
+      <c r="S322" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       <c r="R323" t="n">
         <v>0</v>
       </c>
-      <c r="S323" t="b">
+      <c r="S323" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16672,7 +16672,7 @@
       <c r="R324" t="n">
         <v>0</v>
       </c>
-      <c r="S324" t="b">
+      <c r="S324" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16725,7 +16725,7 @@
       <c r="R325" t="n">
         <v>0</v>
       </c>
-      <c r="S325" t="b">
+      <c r="S325" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16778,7 +16778,7 @@
       <c r="R326" t="n">
         <v>0</v>
       </c>
-      <c r="S326" t="b">
+      <c r="S326" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16831,7 +16831,7 @@
       <c r="R327" t="n">
         <v>0</v>
       </c>
-      <c r="S327" t="b">
+      <c r="S327" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16884,7 +16884,7 @@
       <c r="R328" t="n">
         <v>0</v>
       </c>
-      <c r="S328" t="b">
+      <c r="S328" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16937,7 +16937,7 @@
       <c r="R329" t="n">
         <v>0</v>
       </c>
-      <c r="S329" t="b">
+      <c r="S329" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16990,7 +16990,7 @@
       <c r="R330" t="n">
         <v>0</v>
       </c>
-      <c r="S330" t="b">
+      <c r="S330" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17043,7 +17043,7 @@
       <c r="R331" t="n">
         <v>0</v>
       </c>
-      <c r="S331" t="b">
+      <c r="S331" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17096,7 +17096,7 @@
       <c r="R332" t="n">
         <v>0</v>
       </c>
-      <c r="S332" t="b">
+      <c r="S332" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17149,7 +17149,7 @@
       <c r="R333" t="n">
         <v>0</v>
       </c>
-      <c r="S333" t="b">
+      <c r="S333" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17202,7 +17202,7 @@
       <c r="R334" t="n">
         <v>0</v>
       </c>
-      <c r="S334" t="b">
+      <c r="S334" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17255,7 +17255,7 @@
       <c r="R335" t="n">
         <v>0</v>
       </c>
-      <c r="S335" t="b">
+      <c r="S335" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17308,7 +17308,7 @@
       <c r="R336" t="n">
         <v>0</v>
       </c>
-      <c r="S336" t="b">
+      <c r="S336" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17361,7 +17361,7 @@
       <c r="R337" t="n">
         <v>0</v>
       </c>
-      <c r="S337" t="b">
+      <c r="S337" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17414,7 +17414,7 @@
       <c r="R338" t="n">
         <v>0</v>
       </c>
-      <c r="S338" t="b">
+      <c r="S338" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17467,7 +17467,7 @@
       <c r="R339" t="n">
         <v>0</v>
       </c>
-      <c r="S339" t="b">
+      <c r="S339" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17520,7 +17520,7 @@
       <c r="R340" t="n">
         <v>0</v>
       </c>
-      <c r="S340" t="b">
+      <c r="S340" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17573,7 +17573,7 @@
       <c r="R341" t="n">
         <v>0</v>
       </c>
-      <c r="S341" t="b">
+      <c r="S341" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17626,7 +17626,7 @@
       <c r="R342" t="n">
         <v>0</v>
       </c>
-      <c r="S342" t="b">
+      <c r="S342" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17679,7 +17679,7 @@
       <c r="R343" t="n">
         <v>0</v>
       </c>
-      <c r="S343" t="b">
+      <c r="S343" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17732,7 +17732,7 @@
       <c r="R344" t="n">
         <v>0</v>
       </c>
-      <c r="S344" t="b">
+      <c r="S344" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17785,7 +17785,7 @@
       <c r="R345" t="n">
         <v>0</v>
       </c>
-      <c r="S345" t="b">
+      <c r="S345" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17838,7 +17838,7 @@
       <c r="R346" t="n">
         <v>0</v>
       </c>
-      <c r="S346" t="b">
+      <c r="S346" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17891,7 +17891,7 @@
       <c r="R347" t="n">
         <v>0</v>
       </c>
-      <c r="S347" t="b">
+      <c r="S347" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       <c r="R348" t="n">
         <v>0</v>
       </c>
-      <c r="S348" t="b">
+      <c r="S348" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17997,7 +17997,7 @@
       <c r="R349" t="n">
         <v>0</v>
       </c>
-      <c r="S349" t="b">
+      <c r="S349" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18050,7 +18050,7 @@
       <c r="R350" t="n">
         <v>0</v>
       </c>
-      <c r="S350" t="b">
+      <c r="S350" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18103,7 +18103,7 @@
       <c r="R351" t="n">
         <v>0</v>
       </c>
-      <c r="S351" t="b">
+      <c r="S351" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18156,7 +18156,7 @@
       <c r="R352" t="n">
         <v>0</v>
       </c>
-      <c r="S352" t="b">
+      <c r="S352" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18209,7 +18209,7 @@
       <c r="R353" t="n">
         <v>0</v>
       </c>
-      <c r="S353" t="b">
+      <c r="S353" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18262,7 +18262,7 @@
       <c r="R354" t="n">
         <v>0</v>
       </c>
-      <c r="S354" t="b">
+      <c r="S354" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18315,7 +18315,7 @@
       <c r="R355" t="n">
         <v>0</v>
       </c>
-      <c r="S355" t="b">
+      <c r="S355" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18368,7 +18368,7 @@
       <c r="R356" t="n">
         <v>0</v>
       </c>
-      <c r="S356" t="b">
+      <c r="S356" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18417,7 +18417,7 @@
       <c r="R357" t="n">
         <v>0</v>
       </c>
-      <c r="S357" t="b">
+      <c r="S357" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18470,7 +18470,7 @@
       <c r="R358" t="n">
         <v>0</v>
       </c>
-      <c r="S358" t="b">
+      <c r="S358" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18519,7 +18519,7 @@
       <c r="R359" t="n">
         <v>0</v>
       </c>
-      <c r="S359" t="b">
+      <c r="S359" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18568,7 +18568,7 @@
       <c r="R360" t="n">
         <v>0</v>
       </c>
-      <c r="S360" t="b">
+      <c r="S360" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18617,7 +18617,7 @@
       <c r="R361" t="n">
         <v>0</v>
       </c>
-      <c r="S361" t="b">
+      <c r="S361" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18666,7 +18666,7 @@
       <c r="R362" t="n">
         <v>0</v>
       </c>
-      <c r="S362" t="b">
+      <c r="S362" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       <c r="R363" t="n">
         <v>0</v>
       </c>
-      <c r="S363" t="b">
+      <c r="S363" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18764,7 +18764,7 @@
       <c r="R364" t="n">
         <v>0</v>
       </c>
-      <c r="S364" t="b">
+      <c r="S364" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18813,7 +18813,7 @@
       <c r="R365" t="n">
         <v>0</v>
       </c>
-      <c r="S365" t="b">
+      <c r="S365" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18862,7 +18862,7 @@
       <c r="R366" t="n">
         <v>0</v>
       </c>
-      <c r="S366" t="b">
+      <c r="S366" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18911,7 +18911,7 @@
       <c r="R367" t="n">
         <v>0</v>
       </c>
-      <c r="S367" t="b">
+      <c r="S367" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18960,7 +18960,7 @@
       <c r="R368" t="n">
         <v>0</v>
       </c>
-      <c r="S368" t="b">
+      <c r="S368" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19009,7 +19009,7 @@
       <c r="R369" t="n">
         <v>0</v>
       </c>
-      <c r="S369" t="b">
+      <c r="S369" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19058,7 +19058,7 @@
       <c r="R370" t="n">
         <v>0</v>
       </c>
-      <c r="S370" t="b">
+      <c r="S370" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19107,7 +19107,7 @@
       <c r="R371" t="n">
         <v>0</v>
       </c>
-      <c r="S371" t="b">
+      <c r="S371" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       <c r="R372" t="n">
         <v>0</v>
       </c>
-      <c r="S372" t="b">
+      <c r="S372" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19205,7 +19205,7 @@
       <c r="R373" t="n">
         <v>0</v>
       </c>
-      <c r="S373" t="b">
+      <c r="S373" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19254,7 +19254,7 @@
       <c r="R374" t="n">
         <v>0</v>
       </c>
-      <c r="S374" t="b">
+      <c r="S374" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19303,7 +19303,7 @@
       <c r="R375" t="n">
         <v>0</v>
       </c>
-      <c r="S375" t="b">
+      <c r="S375" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19356,7 +19356,7 @@
       <c r="R376" t="n">
         <v>0</v>
       </c>
-      <c r="S376" t="b">
+      <c r="S376" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19409,7 +19409,7 @@
       <c r="R377" t="n">
         <v>0</v>
       </c>
-      <c r="S377" t="b">
+      <c r="S377" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19458,7 +19458,7 @@
       <c r="R378" t="n">
         <v>0</v>
       </c>
-      <c r="S378" t="b">
+      <c r="S378" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19507,7 +19507,7 @@
       <c r="R379" t="n">
         <v>0</v>
       </c>
-      <c r="S379" t="b">
+      <c r="S379" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19556,7 +19556,7 @@
       <c r="R380" t="n">
         <v>0</v>
       </c>
-      <c r="S380" t="b">
+      <c r="S380" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19609,7 +19609,7 @@
       <c r="R381" t="n">
         <v>0</v>
       </c>
-      <c r="S381" t="b">
+      <c r="S381" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19662,7 +19662,7 @@
       <c r="R382" t="n">
         <v>0</v>
       </c>
-      <c r="S382" t="b">
+      <c r="S382" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19715,7 +19715,7 @@
       <c r="R383" t="n">
         <v>0</v>
       </c>
-      <c r="S383" t="b">
+      <c r="S383" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19768,7 +19768,7 @@
       <c r="R384" t="n">
         <v>0</v>
       </c>
-      <c r="S384" t="b">
+      <c r="S384" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19821,7 +19821,7 @@
       <c r="R385" t="n">
         <v>0</v>
       </c>
-      <c r="S385" t="b">
+      <c r="S385" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19874,7 +19874,7 @@
       <c r="R386" t="n">
         <v>0</v>
       </c>
-      <c r="S386" t="b">
+      <c r="S386" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19927,7 +19927,7 @@
       <c r="R387" t="n">
         <v>0</v>
       </c>
-      <c r="S387" t="b">
+      <c r="S387" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19976,7 +19976,7 @@
       <c r="R388" t="n">
         <v>0</v>
       </c>
-      <c r="S388" t="b">
+      <c r="S388" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20029,7 +20029,7 @@
       <c r="R389" t="n">
         <v>0</v>
       </c>
-      <c r="S389" t="b">
+      <c r="S389" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20082,7 +20082,7 @@
       <c r="R390" t="n">
         <v>0</v>
       </c>
-      <c r="S390" t="b">
+      <c r="S390" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20135,7 +20135,7 @@
       <c r="R391" t="n">
         <v>0</v>
       </c>
-      <c r="S391" t="b">
+      <c r="S391" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20188,7 +20188,7 @@
       <c r="R392" t="n">
         <v>0</v>
       </c>
-      <c r="S392" t="b">
+      <c r="S392" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20241,7 +20241,7 @@
       <c r="R393" t="n">
         <v>0</v>
       </c>
-      <c r="S393" t="b">
+      <c r="S393" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20294,7 +20294,7 @@
       <c r="R394" t="n">
         <v>0</v>
       </c>
-      <c r="S394" t="b">
+      <c r="S394" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20347,7 +20347,7 @@
       <c r="R395" t="n">
         <v>0</v>
       </c>
-      <c r="S395" t="b">
+      <c r="S395" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20400,7 +20400,7 @@
       <c r="R396" t="n">
         <v>0</v>
       </c>
-      <c r="S396" t="b">
+      <c r="S396" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20453,7 +20453,7 @@
       <c r="R397" t="n">
         <v>0</v>
       </c>
-      <c r="S397" t="b">
+      <c r="S397" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20502,7 +20502,7 @@
       <c r="R398" t="n">
         <v>0</v>
       </c>
-      <c r="S398" t="b">
+      <c r="S398" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20555,7 +20555,7 @@
       <c r="R399" t="n">
         <v>0</v>
       </c>
-      <c r="S399" t="b">
+      <c r="S399" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20608,7 +20608,7 @@
       <c r="R400" t="n">
         <v>0</v>
       </c>
-      <c r="S400" t="b">
+      <c r="S400" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20661,7 +20661,7 @@
       <c r="R401" t="n">
         <v>0</v>
       </c>
-      <c r="S401" t="b">
+      <c r="S401" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20714,7 +20714,7 @@
       <c r="R402" t="n">
         <v>0</v>
       </c>
-      <c r="S402" t="b">
+      <c r="S402" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20767,7 +20767,7 @@
       <c r="R403" t="n">
         <v>0</v>
       </c>
-      <c r="S403" t="b">
+      <c r="S403" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20820,7 +20820,7 @@
       <c r="R404" t="n">
         <v>0</v>
       </c>
-      <c r="S404" t="b">
+      <c r="S404" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20871,7 +20871,7 @@
       <c r="R405" t="n">
         <v>0</v>
       </c>
-      <c r="S405" t="b">
+      <c r="S405" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20924,7 +20924,7 @@
       <c r="R406" t="n">
         <v>1000</v>
       </c>
-      <c r="S406" t="b">
+      <c r="S406" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20975,7 +20975,7 @@
       <c r="R407" t="n">
         <v>0</v>
       </c>
-      <c r="S407" t="b">
+      <c r="S407" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21018,7 +21018,7 @@
       <c r="R408" t="n">
         <v>0</v>
       </c>
-      <c r="S408" t="b">
+      <c r="S408" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21061,7 +21061,7 @@
       <c r="R409" t="n">
         <v>0</v>
       </c>
-      <c r="S409" t="b">
+      <c r="S409" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21104,7 +21104,7 @@
       <c r="R410" t="n">
         <v>0</v>
       </c>
-      <c r="S410" t="b">
+      <c r="S410" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21147,9 +21147,165 @@
       <c r="R411" t="n">
         <v>0</v>
       </c>
-      <c r="S411" t="b">
-        <v>1</v>
-      </c>
+      <c r="S411" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>413</v>
+      </c>
+      <c r="B412" t="inlineStr"/>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>현상제</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr"/>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>NDT_CHEM</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr"/>
+      <c r="J412" t="inlineStr"/>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M412" t="n">
+        <v>0</v>
+      </c>
+      <c r="N412" t="inlineStr"/>
+      <c r="O412" t="inlineStr"/>
+      <c r="P412" t="inlineStr"/>
+      <c r="Q412" t="n">
+        <v>5</v>
+      </c>
+      <c r="R412" t="inlineStr"/>
+      <c r="S412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>414</v>
+      </c>
+      <c r="B413" t="inlineStr"/>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>PT 약품</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr"/>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M413" t="n">
+        <v>0</v>
+      </c>
+      <c r="N413" t="inlineStr"/>
+      <c r="O413" t="inlineStr"/>
+      <c r="P413" t="inlineStr"/>
+      <c r="Q413" t="n">
+        <v>10</v>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>415</v>
+      </c>
+      <c r="B414" t="inlineStr"/>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>세척제</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr"/>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>NDT_CHEM</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr"/>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M414" t="n">
+        <v>0</v>
+      </c>
+      <c r="N414" t="inlineStr"/>
+      <c r="O414" t="inlineStr"/>
+      <c r="P414" t="inlineStr"/>
+      <c r="Q414" t="n">
+        <v>5</v>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>416</v>
+      </c>
+      <c r="B415" t="inlineStr"/>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>PT약품</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr"/>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr"/>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M415" t="n">
+        <v>0</v>
+      </c>
+      <c r="N415" t="inlineStr"/>
+      <c r="O415" t="inlineStr"/>
+      <c r="P415" t="inlineStr"/>
+      <c r="Q415" t="n">
+        <v>10</v>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21162,7 +21318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21221,104 +21377,6 @@
           <t>차량비고</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46024.58678976852</v>
-      </c>
-      <c r="B2" t="n">
-        <v>410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>-51</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>롯데현장 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>롯데현장</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>탑차 81도4028</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>156,789</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>주유, 청결, 엔진오일, 타이어, 전조등</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46059.73407405835</v>
-      </c>
-      <c r="B3" t="n">
-        <v>410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>-51</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>롯데현장 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>대리 우명광, 부장 주진철, 주임 김진환</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>롯데현장</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>탑차 81도4028</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>156,789</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>주유, 청결, 엔진오일, 타이어, 전조등</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21382,7 +21440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK4"/>
+  <dimension ref="A1:BK2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21851,336 +21909,6 @@
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>롯데현장</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>410</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" s="1" t="n">
-        <v>46083.58678977221</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>R-RAY</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>25000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1250000</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>50</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>(주야간) 20:00~익일05:00</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>55,500</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>탑차 81도4028</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>156,789</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>주유, 청결, 엔진오일, 타이어, 전조등</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>롯데현장</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>410</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:37:03.998813</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>대리 우명광</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>R-RAY</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>25000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1250000</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>50</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>(주야간) 20:00~익일05:00</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>55,500</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>(주야간) 20:00~익일05:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>55,500</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>주임 김진환</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>(주야간) 20:00~익일05:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>55,500</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>탑차 81도4028</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>156,789</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>주유, 청결, 엔진오일, 타이어, 전조등</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -21318,7 +21318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21377,6 +21377,76 @@
           <t>차량비고</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45758.8463250218</v>
+      </c>
+      <c r="B2" t="n">
+        <v>415</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>대리 현해룡, 부장 주진철, 주임 주유철</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45758.8463250218</v>
+      </c>
+      <c r="B3" t="n">
+        <v>413</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>대리 현해룡, 부장 주진철, 주임 주유철</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21440,7 +21510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK2"/>
+  <dimension ref="A1:BK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21909,6 +21979,167 @@
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>416</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-04-12 20:18:42.482004</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>대리 현해룡</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4200</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~21:00</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~21:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>주임 주유철</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~21:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -21380,7 +21380,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45758.8463250218</v>
+        <v>45758.84632502315</v>
       </c>
       <c r="B2" t="n">
         <v>415</v>
@@ -21415,7 +21415,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45758.8463250218</v>
+        <v>45758.84632502315</v>
       </c>
       <c r="B3" t="n">
         <v>413</v>
@@ -21980,10 +21980,8 @@
       <c r="BK2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-04-11</t>
-        </is>
+      <c r="A3" s="1" t="n">
+        <v>45758</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -21997,10 +21995,8 @@
         <v>0</v>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-04-12 20:18:42.482004</t>
-        </is>
+      <c r="F3" s="1" t="n">
+        <v>46124.84632502319</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -22134,7 +22130,9 @@
       <c r="BF3" t="n">
         <v>0</v>
       </c>
-      <c r="BG3" t="inlineStr"/>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="inlineStr"/>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S415"/>
+  <dimension ref="A1:S416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21306,6 +21306,45 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>417</v>
+      </c>
+      <c r="B416" t="inlineStr"/>
+      <c r="C416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Carestream AA400-3⅓*17"</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr"/>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>FILM</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr"/>
+      <c r="J416" t="inlineStr"/>
+      <c r="K416" t="inlineStr"/>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M416" t="n">
+        <v>0</v>
+      </c>
+      <c r="N416" t="inlineStr"/>
+      <c r="O416" t="inlineStr"/>
+      <c r="P416" t="inlineStr"/>
+      <c r="Q416" t="n">
+        <v>10</v>
+      </c>
+      <c r="R416" t="inlineStr"/>
+      <c r="S416" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21318,7 +21357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21377,76 +21416,6 @@
           <t>차량비고</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>45758.84632502315</v>
-      </c>
-      <c r="B2" t="n">
-        <v>415</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>K1 PJT 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>대리 현해룡, 부장 주진철, 주임 주유철</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>K1 PJT</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>45758.84632502315</v>
-      </c>
-      <c r="B3" t="n">
-        <v>413</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>K1 PJT 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>대리 현해룡, 부장 주진철, 주임 주유철</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>K1 PJT</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21510,7 +21479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK3"/>
+  <dimension ref="A1:BK4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21980,23 +21949,21 @@
       <c r="BK2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>45758</v>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>K1 PJT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" s="1" t="n">
-        <v>46124.84632502319</v>
+        <v>46124.90375616898</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -22024,12 +21991,16 @@
           <t>대리 현해룡</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>R-RAY</t>
+        </is>
+      </c>
       <c r="P3" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="Q3" t="n">
-        <v>4200</v>
+        <v>25500</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -22038,24 +22009,24 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2100000</v>
+        <v>1275000</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>(주간) 09:00~21:00</t>
+          <t>(주야간) 09:00~익일05:00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>150,000</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -22065,12 +22036,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>(주간) 09:00~21:00</t>
+          <t>(주야간) 09:00~익일05:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>150,000</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -22080,12 +22051,12 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>(주간) 09:00~21:00</t>
+          <t>(주야간) 09:00~익일05:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>150,000</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
@@ -22122,10 +22093,10 @@
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
@@ -22133,10 +22104,195 @@
       <c r="BG3" t="n">
         <v>0</v>
       </c>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>탑차 81도4028</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>112,445</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>주유, 청결, 엔진오일, 타이어, 전조등</t>
+        </is>
+      </c>
       <c r="BK3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>408</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" s="1" t="n">
+        <v>46124.90651913195</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>김성현</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>R-RAY</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>25000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>50</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>(주야간) 09:00~20:00</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>82,500</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>김진환</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>(주야간) 09:00~20:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>82,500</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>부장 박광복</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>(주야간) 09:00~20:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>82,500</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>탑차 81도4028</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>111,111</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>주유, 청결, 엔진오일, 타이어, 전조등</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -20872,7 +20872,7 @@
         <v>0</v>
       </c>
       <c r="S405" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -20925,7 +20925,7 @@
         <v>1000</v>
       </c>
       <c r="S406" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407">
@@ -20976,7 +20976,7 @@
         <v>0</v>
       </c>
       <c r="S407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408">
@@ -21019,7 +21019,7 @@
         <v>0</v>
       </c>
       <c r="S408" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="409">
@@ -21062,7 +21062,7 @@
         <v>0</v>
       </c>
       <c r="S409" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="410">
@@ -21105,7 +21105,7 @@
         <v>0</v>
       </c>
       <c r="S410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411">
@@ -21148,7 +21148,7 @@
         <v>0</v>
       </c>
       <c r="S411" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="412">
@@ -21188,7 +21188,9 @@
         <v>5</v>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="inlineStr"/>
+      <c r="S412" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -21227,7 +21229,9 @@
         <v>10</v>
       </c>
       <c r="R413" t="inlineStr"/>
-      <c r="S413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -21266,7 +21270,9 @@
         <v>5</v>
       </c>
       <c r="R414" t="inlineStr"/>
-      <c r="S414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -21305,7 +21311,9 @@
         <v>10</v>
       </c>
       <c r="R415" t="inlineStr"/>
-      <c r="S415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -21344,7 +21352,9 @@
         <v>10</v>
       </c>
       <c r="R416" t="inlineStr"/>
-      <c r="S416" t="inlineStr"/>
+      <c r="S416" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21357,7 +21367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21416,6 +21426,37 @@
           <t>차량비고</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46127.83419630787</v>
+      </c>
+      <c r="B2" t="n">
+        <v>410</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S416"/>
+  <dimension ref="A1:S419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21354,6 +21354,153 @@
       <c r="R416" t="inlineStr"/>
       <c r="S416" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>418</v>
+      </c>
+      <c r="B417" t="inlineStr"/>
+      <c r="C417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>PT약품</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>세척제</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr"/>
+      <c r="H417" t="inlineStr"/>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>NAWOO</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr"/>
+      <c r="K417" t="n">
+        <v>0</v>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M417" t="n">
+        <v>0</v>
+      </c>
+      <c r="N417" t="inlineStr"/>
+      <c r="O417" t="inlineStr"/>
+      <c r="P417" t="inlineStr"/>
+      <c r="Q417" t="n">
+        <v>0</v>
+      </c>
+      <c r="R417" t="n">
+        <v>0</v>
+      </c>
+      <c r="S417" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>419</v>
+      </c>
+      <c r="B418" t="inlineStr"/>
+      <c r="C418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>PT약품</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>침투제</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr"/>
+      <c r="H418" t="inlineStr"/>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>NAWOO</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr"/>
+      <c r="K418" t="n">
+        <v>0</v>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M418" t="n">
+        <v>0</v>
+      </c>
+      <c r="N418" t="inlineStr"/>
+      <c r="O418" t="inlineStr"/>
+      <c r="P418" t="inlineStr"/>
+      <c r="Q418" t="n">
+        <v>0</v>
+      </c>
+      <c r="R418" t="n">
+        <v>0</v>
+      </c>
+      <c r="S418" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>420</v>
+      </c>
+      <c r="B419" t="inlineStr"/>
+      <c r="C419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>PT약품</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>현상제</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr"/>
+      <c r="H419" t="inlineStr"/>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>NAWOO</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr"/>
+      <c r="K419" t="n">
+        <v>0</v>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M419" t="n">
+        <v>0</v>
+      </c>
+      <c r="N419" t="inlineStr"/>
+      <c r="O419" t="inlineStr"/>
+      <c r="P419" t="inlineStr"/>
+      <c r="Q419" t="n">
+        <v>0</v>
+      </c>
+      <c r="R419" t="n">
+        <v>0</v>
+      </c>
+      <c r="S419" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S419"/>
+  <dimension ref="A1:S422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21105,7 +21105,7 @@
         <v>0</v>
       </c>
       <c r="S410" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -21402,7 +21402,7 @@
         <v>0</v>
       </c>
       <c r="S417" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="418">
@@ -21451,7 +21451,7 @@
         <v>0</v>
       </c>
       <c r="S418" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="419">
@@ -21500,6 +21500,165 @@
         <v>0</v>
       </c>
       <c r="S419" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>421</v>
+      </c>
+      <c r="B420" t="inlineStr"/>
+      <c r="C420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>MT약품</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>MT약품</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr"/>
+      <c r="I420" t="inlineStr"/>
+      <c r="J420" t="inlineStr"/>
+      <c r="K420" t="n">
+        <v>0</v>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M420" t="n">
+        <v>0</v>
+      </c>
+      <c r="N420" t="inlineStr"/>
+      <c r="O420" t="inlineStr"/>
+      <c r="P420" t="inlineStr"/>
+      <c r="Q420" t="n">
+        <v>10</v>
+      </c>
+      <c r="R420" t="n">
+        <v>0</v>
+      </c>
+      <c r="S420" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>422</v>
+      </c>
+      <c r="B421" t="inlineStr"/>
+      <c r="C421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>MT약품</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>흑색자분</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr"/>
+      <c r="I421" t="inlineStr"/>
+      <c r="J421" t="inlineStr"/>
+      <c r="K421" t="n">
+        <v>0</v>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M421" t="n">
+        <v>0</v>
+      </c>
+      <c r="N421" t="inlineStr"/>
+      <c r="O421" t="inlineStr"/>
+      <c r="P421" t="inlineStr"/>
+      <c r="Q421" t="n">
+        <v>10</v>
+      </c>
+      <c r="R421" t="n">
+        <v>0</v>
+      </c>
+      <c r="S421" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>423</v>
+      </c>
+      <c r="B422" t="inlineStr"/>
+      <c r="C422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>MT약품</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>백색페인트</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr"/>
+      <c r="I422" t="inlineStr"/>
+      <c r="J422" t="inlineStr"/>
+      <c r="K422" t="n">
+        <v>0</v>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M422" t="n">
+        <v>0</v>
+      </c>
+      <c r="N422" t="inlineStr"/>
+      <c r="O422" t="inlineStr"/>
+      <c r="P422" t="inlineStr"/>
+      <c r="Q422" t="n">
+        <v>10</v>
+      </c>
+      <c r="R422" t="n">
+        <v>0</v>
+      </c>
+      <c r="S422" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21514,7 +21673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21573,37 +21732,6 @@
           <t>차량비고</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46127.83419630787</v>
-      </c>
-      <c r="B2" t="n">
-        <v>410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>-200</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21667,7 +21795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK4"/>
+  <dimension ref="A1:BM4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21984,6 +22112,16 @@
       <c r="BK1" t="inlineStr">
         <is>
           <t>차량비고</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>RTK_총계</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>회사코드</t>
         </is>
       </c>
     </row>
@@ -22135,6 +22273,8 @@
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -22308,6 +22448,8 @@
         </is>
       </c>
       <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -22481,6 +22623,8 @@
         </is>
       </c>
       <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -21673,7 +21673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21730,6 +21730,57 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>차량비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B2" t="n">
+        <v>410</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-25</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>K1-PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>부장 주진철, 주임 김진환</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -21795,7 +21846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM4"/>
+  <dimension ref="A1:BN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22122,6 +22173,11 @@
       <c r="BM1" t="inlineStr">
         <is>
           <t>회사코드</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>업체명</t>
         </is>
       </c>
     </row>
@@ -22275,6 +22331,7 @@
       <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="inlineStr"/>
       <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -22450,6 +22507,7 @@
       <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr"/>
       <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -22625,6 +22683,165 @@
       <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>410</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" s="1" t="n">
+        <v>46131.88805793982</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>R-RAY</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>09:00~20:00</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>82,500</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>주임 김진환</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:00~20:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>82,500</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S422"/>
+  <dimension ref="A1:S425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,8 +522,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
@@ -575,8 +577,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
@@ -628,8 +632,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
@@ -681,8 +687,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
@@ -734,8 +742,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
@@ -787,8 +797,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
@@ -840,8 +852,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
@@ -893,8 +907,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
@@ -946,8 +962,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
@@ -999,8 +1017,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
@@ -1052,8 +1072,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
@@ -1105,8 +1127,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
@@ -1158,8 +1182,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
@@ -1211,8 +1237,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
@@ -1264,8 +1292,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
@@ -1317,8 +1347,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
@@ -1370,8 +1402,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
@@ -1423,8 +1457,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
@@ -1476,8 +1512,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
@@ -1529,8 +1567,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
@@ -1582,8 +1622,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
@@ -1635,8 +1677,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
@@ -1688,8 +1732,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
@@ -1741,8 +1787,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
@@ -1794,8 +1842,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
@@ -1847,8 +1897,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
@@ -1900,8 +1952,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
@@ -1953,8 +2007,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
@@ -2006,8 +2062,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
@@ -2059,8 +2117,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
@@ -2112,8 +2172,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
@@ -2165,8 +2227,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
@@ -2218,8 +2282,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
@@ -2271,8 +2337,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
@@ -2324,8 +2392,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
@@ -2377,8 +2447,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
@@ -2430,8 +2502,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
@@ -2483,8 +2557,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
@@ -2536,8 +2612,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
@@ -2589,8 +2667,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
@@ -2642,8 +2722,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
@@ -2695,8 +2777,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
@@ -2748,8 +2832,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
@@ -2801,8 +2887,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
@@ -2854,8 +2942,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
@@ -2907,8 +2997,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
@@ -2960,8 +3052,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
@@ -3009,8 +3103,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
@@ -3058,8 +3154,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
@@ -3107,8 +3205,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
@@ -3156,8 +3256,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
@@ -3205,8 +3307,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
@@ -3258,8 +3362,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
@@ -3311,8 +3417,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
@@ -3364,8 +3472,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
@@ -3417,8 +3527,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
@@ -3470,8 +3582,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
@@ -3523,8 +3637,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
@@ -3576,8 +3692,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
@@ -3629,8 +3747,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
@@ -3682,8 +3802,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
@@ -3735,8 +3857,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
@@ -3788,8 +3912,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
@@ -3841,8 +3967,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
@@ -3894,8 +4022,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
@@ -3947,8 +4077,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
@@ -3996,8 +4128,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>67</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
@@ -4045,8 +4179,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
@@ -4098,8 +4234,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
@@ -4151,8 +4289,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
@@ -4204,8 +4344,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
@@ -4257,8 +4399,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
@@ -4310,8 +4454,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
@@ -4363,8 +4509,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
-        <v>74</v>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
@@ -4416,8 +4564,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
-        <v>75</v>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
@@ -4469,8 +4619,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
-        <v>76</v>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
@@ -4518,8 +4670,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
@@ -4571,8 +4725,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
-        <v>78</v>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
@@ -4624,8 +4780,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
-        <v>79</v>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
@@ -4677,8 +4835,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
-        <v>80</v>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
@@ -4730,8 +4890,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
-        <v>81</v>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
@@ -4783,8 +4945,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
-        <v>82</v>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
@@ -4836,8 +5000,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
-        <v>83</v>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
@@ -4889,8 +5055,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
-        <v>84</v>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
@@ -4942,8 +5110,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
-        <v>85</v>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
@@ -4991,8 +5161,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
-        <v>86</v>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
@@ -5040,8 +5212,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
-        <v>87</v>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
@@ -5093,8 +5267,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
-        <v>88</v>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
@@ -5146,8 +5322,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
-        <v>89</v>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
@@ -5199,8 +5377,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="n">
-        <v>90</v>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
@@ -5252,8 +5432,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
-        <v>91</v>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
@@ -5301,8 +5483,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="n">
-        <v>92</v>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
@@ -5354,8 +5538,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
-        <v>93</v>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
@@ -5403,8 +5589,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
-        <v>94</v>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
@@ -5456,8 +5644,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
-        <v>95</v>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
@@ -5509,8 +5699,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
-        <v>96</v>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
@@ -5554,8 +5746,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
-        <v>97</v>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
@@ -5599,8 +5793,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
-        <v>98</v>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
@@ -5644,8 +5840,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
-        <v>99</v>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
@@ -5689,8 +5887,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
-        <v>100</v>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
@@ -5734,8 +5934,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="n">
-        <v>101</v>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
@@ -5779,8 +5981,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="n">
-        <v>102</v>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
@@ -5824,8 +6028,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="n">
-        <v>103</v>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
@@ -5869,8 +6075,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="n">
-        <v>104</v>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
@@ -5914,8 +6122,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="n">
-        <v>105</v>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
@@ -5959,8 +6169,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="n">
-        <v>106</v>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
@@ -6004,8 +6216,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="n">
-        <v>107</v>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
@@ -6049,8 +6263,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="n">
-        <v>108</v>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
@@ -6094,8 +6310,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="n">
-        <v>109</v>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
@@ -6139,8 +6357,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="n">
-        <v>110</v>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
@@ -6184,8 +6404,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="n">
-        <v>111</v>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
@@ -6229,8 +6451,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="n">
-        <v>112</v>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
@@ -6274,8 +6498,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="n">
-        <v>113</v>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
@@ -6319,8 +6545,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="n">
-        <v>114</v>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
@@ -6364,8 +6592,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="n">
-        <v>115</v>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
@@ -6409,8 +6639,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="n">
-        <v>116</v>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
@@ -6454,8 +6686,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="n">
-        <v>117</v>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
@@ -6499,8 +6733,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="n">
-        <v>118</v>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
@@ -6544,8 +6780,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="n">
-        <v>119</v>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
@@ -6589,8 +6827,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="n">
-        <v>120</v>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
@@ -6634,8 +6874,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="n">
-        <v>121</v>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
@@ -6679,8 +6921,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="n">
-        <v>122</v>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
@@ -6724,8 +6968,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="n">
-        <v>123</v>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
@@ -6769,8 +7015,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="n">
-        <v>124</v>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
@@ -6814,8 +7062,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="n">
-        <v>125</v>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
@@ -6859,8 +7109,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="n">
-        <v>126</v>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
@@ -6904,8 +7156,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="n">
-        <v>127</v>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
@@ -6949,8 +7203,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="n">
-        <v>128</v>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
@@ -6994,8 +7250,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="n">
-        <v>129</v>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
@@ -7039,8 +7297,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="n">
-        <v>130</v>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
@@ -7084,8 +7344,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="n">
-        <v>131</v>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
@@ -7129,8 +7391,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="n">
-        <v>132</v>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
@@ -7174,8 +7438,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
-        <v>133</v>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
@@ -7219,8 +7485,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="n">
-        <v>134</v>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
@@ -7264,8 +7532,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="n">
-        <v>135</v>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
@@ -7309,8 +7579,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="n">
-        <v>136</v>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
@@ -7354,8 +7626,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="n">
-        <v>137</v>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
@@ -7399,8 +7673,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="n">
-        <v>138</v>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
@@ -7444,8 +7720,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="n">
-        <v>139</v>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
@@ -7489,8 +7767,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="n">
-        <v>140</v>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
@@ -7534,8 +7814,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="n">
-        <v>141</v>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
@@ -7579,8 +7861,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="n">
-        <v>142</v>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
@@ -7624,8 +7908,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="n">
-        <v>143</v>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
@@ -7669,8 +7955,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="n">
-        <v>144</v>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
@@ -7714,8 +8002,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="n">
-        <v>145</v>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
@@ -7759,8 +8049,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="n">
-        <v>146</v>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
@@ -7804,8 +8096,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="n">
-        <v>147</v>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
@@ -7849,8 +8143,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="n">
-        <v>148</v>
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
@@ -7894,8 +8190,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="n">
-        <v>149</v>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
@@ -7939,8 +8237,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="n">
-        <v>150</v>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
@@ -7984,8 +8284,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="n">
-        <v>151</v>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
@@ -8029,8 +8331,10 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="n">
-        <v>152</v>
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
@@ -8074,8 +8378,10 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="n">
-        <v>153</v>
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
@@ -8119,8 +8425,10 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="n">
-        <v>154</v>
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
@@ -8164,8 +8472,10 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="n">
-        <v>155</v>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
@@ -8209,8 +8519,10 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="n">
-        <v>156</v>
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
@@ -8254,8 +8566,10 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="n">
-        <v>157</v>
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
@@ -8299,8 +8613,10 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="n">
-        <v>158</v>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
@@ -8344,8 +8660,10 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="n">
-        <v>159</v>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
@@ -8389,8 +8707,10 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="n">
-        <v>160</v>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
@@ -8434,8 +8754,10 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="n">
-        <v>161</v>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
@@ -8479,8 +8801,10 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="n">
-        <v>162</v>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
@@ -8524,8 +8848,10 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="n">
-        <v>163</v>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
@@ -8569,8 +8895,10 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="n">
-        <v>164</v>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
@@ -8614,8 +8942,10 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="n">
-        <v>165</v>
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
@@ -8659,8 +8989,10 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="n">
-        <v>166</v>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
@@ -8704,8 +9036,10 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="n">
-        <v>167</v>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
@@ -8749,8 +9083,10 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="n">
-        <v>168</v>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
       </c>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
@@ -8794,8 +9130,10 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="n">
-        <v>169</v>
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
@@ -8839,8 +9177,10 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="n">
-        <v>170</v>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
@@ -8884,8 +9224,10 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="n">
-        <v>171</v>
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
@@ -8929,8 +9271,10 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="n">
-        <v>172</v>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
@@ -8974,8 +9318,10 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="n">
-        <v>173</v>
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
       </c>
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
@@ -9023,8 +9369,10 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="n">
-        <v>174</v>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
@@ -9076,8 +9424,10 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="n">
-        <v>175</v>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
@@ -9129,8 +9479,10 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="n">
-        <v>176</v>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
@@ -9174,8 +9526,10 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="n">
-        <v>177</v>
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
@@ -9219,8 +9573,10 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="n">
-        <v>178</v>
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
@@ -9264,8 +9620,10 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="n">
-        <v>179</v>
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
@@ -9309,8 +9667,10 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="n">
-        <v>180</v>
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
@@ -9354,8 +9714,10 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="n">
-        <v>181</v>
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
       </c>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
@@ -9399,8 +9761,10 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="n">
-        <v>182</v>
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
@@ -9444,8 +9808,10 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="n">
-        <v>183</v>
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
@@ -9489,8 +9855,10 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="n">
-        <v>184</v>
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
       </c>
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
@@ -9534,8 +9902,10 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="n">
-        <v>185</v>
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
       </c>
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
@@ -9579,8 +9949,10 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="n">
-        <v>186</v>
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
       </c>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
@@ -9624,8 +9996,10 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="n">
-        <v>187</v>
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
@@ -9669,8 +10043,10 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="n">
-        <v>188</v>
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
       </c>
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr">
@@ -9714,8 +10090,10 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="n">
-        <v>189</v>
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
       </c>
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr">
@@ -9759,8 +10137,10 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="n">
-        <v>190</v>
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
       </c>
       <c r="B191" t="inlineStr"/>
       <c r="C191" t="inlineStr">
@@ -9804,8 +10184,10 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="n">
-        <v>191</v>
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr">
@@ -9849,8 +10231,10 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="n">
-        <v>192</v>
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
       </c>
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="inlineStr">
@@ -9894,8 +10278,10 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="n">
-        <v>193</v>
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
       </c>
       <c r="B194" t="inlineStr"/>
       <c r="C194" t="inlineStr">
@@ -9939,8 +10325,10 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="n">
-        <v>194</v>
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
       </c>
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="inlineStr">
@@ -9984,8 +10372,10 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="n">
-        <v>195</v>
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr">
@@ -10029,8 +10419,10 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="n">
-        <v>196</v>
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="inlineStr">
@@ -10074,8 +10466,10 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="n">
-        <v>197</v>
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
       </c>
       <c r="B198" t="inlineStr"/>
       <c r="C198" t="inlineStr">
@@ -10119,8 +10513,10 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="n">
-        <v>198</v>
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
       </c>
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr">
@@ -10164,8 +10560,10 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="n">
-        <v>199</v>
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
       </c>
       <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr">
@@ -10209,8 +10607,10 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="n">
-        <v>200</v>
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr">
@@ -10254,8 +10654,10 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="n">
-        <v>201</v>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
       </c>
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="inlineStr">
@@ -10299,8 +10701,10 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="n">
-        <v>202</v>
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="inlineStr">
@@ -10344,8 +10748,10 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="n">
-        <v>203</v>
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
       </c>
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="inlineStr">
@@ -10389,8 +10795,10 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="n">
-        <v>204</v>
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
       </c>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr">
@@ -10434,8 +10842,10 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="n">
-        <v>205</v>
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
       </c>
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="inlineStr">
@@ -10479,8 +10889,10 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="n">
-        <v>206</v>
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
       </c>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr">
@@ -10524,8 +10936,10 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="n">
-        <v>207</v>
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
       </c>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="inlineStr">
@@ -10569,8 +10983,10 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="n">
-        <v>208</v>
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
       </c>
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr">
@@ -10614,8 +11030,10 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="n">
-        <v>209</v>
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
       </c>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
@@ -10667,8 +11085,10 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="n">
-        <v>210</v>
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
       </c>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
@@ -10720,8 +11140,10 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="n">
-        <v>211</v>
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
       </c>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
@@ -10773,8 +11195,10 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="n">
-        <v>212</v>
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
       </c>
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="inlineStr">
@@ -10826,8 +11250,10 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="n">
-        <v>213</v>
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
       </c>
       <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr">
@@ -10879,8 +11305,10 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="n">
-        <v>214</v>
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
       </c>
       <c r="B215" t="inlineStr"/>
       <c r="C215" t="inlineStr">
@@ -10932,8 +11360,10 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="n">
-        <v>215</v>
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
       </c>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr">
@@ -10985,8 +11415,10 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="n">
-        <v>216</v>
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
       </c>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr">
@@ -11038,8 +11470,10 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="n">
-        <v>217</v>
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
       </c>
       <c r="B218" t="inlineStr"/>
       <c r="C218" t="inlineStr">
@@ -11091,8 +11525,10 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="n">
-        <v>218</v>
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
       </c>
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
@@ -11144,8 +11580,10 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="n">
-        <v>219</v>
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
       </c>
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr">
@@ -11197,8 +11635,10 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="n">
-        <v>220</v>
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
       </c>
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="inlineStr">
@@ -11250,8 +11690,10 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="n">
-        <v>221</v>
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
       </c>
       <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr">
@@ -11303,8 +11745,10 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="n">
-        <v>222</v>
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
       </c>
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
@@ -11356,8 +11800,10 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="n">
-        <v>223</v>
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
       </c>
       <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr">
@@ -11409,8 +11855,10 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="n">
-        <v>224</v>
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
       </c>
       <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr">
@@ -11462,8 +11910,10 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="n">
-        <v>225</v>
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
       </c>
       <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr">
@@ -11515,8 +11965,10 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="n">
-        <v>226</v>
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
       </c>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="inlineStr">
@@ -11568,8 +12020,10 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="n">
-        <v>227</v>
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
       </c>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="inlineStr">
@@ -11621,8 +12075,10 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="n">
-        <v>228</v>
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
       </c>
       <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr">
@@ -11670,8 +12126,10 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="n">
-        <v>229</v>
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
       </c>
       <c r="B230" t="inlineStr"/>
       <c r="C230" t="inlineStr">
@@ -11723,8 +12181,10 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="n">
-        <v>230</v>
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
       </c>
       <c r="B231" t="inlineStr"/>
       <c r="C231" t="inlineStr">
@@ -11776,8 +12236,10 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="n">
-        <v>231</v>
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
       </c>
       <c r="B232" t="inlineStr"/>
       <c r="C232" t="inlineStr">
@@ -11829,8 +12291,10 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="n">
-        <v>232</v>
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
       </c>
       <c r="B233" t="inlineStr"/>
       <c r="C233" t="inlineStr">
@@ -11882,8 +12346,10 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="n">
-        <v>233</v>
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
       </c>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="inlineStr">
@@ -11935,8 +12401,10 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="n">
-        <v>234</v>
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
       </c>
       <c r="B235" t="inlineStr"/>
       <c r="C235" t="inlineStr">
@@ -11988,8 +12456,10 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="n">
-        <v>235</v>
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
       </c>
       <c r="B236" t="inlineStr"/>
       <c r="C236" t="inlineStr">
@@ -12041,8 +12511,10 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="n">
-        <v>236</v>
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
       </c>
       <c r="B237" t="inlineStr"/>
       <c r="C237" t="inlineStr">
@@ -12094,8 +12566,10 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="n">
-        <v>237</v>
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
       </c>
       <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr">
@@ -12147,8 +12621,10 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="n">
-        <v>238</v>
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
       </c>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="inlineStr">
@@ -12200,8 +12676,10 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="n">
-        <v>239</v>
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
       </c>
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr">
@@ -12253,8 +12731,10 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="n">
-        <v>240</v>
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
       </c>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr">
@@ -12306,8 +12786,10 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="n">
-        <v>241</v>
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
       </c>
       <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr">
@@ -12359,8 +12841,10 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="n">
-        <v>242</v>
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
       </c>
       <c r="B243" t="inlineStr"/>
       <c r="C243" t="inlineStr">
@@ -12412,8 +12896,10 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="n">
-        <v>243</v>
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
       </c>
       <c r="B244" t="inlineStr"/>
       <c r="C244" t="inlineStr">
@@ -12465,8 +12951,10 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="n">
-        <v>244</v>
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
       </c>
       <c r="B245" t="inlineStr"/>
       <c r="C245" t="inlineStr">
@@ -12514,8 +13002,10 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="n">
-        <v>245</v>
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
       </c>
       <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr">
@@ -12563,8 +13053,10 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="n">
-        <v>246</v>
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
       </c>
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
@@ -12612,8 +13104,10 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="n">
-        <v>247</v>
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
       </c>
       <c r="B248" t="inlineStr"/>
       <c r="C248" t="inlineStr">
@@ -12665,8 +13159,10 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="n">
-        <v>248</v>
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
       </c>
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="inlineStr">
@@ -12718,8 +13214,10 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="n">
-        <v>249</v>
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
       </c>
       <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr">
@@ -12767,8 +13265,10 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="n">
-        <v>250</v>
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="B251" t="inlineStr"/>
       <c r="C251" t="inlineStr">
@@ -12820,8 +13320,10 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="n">
-        <v>251</v>
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
       </c>
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr">
@@ -12869,8 +13371,10 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="n">
-        <v>252</v>
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
       </c>
       <c r="B253" t="inlineStr"/>
       <c r="C253" t="inlineStr">
@@ -12918,8 +13422,10 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="n">
-        <v>253</v>
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
       </c>
       <c r="B254" t="inlineStr"/>
       <c r="C254" t="inlineStr">
@@ -12971,8 +13477,10 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="n">
-        <v>254</v>
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
       </c>
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr">
@@ -13024,8 +13532,10 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="n">
-        <v>255</v>
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
       </c>
       <c r="B256" t="inlineStr"/>
       <c r="C256" t="inlineStr">
@@ -13077,8 +13587,10 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="n">
-        <v>256</v>
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
       </c>
       <c r="B257" t="inlineStr"/>
       <c r="C257" t="inlineStr">
@@ -13130,8 +13642,10 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="n">
-        <v>257</v>
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
       </c>
       <c r="B258" t="inlineStr"/>
       <c r="C258" t="inlineStr">
@@ -13183,8 +13697,10 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="n">
-        <v>258</v>
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
       </c>
       <c r="B259" t="inlineStr"/>
       <c r="C259" t="inlineStr">
@@ -13236,8 +13752,10 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="n">
-        <v>259</v>
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
       </c>
       <c r="B260" t="inlineStr"/>
       <c r="C260" t="inlineStr">
@@ -13289,8 +13807,10 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="n">
-        <v>260</v>
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
       </c>
       <c r="B261" t="inlineStr"/>
       <c r="C261" t="inlineStr">
@@ -13338,8 +13858,10 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="n">
-        <v>261</v>
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
       </c>
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="inlineStr">
@@ -13391,8 +13913,10 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="n">
-        <v>262</v>
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
       </c>
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="inlineStr">
@@ -13444,8 +13968,10 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="n">
-        <v>263</v>
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
       </c>
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="inlineStr">
@@ -13497,8 +14023,10 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="n">
-        <v>264</v>
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
       </c>
       <c r="B265" t="inlineStr"/>
       <c r="C265" t="inlineStr">
@@ -13550,8 +14078,10 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="n">
-        <v>265</v>
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
       </c>
       <c r="B266" t="inlineStr"/>
       <c r="C266" t="inlineStr">
@@ -13603,8 +14133,10 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="n">
-        <v>266</v>
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
       </c>
       <c r="B267" t="inlineStr"/>
       <c r="C267" t="inlineStr">
@@ -13656,8 +14188,10 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="n">
-        <v>267</v>
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
       </c>
       <c r="B268" t="inlineStr"/>
       <c r="C268" t="inlineStr">
@@ -13709,8 +14243,10 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="n">
-        <v>268</v>
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
       </c>
       <c r="B269" t="inlineStr"/>
       <c r="C269" t="inlineStr">
@@ -13762,8 +14298,10 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="n">
-        <v>269</v>
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
       </c>
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="inlineStr">
@@ -13815,8 +14353,10 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="n">
-        <v>270</v>
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
       </c>
       <c r="B271" t="inlineStr"/>
       <c r="C271" t="inlineStr">
@@ -13868,8 +14408,10 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="n">
-        <v>271</v>
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
       </c>
       <c r="B272" t="inlineStr"/>
       <c r="C272" t="inlineStr">
@@ -13921,8 +14463,10 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="n">
-        <v>272</v>
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
       </c>
       <c r="B273" t="inlineStr"/>
       <c r="C273" t="inlineStr">
@@ -13974,8 +14518,10 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="n">
-        <v>273</v>
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
       </c>
       <c r="B274" t="inlineStr"/>
       <c r="C274" t="inlineStr">
@@ -14027,8 +14573,10 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="n">
-        <v>274</v>
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
       </c>
       <c r="B275" t="inlineStr"/>
       <c r="C275" t="inlineStr">
@@ -14080,8 +14628,10 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="n">
-        <v>275</v>
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
       </c>
       <c r="B276" t="inlineStr"/>
       <c r="C276" t="inlineStr">
@@ -14133,8 +14683,10 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="n">
-        <v>276</v>
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
       </c>
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="inlineStr">
@@ -14186,8 +14738,10 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="n">
-        <v>277</v>
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
       </c>
       <c r="B278" t="inlineStr"/>
       <c r="C278" t="inlineStr">
@@ -14239,8 +14793,10 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="n">
-        <v>278</v>
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
       </c>
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
@@ -14292,8 +14848,10 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="n">
-        <v>279</v>
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
       </c>
       <c r="B280" t="inlineStr"/>
       <c r="C280" t="inlineStr">
@@ -14345,8 +14903,10 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="n">
-        <v>280</v>
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
       </c>
       <c r="B281" t="inlineStr"/>
       <c r="C281" t="inlineStr">
@@ -14398,8 +14958,10 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="n">
-        <v>281</v>
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
       </c>
       <c r="B282" t="inlineStr"/>
       <c r="C282" t="inlineStr">
@@ -14451,8 +15013,10 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="n">
-        <v>282</v>
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
       </c>
       <c r="B283" t="inlineStr"/>
       <c r="C283" t="inlineStr">
@@ -14504,8 +15068,10 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="n">
-        <v>283</v>
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
       </c>
       <c r="B284" t="inlineStr"/>
       <c r="C284" t="inlineStr">
@@ -14557,8 +15123,10 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="n">
-        <v>284</v>
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
       </c>
       <c r="B285" t="inlineStr"/>
       <c r="C285" t="inlineStr">
@@ -14610,8 +15178,10 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="n">
-        <v>285</v>
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
       </c>
       <c r="B286" t="inlineStr"/>
       <c r="C286" t="inlineStr">
@@ -14663,8 +15233,10 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="n">
-        <v>286</v>
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
       </c>
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="inlineStr">
@@ -14716,8 +15288,10 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="n">
-        <v>287</v>
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
       </c>
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="inlineStr">
@@ -14769,8 +15343,10 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="n">
-        <v>288</v>
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
       </c>
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="inlineStr">
@@ -14822,8 +15398,10 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="n">
-        <v>289</v>
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
       </c>
       <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
@@ -14875,8 +15453,10 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="n">
-        <v>290</v>
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
       </c>
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr">
@@ -14928,8 +15508,10 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="n">
-        <v>291</v>
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
       </c>
       <c r="B292" t="inlineStr"/>
       <c r="C292" t="inlineStr">
@@ -14981,8 +15563,10 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="n">
-        <v>292</v>
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
       </c>
       <c r="B293" t="inlineStr"/>
       <c r="C293" t="inlineStr">
@@ -15034,8 +15618,10 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="n">
-        <v>293</v>
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
       </c>
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
@@ -15087,8 +15673,10 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="n">
-        <v>294</v>
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
       </c>
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
@@ -15140,8 +15728,10 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="n">
-        <v>295</v>
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
       </c>
       <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr">
@@ -15193,8 +15783,10 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="n">
-        <v>296</v>
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
       </c>
       <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr">
@@ -15246,8 +15838,10 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="n">
-        <v>297</v>
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
       </c>
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr">
@@ -15299,8 +15893,10 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="n">
-        <v>298</v>
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
       </c>
       <c r="B299" t="inlineStr"/>
       <c r="C299" t="inlineStr">
@@ -15352,8 +15948,10 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="n">
-        <v>299</v>
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
       </c>
       <c r="B300" t="inlineStr"/>
       <c r="C300" t="inlineStr">
@@ -15405,8 +16003,10 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="n">
-        <v>300</v>
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr">
@@ -15458,8 +16058,10 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="n">
-        <v>301</v>
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
       </c>
       <c r="B302" t="inlineStr"/>
       <c r="C302" t="inlineStr">
@@ -15511,8 +16113,10 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="n">
-        <v>302</v>
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
       </c>
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr">
@@ -15564,8 +16168,10 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="n">
-        <v>303</v>
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
       </c>
       <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
@@ -15617,8 +16223,10 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="n">
-        <v>304</v>
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
       </c>
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr">
@@ -15670,8 +16278,10 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="n">
-        <v>305</v>
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
       </c>
       <c r="B306" t="inlineStr"/>
       <c r="C306" t="inlineStr">
@@ -15723,8 +16333,10 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="n">
-        <v>306</v>
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
       </c>
       <c r="B307" t="inlineStr"/>
       <c r="C307" t="inlineStr">
@@ -15776,8 +16388,10 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="n">
-        <v>307</v>
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
       </c>
       <c r="B308" t="inlineStr"/>
       <c r="C308" t="inlineStr">
@@ -15829,8 +16443,10 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="n">
-        <v>308</v>
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
       </c>
       <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr">
@@ -15882,8 +16498,10 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="n">
-        <v>309</v>
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
       </c>
       <c r="B310" t="inlineStr"/>
       <c r="C310" t="inlineStr">
@@ -15935,8 +16553,10 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="n">
-        <v>310</v>
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
       </c>
       <c r="B311" t="inlineStr"/>
       <c r="C311" t="inlineStr">
@@ -15988,8 +16608,10 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="n">
-        <v>311</v>
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
       </c>
       <c r="B312" t="inlineStr"/>
       <c r="C312" t="inlineStr">
@@ -16041,8 +16663,10 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="n">
-        <v>312</v>
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
       </c>
       <c r="B313" t="inlineStr"/>
       <c r="C313" t="inlineStr">
@@ -16094,8 +16718,10 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="n">
-        <v>313</v>
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
       </c>
       <c r="B314" t="inlineStr"/>
       <c r="C314" t="inlineStr">
@@ -16147,8 +16773,10 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="n">
-        <v>314</v>
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
       </c>
       <c r="B315" t="inlineStr"/>
       <c r="C315" t="inlineStr">
@@ -16200,8 +16828,10 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="n">
-        <v>315</v>
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
       </c>
       <c r="B316" t="inlineStr"/>
       <c r="C316" t="inlineStr">
@@ -16253,8 +16883,10 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="n">
-        <v>316</v>
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
       </c>
       <c r="B317" t="inlineStr"/>
       <c r="C317" t="inlineStr">
@@ -16306,8 +16938,10 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="n">
-        <v>317</v>
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
       </c>
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="inlineStr">
@@ -16359,8 +16993,10 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="n">
-        <v>318</v>
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
       </c>
       <c r="B319" t="inlineStr"/>
       <c r="C319" t="inlineStr">
@@ -16412,8 +17048,10 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="n">
-        <v>319</v>
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
       </c>
       <c r="B320" t="inlineStr"/>
       <c r="C320" t="inlineStr">
@@ -16465,8 +17103,10 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="n">
-        <v>320</v>
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
       </c>
       <c r="B321" t="inlineStr"/>
       <c r="C321" t="inlineStr">
@@ -16518,8 +17158,10 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="n">
-        <v>321</v>
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
       </c>
       <c r="B322" t="inlineStr"/>
       <c r="C322" t="inlineStr">
@@ -16571,8 +17213,10 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="n">
-        <v>322</v>
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
       </c>
       <c r="B323" t="inlineStr"/>
       <c r="C323" t="inlineStr">
@@ -16624,8 +17268,10 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="n">
-        <v>323</v>
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
       </c>
       <c r="B324" t="inlineStr"/>
       <c r="C324" t="inlineStr">
@@ -16677,8 +17323,10 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="n">
-        <v>324</v>
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
       </c>
       <c r="B325" t="inlineStr"/>
       <c r="C325" t="inlineStr">
@@ -16730,8 +17378,10 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="n">
-        <v>325</v>
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
       </c>
       <c r="B326" t="inlineStr"/>
       <c r="C326" t="inlineStr">
@@ -16783,8 +17433,10 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="n">
-        <v>326</v>
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
       </c>
       <c r="B327" t="inlineStr"/>
       <c r="C327" t="inlineStr">
@@ -16836,8 +17488,10 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="n">
-        <v>327</v>
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
       </c>
       <c r="B328" t="inlineStr"/>
       <c r="C328" t="inlineStr">
@@ -16889,8 +17543,10 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="n">
-        <v>328</v>
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
       </c>
       <c r="B329" t="inlineStr"/>
       <c r="C329" t="inlineStr">
@@ -16942,8 +17598,10 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="n">
-        <v>329</v>
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
       </c>
       <c r="B330" t="inlineStr"/>
       <c r="C330" t="inlineStr">
@@ -16995,8 +17653,10 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="n">
-        <v>330</v>
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
       </c>
       <c r="B331" t="inlineStr"/>
       <c r="C331" t="inlineStr">
@@ -17048,8 +17708,10 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="n">
-        <v>331</v>
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
       </c>
       <c r="B332" t="inlineStr"/>
       <c r="C332" t="inlineStr">
@@ -17101,8 +17763,10 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="n">
-        <v>332</v>
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
       </c>
       <c r="B333" t="inlineStr"/>
       <c r="C333" t="inlineStr">
@@ -17154,8 +17818,10 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="n">
-        <v>333</v>
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
       </c>
       <c r="B334" t="inlineStr"/>
       <c r="C334" t="inlineStr">
@@ -17207,8 +17873,10 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="n">
-        <v>334</v>
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
       </c>
       <c r="B335" t="inlineStr"/>
       <c r="C335" t="inlineStr">
@@ -17260,8 +17928,10 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="n">
-        <v>335</v>
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
       </c>
       <c r="B336" t="inlineStr"/>
       <c r="C336" t="inlineStr">
@@ -17313,8 +17983,10 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="n">
-        <v>336</v>
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
       </c>
       <c r="B337" t="inlineStr"/>
       <c r="C337" t="inlineStr">
@@ -17366,8 +18038,10 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="n">
-        <v>337</v>
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
       </c>
       <c r="B338" t="inlineStr"/>
       <c r="C338" t="inlineStr">
@@ -17419,8 +18093,10 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="n">
-        <v>338</v>
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
       </c>
       <c r="B339" t="inlineStr"/>
       <c r="C339" t="inlineStr">
@@ -17472,8 +18148,10 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="n">
-        <v>339</v>
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
       </c>
       <c r="B340" t="inlineStr"/>
       <c r="C340" t="inlineStr">
@@ -17525,8 +18203,10 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="n">
-        <v>340</v>
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
       </c>
       <c r="B341" t="inlineStr"/>
       <c r="C341" t="inlineStr">
@@ -17578,8 +18258,10 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="n">
-        <v>341</v>
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
       </c>
       <c r="B342" t="inlineStr"/>
       <c r="C342" t="inlineStr">
@@ -17631,8 +18313,10 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="n">
-        <v>342</v>
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
       </c>
       <c r="B343" t="inlineStr"/>
       <c r="C343" t="inlineStr">
@@ -17684,8 +18368,10 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="n">
-        <v>343</v>
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
       </c>
       <c r="B344" t="inlineStr"/>
       <c r="C344" t="inlineStr">
@@ -17737,8 +18423,10 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="n">
-        <v>344</v>
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
       </c>
       <c r="B345" t="inlineStr"/>
       <c r="C345" t="inlineStr">
@@ -17790,8 +18478,10 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="n">
-        <v>345</v>
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
       </c>
       <c r="B346" t="inlineStr"/>
       <c r="C346" t="inlineStr">
@@ -17843,8 +18533,10 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="n">
-        <v>346</v>
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
       </c>
       <c r="B347" t="inlineStr"/>
       <c r="C347" t="inlineStr">
@@ -17896,8 +18588,10 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="n">
-        <v>347</v>
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
       </c>
       <c r="B348" t="inlineStr"/>
       <c r="C348" t="inlineStr">
@@ -17949,8 +18643,10 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="n">
-        <v>348</v>
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
       </c>
       <c r="B349" t="inlineStr"/>
       <c r="C349" t="inlineStr">
@@ -18002,8 +18698,10 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="n">
-        <v>349</v>
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
       </c>
       <c r="B350" t="inlineStr"/>
       <c r="C350" t="inlineStr">
@@ -18055,8 +18753,10 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="n">
-        <v>350</v>
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
       </c>
       <c r="B351" t="inlineStr"/>
       <c r="C351" t="inlineStr">
@@ -18108,8 +18808,10 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="n">
-        <v>351</v>
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
       </c>
       <c r="B352" t="inlineStr"/>
       <c r="C352" t="inlineStr">
@@ -18161,8 +18863,10 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="n">
-        <v>352</v>
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
       </c>
       <c r="B353" t="inlineStr"/>
       <c r="C353" t="inlineStr">
@@ -18214,8 +18918,10 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" t="n">
-        <v>353</v>
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
       </c>
       <c r="B354" t="inlineStr"/>
       <c r="C354" t="inlineStr">
@@ -18267,8 +18973,10 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="n">
-        <v>354</v>
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
       </c>
       <c r="B355" t="inlineStr"/>
       <c r="C355" t="inlineStr">
@@ -18320,8 +19028,10 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="n">
-        <v>355</v>
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
       </c>
       <c r="B356" t="inlineStr"/>
       <c r="C356" t="inlineStr">
@@ -18373,8 +19083,10 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="n">
-        <v>356</v>
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
       </c>
       <c r="B357" t="inlineStr"/>
       <c r="C357" t="inlineStr">
@@ -18422,8 +19134,10 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="n">
-        <v>357</v>
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
       </c>
       <c r="B358" t="inlineStr"/>
       <c r="C358" t="inlineStr">
@@ -18475,8 +19189,10 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="n">
-        <v>358</v>
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
       </c>
       <c r="B359" t="inlineStr"/>
       <c r="C359" t="inlineStr">
@@ -18524,8 +19240,10 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="n">
-        <v>359</v>
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
       </c>
       <c r="B360" t="inlineStr"/>
       <c r="C360" t="inlineStr">
@@ -18573,8 +19291,10 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="n">
-        <v>360</v>
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
       </c>
       <c r="B361" t="inlineStr"/>
       <c r="C361" t="inlineStr">
@@ -18622,8 +19342,10 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="n">
-        <v>361</v>
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
       </c>
       <c r="B362" t="inlineStr"/>
       <c r="C362" t="inlineStr">
@@ -18671,8 +19393,10 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="n">
-        <v>362</v>
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
       </c>
       <c r="B363" t="inlineStr"/>
       <c r="C363" t="inlineStr">
@@ -18720,8 +19444,10 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="n">
-        <v>363</v>
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
       </c>
       <c r="B364" t="inlineStr"/>
       <c r="C364" t="inlineStr">
@@ -18769,8 +19495,10 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="n">
-        <v>364</v>
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
       </c>
       <c r="B365" t="inlineStr"/>
       <c r="C365" t="inlineStr">
@@ -18818,8 +19546,10 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="n">
-        <v>365</v>
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
       </c>
       <c r="B366" t="inlineStr"/>
       <c r="C366" t="inlineStr">
@@ -18867,8 +19597,10 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="n">
-        <v>366</v>
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
       </c>
       <c r="B367" t="inlineStr"/>
       <c r="C367" t="inlineStr">
@@ -18916,8 +19648,10 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="n">
-        <v>367</v>
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
       </c>
       <c r="B368" t="inlineStr"/>
       <c r="C368" t="inlineStr">
@@ -18965,8 +19699,10 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="n">
-        <v>368</v>
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
       </c>
       <c r="B369" t="inlineStr"/>
       <c r="C369" t="inlineStr">
@@ -19014,8 +19750,10 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="n">
-        <v>369</v>
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
       </c>
       <c r="B370" t="inlineStr"/>
       <c r="C370" t="inlineStr">
@@ -19063,8 +19801,10 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="n">
-        <v>370</v>
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
       </c>
       <c r="B371" t="inlineStr"/>
       <c r="C371" t="inlineStr">
@@ -19112,8 +19852,10 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="n">
-        <v>371</v>
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
       </c>
       <c r="B372" t="inlineStr"/>
       <c r="C372" t="inlineStr">
@@ -19161,8 +19903,10 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="n">
-        <v>372</v>
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
       </c>
       <c r="B373" t="inlineStr"/>
       <c r="C373" t="inlineStr">
@@ -19210,8 +19954,10 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="n">
-        <v>373</v>
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
       </c>
       <c r="B374" t="inlineStr"/>
       <c r="C374" t="inlineStr">
@@ -19259,8 +20005,10 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="n">
-        <v>374</v>
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
       </c>
       <c r="B375" t="inlineStr"/>
       <c r="C375" t="inlineStr">
@@ -19308,8 +20056,10 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="n">
-        <v>375</v>
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
       </c>
       <c r="B376" t="inlineStr"/>
       <c r="C376" t="inlineStr">
@@ -19361,8 +20111,10 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="n">
-        <v>376</v>
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
       </c>
       <c r="B377" t="inlineStr"/>
       <c r="C377" t="inlineStr">
@@ -19414,8 +20166,10 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" t="n">
-        <v>377</v>
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
       </c>
       <c r="B378" t="inlineStr"/>
       <c r="C378" t="inlineStr">
@@ -19463,8 +20217,10 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="n">
-        <v>378</v>
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
       </c>
       <c r="B379" t="inlineStr"/>
       <c r="C379" t="inlineStr">
@@ -19512,8 +20268,10 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" t="n">
-        <v>379</v>
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
       </c>
       <c r="B380" t="inlineStr"/>
       <c r="C380" t="inlineStr">
@@ -19561,8 +20319,10 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" t="n">
-        <v>380</v>
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
       </c>
       <c r="B381" t="inlineStr"/>
       <c r="C381" t="inlineStr">
@@ -19614,8 +20374,10 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="n">
-        <v>381</v>
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
       </c>
       <c r="B382" t="inlineStr"/>
       <c r="C382" t="inlineStr">
@@ -19667,8 +20429,10 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" t="n">
-        <v>382</v>
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
       </c>
       <c r="B383" t="inlineStr"/>
       <c r="C383" t="inlineStr">
@@ -19720,8 +20484,10 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="n">
-        <v>383</v>
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
       </c>
       <c r="B384" t="inlineStr"/>
       <c r="C384" t="inlineStr">
@@ -19773,8 +20539,10 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="n">
-        <v>384</v>
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
       </c>
       <c r="B385" t="inlineStr"/>
       <c r="C385" t="inlineStr">
@@ -19826,8 +20594,10 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="n">
-        <v>385</v>
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
       </c>
       <c r="B386" t="inlineStr"/>
       <c r="C386" t="inlineStr">
@@ -19879,8 +20649,10 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="n">
-        <v>386</v>
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
       </c>
       <c r="B387" t="inlineStr"/>
       <c r="C387" t="inlineStr">
@@ -19932,8 +20704,10 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="n">
-        <v>387</v>
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
       </c>
       <c r="B388" t="inlineStr"/>
       <c r="C388" t="inlineStr">
@@ -19981,8 +20755,10 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="n">
-        <v>388</v>
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
       </c>
       <c r="B389" t="inlineStr"/>
       <c r="C389" t="inlineStr">
@@ -20034,8 +20810,10 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="n">
-        <v>389</v>
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
       </c>
       <c r="B390" t="inlineStr"/>
       <c r="C390" t="inlineStr">
@@ -20087,8 +20865,10 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="n">
-        <v>390</v>
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
       </c>
       <c r="B391" t="inlineStr"/>
       <c r="C391" t="inlineStr">
@@ -20140,8 +20920,10 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="n">
-        <v>391</v>
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
       </c>
       <c r="B392" t="inlineStr"/>
       <c r="C392" t="inlineStr">
@@ -20193,8 +20975,10 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="n">
-        <v>392</v>
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
       </c>
       <c r="B393" t="inlineStr"/>
       <c r="C393" t="inlineStr">
@@ -20246,8 +21030,10 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="n">
-        <v>393</v>
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
       </c>
       <c r="B394" t="inlineStr"/>
       <c r="C394" t="inlineStr">
@@ -20299,8 +21085,10 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="n">
-        <v>394</v>
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
       </c>
       <c r="B395" t="inlineStr"/>
       <c r="C395" t="inlineStr">
@@ -20352,8 +21140,10 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="n">
-        <v>395</v>
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
       </c>
       <c r="B396" t="inlineStr"/>
       <c r="C396" t="inlineStr">
@@ -20405,8 +21195,10 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="n">
-        <v>396</v>
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
       </c>
       <c r="B397" t="inlineStr"/>
       <c r="C397" t="inlineStr">
@@ -20458,8 +21250,10 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="n">
-        <v>397</v>
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
       </c>
       <c r="B398" t="inlineStr"/>
       <c r="C398" t="inlineStr">
@@ -20507,8 +21301,10 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="n">
-        <v>398</v>
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
       </c>
       <c r="B399" t="inlineStr"/>
       <c r="C399" t="inlineStr">
@@ -20560,8 +21356,10 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="n">
-        <v>399</v>
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
       </c>
       <c r="B400" t="inlineStr"/>
       <c r="C400" t="inlineStr">
@@ -20613,8 +21411,10 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="n">
-        <v>400</v>
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="B401" t="inlineStr"/>
       <c r="C401" t="inlineStr">
@@ -20666,8 +21466,10 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="n">
-        <v>401</v>
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
       </c>
       <c r="B402" t="inlineStr"/>
       <c r="C402" t="inlineStr">
@@ -20719,8 +21521,10 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="n">
-        <v>402</v>
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
       </c>
       <c r="B403" t="inlineStr"/>
       <c r="C403" t="inlineStr">
@@ -20772,8 +21576,10 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="n">
-        <v>403</v>
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
       </c>
       <c r="B404" t="inlineStr"/>
       <c r="C404" t="inlineStr">
@@ -20825,8 +21631,10 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="n">
-        <v>405</v>
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
       </c>
       <c r="B405" t="inlineStr"/>
       <c r="C405" t="inlineStr"/>
@@ -20876,8 +21684,10 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="n">
-        <v>406</v>
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
       </c>
       <c r="B406" t="inlineStr"/>
       <c r="C406" t="inlineStr"/>
@@ -20929,8 +21739,10 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="n">
-        <v>407</v>
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
       </c>
       <c r="B407" t="inlineStr"/>
       <c r="C407" t="inlineStr"/>
@@ -20980,8 +21792,10 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="n">
-        <v>408</v>
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
       </c>
       <c r="B408" t="inlineStr"/>
       <c r="C408" t="inlineStr"/>
@@ -21023,8 +21837,10 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="n">
-        <v>409</v>
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
       </c>
       <c r="B409" t="inlineStr"/>
       <c r="C409" t="inlineStr"/>
@@ -21066,8 +21882,10 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="n">
-        <v>410</v>
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
       </c>
       <c r="B410" t="inlineStr"/>
       <c r="C410" t="inlineStr"/>
@@ -21105,12 +21923,14 @@
         <v>0</v>
       </c>
       <c r="S410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="n">
-        <v>412</v>
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
       </c>
       <c r="B411" t="inlineStr"/>
       <c r="C411" t="inlineStr"/>
@@ -21152,8 +21972,10 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="n">
-        <v>413</v>
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
       </c>
       <c r="B412" t="inlineStr"/>
       <c r="C412" t="inlineStr"/>
@@ -21193,8 +22015,10 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="n">
-        <v>414</v>
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
       </c>
       <c r="B413" t="inlineStr"/>
       <c r="C413" t="inlineStr"/>
@@ -21234,8 +22058,10 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="n">
-        <v>415</v>
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
       </c>
       <c r="B414" t="inlineStr"/>
       <c r="C414" t="inlineStr"/>
@@ -21275,8 +22101,10 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="n">
-        <v>416</v>
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
       </c>
       <c r="B415" t="inlineStr"/>
       <c r="C415" t="inlineStr"/>
@@ -21316,8 +22144,10 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="n">
-        <v>417</v>
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
       </c>
       <c r="B416" t="inlineStr"/>
       <c r="C416" t="inlineStr"/>
@@ -21357,8 +22187,10 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="n">
-        <v>418</v>
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
       </c>
       <c r="B417" t="inlineStr"/>
       <c r="C417" t="inlineStr"/>
@@ -21406,8 +22238,10 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="n">
-        <v>419</v>
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
       </c>
       <c r="B418" t="inlineStr"/>
       <c r="C418" t="inlineStr"/>
@@ -21455,8 +22289,10 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="n">
-        <v>420</v>
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
       </c>
       <c r="B419" t="inlineStr"/>
       <c r="C419" t="inlineStr"/>
@@ -21504,14 +22340,16 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="n">
-        <v>421</v>
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
       </c>
       <c r="B420" t="inlineStr"/>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
-          <t>MT약품</t>
+          <t>Carestream M100-14*17"</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -21521,7 +22359,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>MT약품</t>
+          <t>Carestream M100-14*17"</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
@@ -21557,14 +22395,16 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="n">
-        <v>422</v>
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
       </c>
       <c r="B421" t="inlineStr"/>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
-          <t>MT약품</t>
+          <t>Carestream M100-14*17"</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -21574,7 +22414,7 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>흑색자분</t>
+          <t>Carestream M100-14*17"</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
@@ -21606,18 +22446,20 @@
         <v>0</v>
       </c>
       <c r="S421" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="n">
-        <v>423</v>
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
       </c>
       <c r="B422" t="inlineStr"/>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
-          <t>MT약품</t>
+          <t>Carestream M100-14*17"</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -21627,7 +22469,7 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>백색페인트</t>
+          <t>Carestream M100-14*17"</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
@@ -21659,7 +22501,172 @@
         <v>0</v>
       </c>
       <c r="S422" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr"/>
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Carestream M100-14*17"</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Carestream M100-14*17"</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr"/>
+      <c r="I423" t="inlineStr"/>
+      <c r="J423" t="inlineStr"/>
+      <c r="K423" t="n">
+        <v>0</v>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M423" t="n">
+        <v>0</v>
+      </c>
+      <c r="N423" t="inlineStr"/>
+      <c r="O423" t="inlineStr"/>
+      <c r="P423" t="inlineStr"/>
+      <c r="Q423" t="n">
+        <v>10</v>
+      </c>
+      <c r="R423" t="n">
+        <v>0</v>
+      </c>
+      <c r="S423" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr"/>
+      <c r="C424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Carestream M100-14*17"</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Carestream M100-14*17"</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr"/>
+      <c r="I424" t="inlineStr"/>
+      <c r="J424" t="inlineStr"/>
+      <c r="K424" t="n">
+        <v>0</v>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M424" t="n">
+        <v>0</v>
+      </c>
+      <c r="N424" t="inlineStr"/>
+      <c r="O424" t="inlineStr"/>
+      <c r="P424" t="inlineStr"/>
+      <c r="Q424" t="n">
+        <v>10</v>
+      </c>
+      <c r="R424" t="n">
+        <v>0</v>
+      </c>
+      <c r="S424" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr"/>
+      <c r="C425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Carestream M100-14*17"</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Carestream M100-14*17"</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr"/>
+      <c r="I425" t="inlineStr"/>
+      <c r="J425" t="inlineStr"/>
+      <c r="K425" t="n">
+        <v>0</v>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M425" t="n">
+        <v>0</v>
+      </c>
+      <c r="N425" t="inlineStr"/>
+      <c r="O425" t="inlineStr"/>
+      <c r="P425" t="inlineStr"/>
+      <c r="Q425" t="n">
+        <v>10</v>
+      </c>
+      <c r="R425" t="n">
+        <v>0</v>
+      </c>
+      <c r="S425" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -21673,7 +22680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21732,13 +22739,75 @@
           <t>차량비고</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>방법</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>장비명</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>품목명</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>형광자분</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>흑색자분</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>백색페인트</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>침투제</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>세척제</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>현상제</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>형광침투제</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>회사코드</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46131</v>
-      </c>
-      <c r="B2" t="n">
-        <v>410</v>
+        <v>46129.55760175926</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -21746,42 +22815,115 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>K1-PJT 현장 사용 (자동 차감)</t>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>부장 주진철, 주임 김진환</t>
+          <t>부장 주진철</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>R-RAY</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Carestream MX125-3⅓*12"</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46129.66845252315</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-60</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>R-RAY</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Carestream MX125-3⅓*12"</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -21846,7 +22988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN5"/>
+  <dimension ref="A1:BN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22167,42 +23309,44 @@
       </c>
       <c r="BL1" t="inlineStr">
         <is>
+          <t>품목명</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
           <t>RTK_총계</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>회사코드</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>업체명</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" s="1" t="n">
+        <v>46129</v>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>가스공사 의왕</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>410</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="1" t="n">
-        <v>46073.93459934027</v>
+        <v>46129.66845251157</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -22221,7 +23365,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>김성현</t>
+          <t>부장 주진철</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -22230,10 +23374,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q2" t="n">
-        <v>2500</v>
+        <v>25500</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -22242,7 +23386,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>125000</v>
+        <v>1530000</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -22250,31 +23394,31 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>(주간) 09:00~20:00</t>
+          <t>09:00~24:00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>김진환</t>
+          <t>대리 현해룡</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>(주간) 09:00~20:00</t>
+          <t>09:00~24:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -22329,519 +23473,15 @@
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>Carestream MX125-3⅓*12"</t>
+        </is>
+      </c>
+      <c r="BM2" t="n">
+        <v>0</v>
+      </c>
       <c r="BN2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>K1 PJT</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>410</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" s="1" t="n">
-        <v>46124.90375616898</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>대리 현해룡</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>R-RAY</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1275000</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>50</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>(주야간) 09:00~익일05:00</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>150,000</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>(주야간) 09:00~익일05:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>150,000</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>주임 주유철</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>(주야간) 09:00~익일05:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>150,000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>탑차 81도4028</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>112,445</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>주유, 청결, 엔진오일, 타이어, 전조등</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>K1 PJT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>408</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" s="1" t="n">
-        <v>46124.90651913195</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>김성현</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>R-RAY</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>25000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1250000</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>50</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>(주야간) 09:00~20:00</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>82,500</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>김진환</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>(주야간) 09:00~20:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>82,500</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>부장 박광복</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>(주야간) 09:00~20:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>82,500</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>탑차 81도4028</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>111,111</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>주유, 청결, 엔진오일, 타이어, 전조등</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46131</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>410</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" s="1" t="n">
-        <v>46131.88805793982</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>R-RAY</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>09:00~20:00</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>82,500</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>주임 김진환</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:00~20:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>82,500</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,10 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -53,9 +51,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S425"/>
+  <dimension ref="A1:S426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,10 +519,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
@@ -577,10 +572,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
@@ -632,10 +625,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
@@ -687,10 +678,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
@@ -742,10 +731,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
@@ -797,10 +784,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
@@ -852,10 +837,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
@@ -907,10 +890,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
@@ -962,10 +943,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
@@ -1017,10 +996,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
@@ -1072,10 +1049,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
@@ -1127,10 +1102,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
@@ -1182,10 +1155,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="A14" t="n">
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
@@ -1237,10 +1208,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="A15" t="n">
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
@@ -1292,10 +1261,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="A16" t="n">
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
@@ -1347,10 +1314,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A17" t="n">
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
@@ -1402,10 +1367,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="A18" t="n">
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
@@ -1457,10 +1420,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A19" t="n">
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
@@ -1512,10 +1473,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="A20" t="n">
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
@@ -1567,10 +1526,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A21" t="n">
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
@@ -1622,10 +1579,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="A22" t="n">
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
@@ -1677,10 +1632,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="A23" t="n">
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
@@ -1732,10 +1685,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="A24" t="n">
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
@@ -1787,10 +1738,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="A25" t="n">
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
@@ -1842,10 +1791,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="A26" t="n">
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
@@ -1897,10 +1844,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="A27" t="n">
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
@@ -1952,10 +1897,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="A28" t="n">
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
@@ -2007,10 +1950,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="A29" t="n">
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
@@ -2062,10 +2003,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="A30" t="n">
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
@@ -2117,10 +2056,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="A31" t="n">
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
@@ -2172,10 +2109,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="A32" t="n">
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
@@ -2227,10 +2162,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="A33" t="n">
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
@@ -2282,10 +2215,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="A34" t="n">
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
@@ -2337,10 +2268,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="A35" t="n">
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
@@ -2392,10 +2321,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="A36" t="n">
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
@@ -2447,10 +2374,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="A37" t="n">
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
@@ -2502,10 +2427,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="A38" t="n">
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
@@ -2557,10 +2480,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="A39" t="n">
+        <v>38</v>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
@@ -2612,10 +2533,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="A40" t="n">
+        <v>39</v>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
@@ -2667,10 +2586,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="A41" t="n">
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
@@ -2722,10 +2639,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="A42" t="n">
+        <v>41</v>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
@@ -2777,10 +2692,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="A43" t="n">
+        <v>42</v>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
@@ -2832,10 +2745,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="A44" t="n">
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
@@ -2887,10 +2798,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="A45" t="n">
+        <v>44</v>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
@@ -2942,10 +2851,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="A46" t="n">
+        <v>45</v>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
@@ -2997,10 +2904,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="A47" t="n">
+        <v>46</v>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
@@ -3052,10 +2957,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="A48" t="n">
+        <v>47</v>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
@@ -3103,10 +3006,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="A49" t="n">
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
@@ -3154,10 +3055,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="A50" t="n">
+        <v>49</v>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
@@ -3205,10 +3104,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="A51" t="n">
+        <v>50</v>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
@@ -3256,10 +3153,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="A52" t="n">
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
@@ -3307,10 +3202,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="A53" t="n">
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
@@ -3362,10 +3255,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="A54" t="n">
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
@@ -3417,10 +3308,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="A55" t="n">
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
@@ -3472,10 +3361,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="A56" t="n">
+        <v>55</v>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
@@ -3527,10 +3414,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+      <c r="A57" t="n">
+        <v>56</v>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
@@ -3582,10 +3467,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="A58" t="n">
+        <v>57</v>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
@@ -3637,10 +3520,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="A59" t="n">
+        <v>58</v>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
@@ -3692,10 +3573,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+      <c r="A60" t="n">
+        <v>59</v>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
@@ -3747,10 +3626,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="A61" t="n">
+        <v>60</v>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
@@ -3802,10 +3679,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+      <c r="A62" t="n">
+        <v>61</v>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
@@ -3857,10 +3732,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="A63" t="n">
+        <v>62</v>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
@@ -3912,10 +3785,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="A64" t="n">
+        <v>63</v>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
@@ -3967,10 +3838,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="A65" t="n">
+        <v>64</v>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
@@ -4022,10 +3891,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="A66" t="n">
+        <v>65</v>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
@@ -4077,10 +3944,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="A67" t="n">
+        <v>66</v>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
@@ -4128,10 +3993,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="A68" t="n">
+        <v>67</v>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
@@ -4179,10 +4042,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="A69" t="n">
+        <v>68</v>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
@@ -4234,10 +4095,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="A70" t="n">
+        <v>69</v>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
@@ -4289,10 +4148,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="A71" t="n">
+        <v>70</v>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
@@ -4344,10 +4201,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="A72" t="n">
+        <v>71</v>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
@@ -4399,10 +4254,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="A73" t="n">
+        <v>72</v>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
@@ -4454,10 +4307,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="A74" t="n">
+        <v>73</v>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
@@ -4509,10 +4360,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="A75" t="n">
+        <v>74</v>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
@@ -4564,10 +4413,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="A76" t="n">
+        <v>75</v>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
@@ -4619,10 +4466,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="A77" t="n">
+        <v>76</v>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
@@ -4670,10 +4515,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="A78" t="n">
+        <v>77</v>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
@@ -4725,10 +4568,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="A79" t="n">
+        <v>78</v>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
@@ -4780,10 +4621,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="A80" t="n">
+        <v>79</v>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
@@ -4835,10 +4674,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="A81" t="n">
+        <v>80</v>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
@@ -4890,10 +4727,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="A82" t="n">
+        <v>81</v>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
@@ -4945,10 +4780,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="A83" t="n">
+        <v>82</v>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
@@ -5000,10 +4833,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="A84" t="n">
+        <v>83</v>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
@@ -5055,10 +4886,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="A85" t="n">
+        <v>84</v>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
@@ -5110,10 +4939,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="A86" t="n">
+        <v>85</v>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
@@ -5161,10 +4988,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+      <c r="A87" t="n">
+        <v>86</v>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
@@ -5212,10 +5037,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
+      <c r="A88" t="n">
+        <v>87</v>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
@@ -5267,10 +5090,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
+      <c r="A89" t="n">
+        <v>88</v>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
@@ -5322,10 +5143,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
+      <c r="A90" t="n">
+        <v>89</v>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
@@ -5377,10 +5196,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="A91" t="n">
+        <v>90</v>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
@@ -5432,10 +5249,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
+      <c r="A92" t="n">
+        <v>91</v>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
@@ -5483,10 +5298,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="A93" t="n">
+        <v>92</v>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
@@ -5538,10 +5351,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
+      <c r="A94" t="n">
+        <v>93</v>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
@@ -5589,10 +5400,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
+      <c r="A95" t="n">
+        <v>94</v>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
@@ -5644,10 +5453,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
+      <c r="A96" t="n">
+        <v>95</v>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
@@ -5699,10 +5506,8 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
+      <c r="A97" t="n">
+        <v>96</v>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
@@ -5746,10 +5551,8 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
+      <c r="A98" t="n">
+        <v>97</v>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
@@ -5793,10 +5596,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+      <c r="A99" t="n">
+        <v>98</v>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
@@ -5840,10 +5641,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
+      <c r="A100" t="n">
+        <v>99</v>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
@@ -5887,10 +5686,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="A101" t="n">
+        <v>100</v>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
@@ -5934,10 +5731,8 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
+      <c r="A102" t="n">
+        <v>101</v>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
@@ -5981,10 +5776,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
+      <c r="A103" t="n">
+        <v>102</v>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
@@ -6028,10 +5821,8 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="A104" t="n">
+        <v>103</v>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
@@ -6075,10 +5866,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
+      <c r="A105" t="n">
+        <v>104</v>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
@@ -6122,10 +5911,8 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
+      <c r="A106" t="n">
+        <v>105</v>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
@@ -6169,10 +5956,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
+      <c r="A107" t="n">
+        <v>106</v>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
@@ -6216,10 +6001,8 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
+      <c r="A108" t="n">
+        <v>107</v>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
@@ -6263,10 +6046,8 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
+      <c r="A109" t="n">
+        <v>108</v>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
@@ -6310,10 +6091,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A110" t="n">
+        <v>109</v>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
@@ -6357,10 +6136,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
+      <c r="A111" t="n">
+        <v>110</v>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
@@ -6404,10 +6181,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="A112" t="n">
+        <v>111</v>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
@@ -6451,10 +6226,8 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="A113" t="n">
+        <v>112</v>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
@@ -6498,10 +6271,8 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+      <c r="A114" t="n">
+        <v>113</v>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
@@ -6545,10 +6316,8 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="A115" t="n">
+        <v>114</v>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
@@ -6592,10 +6361,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+      <c r="A116" t="n">
+        <v>115</v>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
@@ -6639,10 +6406,8 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="A117" t="n">
+        <v>116</v>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
@@ -6686,10 +6451,8 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="A118" t="n">
+        <v>117</v>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
@@ -6733,10 +6496,8 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
+      <c r="A119" t="n">
+        <v>118</v>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
@@ -6780,10 +6541,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="A120" t="n">
+        <v>119</v>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
@@ -6827,10 +6586,8 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+      <c r="A121" t="n">
+        <v>120</v>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
@@ -6874,10 +6631,8 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
+      <c r="A122" t="n">
+        <v>121</v>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
@@ -6921,10 +6676,8 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
+      <c r="A123" t="n">
+        <v>122</v>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
@@ -6968,10 +6721,8 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="A124" t="n">
+        <v>123</v>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
@@ -7015,10 +6766,8 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="A125" t="n">
+        <v>124</v>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
@@ -7062,10 +6811,8 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+      <c r="A126" t="n">
+        <v>125</v>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
@@ -7109,10 +6856,8 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
+      <c r="A127" t="n">
+        <v>126</v>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
@@ -7156,10 +6901,8 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+      <c r="A128" t="n">
+        <v>127</v>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
@@ -7203,10 +6946,8 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="A129" t="n">
+        <v>128</v>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
@@ -7250,10 +6991,8 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
+      <c r="A130" t="n">
+        <v>129</v>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
@@ -7297,10 +7036,8 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
+      <c r="A131" t="n">
+        <v>130</v>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
@@ -7344,10 +7081,8 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
+      <c r="A132" t="n">
+        <v>131</v>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
@@ -7391,10 +7126,8 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
+      <c r="A133" t="n">
+        <v>132</v>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
@@ -7438,10 +7171,8 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
+      <c r="A134" t="n">
+        <v>133</v>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
@@ -7485,10 +7216,8 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
+      <c r="A135" t="n">
+        <v>134</v>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
@@ -7532,10 +7261,8 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
+      <c r="A136" t="n">
+        <v>135</v>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
@@ -7579,10 +7306,8 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+      <c r="A137" t="n">
+        <v>136</v>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
@@ -7626,10 +7351,8 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
+      <c r="A138" t="n">
+        <v>137</v>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
@@ -7673,10 +7396,8 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="A139" t="n">
+        <v>138</v>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
@@ -7720,10 +7441,8 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="A140" t="n">
+        <v>139</v>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
@@ -7767,10 +7486,8 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
+      <c r="A141" t="n">
+        <v>140</v>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
@@ -7814,10 +7531,8 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
+      <c r="A142" t="n">
+        <v>141</v>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
@@ -7861,10 +7576,8 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
+      <c r="A143" t="n">
+        <v>142</v>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
@@ -7908,10 +7621,8 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
+      <c r="A144" t="n">
+        <v>143</v>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
@@ -7955,10 +7666,8 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
+      <c r="A145" t="n">
+        <v>144</v>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
@@ -8002,10 +7711,8 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
+      <c r="A146" t="n">
+        <v>145</v>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
@@ -8049,10 +7756,8 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
+      <c r="A147" t="n">
+        <v>146</v>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
@@ -8096,10 +7801,8 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
+      <c r="A148" t="n">
+        <v>147</v>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
@@ -8143,10 +7846,8 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
+      <c r="A149" t="n">
+        <v>148</v>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
@@ -8190,10 +7891,8 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
+      <c r="A150" t="n">
+        <v>149</v>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
@@ -8237,10 +7936,8 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="A151" t="n">
+        <v>150</v>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
@@ -8284,10 +7981,8 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
+      <c r="A152" t="n">
+        <v>151</v>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
@@ -8331,10 +8026,8 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
+      <c r="A153" t="n">
+        <v>152</v>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
@@ -8378,10 +8071,8 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
+      <c r="A154" t="n">
+        <v>153</v>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
@@ -8425,10 +8116,8 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
+      <c r="A155" t="n">
+        <v>154</v>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
@@ -8472,10 +8161,8 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
+      <c r="A156" t="n">
+        <v>155</v>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
@@ -8519,10 +8206,8 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
+      <c r="A157" t="n">
+        <v>156</v>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
@@ -8566,10 +8251,8 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
+      <c r="A158" t="n">
+        <v>157</v>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
@@ -8613,10 +8296,8 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
+      <c r="A159" t="n">
+        <v>158</v>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
@@ -8660,10 +8341,8 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
+      <c r="A160" t="n">
+        <v>159</v>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
@@ -8707,10 +8386,8 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="A161" t="n">
+        <v>160</v>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
@@ -8754,10 +8431,8 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="A162" t="n">
+        <v>161</v>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
@@ -8801,10 +8476,8 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
+      <c r="A163" t="n">
+        <v>162</v>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
@@ -8848,10 +8521,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
+      <c r="A164" t="n">
+        <v>163</v>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
@@ -8895,10 +8566,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
+      <c r="A165" t="n">
+        <v>164</v>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
@@ -8942,10 +8611,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="A166" t="n">
+        <v>165</v>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
@@ -8989,10 +8656,8 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
+      <c r="A167" t="n">
+        <v>166</v>
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
@@ -9036,10 +8701,8 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
+      <c r="A168" t="n">
+        <v>167</v>
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
@@ -9083,10 +8746,8 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
+      <c r="A169" t="n">
+        <v>168</v>
       </c>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
@@ -9130,10 +8791,8 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
+      <c r="A170" t="n">
+        <v>169</v>
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
@@ -9177,10 +8836,8 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
+      <c r="A171" t="n">
+        <v>170</v>
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
@@ -9224,10 +8881,8 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
+      <c r="A172" t="n">
+        <v>171</v>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
@@ -9271,10 +8926,8 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
+      <c r="A173" t="n">
+        <v>172</v>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
@@ -9318,10 +8971,8 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
+      <c r="A174" t="n">
+        <v>173</v>
       </c>
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
@@ -9369,10 +9020,8 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
+      <c r="A175" t="n">
+        <v>174</v>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
@@ -9424,10 +9073,8 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
+      <c r="A176" t="n">
+        <v>175</v>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
@@ -9479,10 +9126,8 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
+      <c r="A177" t="n">
+        <v>176</v>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
@@ -9526,10 +9171,8 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
+      <c r="A178" t="n">
+        <v>177</v>
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
@@ -9573,10 +9216,8 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
+      <c r="A179" t="n">
+        <v>178</v>
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
@@ -9620,10 +9261,8 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
+      <c r="A180" t="n">
+        <v>179</v>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
@@ -9667,10 +9306,8 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
+      <c r="A181" t="n">
+        <v>180</v>
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
@@ -9714,10 +9351,8 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
+      <c r="A182" t="n">
+        <v>181</v>
       </c>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
@@ -9761,10 +9396,8 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
+      <c r="A183" t="n">
+        <v>182</v>
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
@@ -9808,10 +9441,8 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
+      <c r="A184" t="n">
+        <v>183</v>
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
@@ -9855,10 +9486,8 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
+      <c r="A185" t="n">
+        <v>184</v>
       </c>
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
@@ -9902,10 +9531,8 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
+      <c r="A186" t="n">
+        <v>185</v>
       </c>
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
@@ -9949,10 +9576,8 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
+      <c r="A187" t="n">
+        <v>186</v>
       </c>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
@@ -9996,10 +9621,8 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
+      <c r="A188" t="n">
+        <v>187</v>
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
@@ -10043,10 +9666,8 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="A189" t="n">
+        <v>188</v>
       </c>
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr">
@@ -10090,10 +9711,8 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
+      <c r="A190" t="n">
+        <v>189</v>
       </c>
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr">
@@ -10137,10 +9756,8 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
+      <c r="A191" t="n">
+        <v>190</v>
       </c>
       <c r="B191" t="inlineStr"/>
       <c r="C191" t="inlineStr">
@@ -10184,10 +9801,8 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
+      <c r="A192" t="n">
+        <v>191</v>
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr">
@@ -10231,10 +9846,8 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+      <c r="A193" t="n">
+        <v>192</v>
       </c>
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="inlineStr">
@@ -10278,10 +9891,8 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
+      <c r="A194" t="n">
+        <v>193</v>
       </c>
       <c r="B194" t="inlineStr"/>
       <c r="C194" t="inlineStr">
@@ -10325,10 +9936,8 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
+      <c r="A195" t="n">
+        <v>194</v>
       </c>
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="inlineStr">
@@ -10372,10 +9981,8 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
+      <c r="A196" t="n">
+        <v>195</v>
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr">
@@ -10419,10 +10026,8 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
+      <c r="A197" t="n">
+        <v>196</v>
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="inlineStr">
@@ -10466,10 +10071,8 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
+      <c r="A198" t="n">
+        <v>197</v>
       </c>
       <c r="B198" t="inlineStr"/>
       <c r="C198" t="inlineStr">
@@ -10513,10 +10116,8 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
+      <c r="A199" t="n">
+        <v>198</v>
       </c>
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr">
@@ -10560,10 +10161,8 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
+      <c r="A200" t="n">
+        <v>199</v>
       </c>
       <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr">
@@ -10607,10 +10206,8 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="A201" t="n">
+        <v>200</v>
       </c>
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr">
@@ -10654,10 +10251,8 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
+      <c r="A202" t="n">
+        <v>201</v>
       </c>
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="inlineStr">
@@ -10701,10 +10296,8 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
+      <c r="A203" t="n">
+        <v>202</v>
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="inlineStr">
@@ -10748,10 +10341,8 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
+      <c r="A204" t="n">
+        <v>203</v>
       </c>
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="inlineStr">
@@ -10795,10 +10386,8 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
+      <c r="A205" t="n">
+        <v>204</v>
       </c>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr">
@@ -10842,10 +10431,8 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
+      <c r="A206" t="n">
+        <v>205</v>
       </c>
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="inlineStr">
@@ -10889,10 +10476,8 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
+      <c r="A207" t="n">
+        <v>206</v>
       </c>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr">
@@ -10936,10 +10521,8 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
+      <c r="A208" t="n">
+        <v>207</v>
       </c>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="inlineStr">
@@ -10983,10 +10566,8 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
+      <c r="A209" t="n">
+        <v>208</v>
       </c>
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr">
@@ -11030,10 +10611,8 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
+      <c r="A210" t="n">
+        <v>209</v>
       </c>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
@@ -11085,10 +10664,8 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
+      <c r="A211" t="n">
+        <v>210</v>
       </c>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
@@ -11140,10 +10717,8 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
+      <c r="A212" t="n">
+        <v>211</v>
       </c>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
@@ -11195,10 +10770,8 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
+      <c r="A213" t="n">
+        <v>212</v>
       </c>
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="inlineStr">
@@ -11250,10 +10823,8 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
+      <c r="A214" t="n">
+        <v>213</v>
       </c>
       <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr">
@@ -11305,10 +10876,8 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
+      <c r="A215" t="n">
+        <v>214</v>
       </c>
       <c r="B215" t="inlineStr"/>
       <c r="C215" t="inlineStr">
@@ -11360,10 +10929,8 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
+      <c r="A216" t="n">
+        <v>215</v>
       </c>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr">
@@ -11415,10 +10982,8 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
+      <c r="A217" t="n">
+        <v>216</v>
       </c>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr">
@@ -11470,10 +11035,8 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
+      <c r="A218" t="n">
+        <v>217</v>
       </c>
       <c r="B218" t="inlineStr"/>
       <c r="C218" t="inlineStr">
@@ -11525,10 +11088,8 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
+      <c r="A219" t="n">
+        <v>218</v>
       </c>
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
@@ -11580,10 +11141,8 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
+      <c r="A220" t="n">
+        <v>219</v>
       </c>
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr">
@@ -11635,10 +11194,8 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
+      <c r="A221" t="n">
+        <v>220</v>
       </c>
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="inlineStr">
@@ -11690,10 +11247,8 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
+      <c r="A222" t="n">
+        <v>221</v>
       </c>
       <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr">
@@ -11745,10 +11300,8 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
+      <c r="A223" t="n">
+        <v>222</v>
       </c>
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
@@ -11800,10 +11353,8 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
+      <c r="A224" t="n">
+        <v>223</v>
       </c>
       <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr">
@@ -11855,10 +11406,8 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
+      <c r="A225" t="n">
+        <v>224</v>
       </c>
       <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr">
@@ -11910,10 +11459,8 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
+      <c r="A226" t="n">
+        <v>225</v>
       </c>
       <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr">
@@ -11965,10 +11512,8 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
+      <c r="A227" t="n">
+        <v>226</v>
       </c>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="inlineStr">
@@ -12020,10 +11565,8 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
+      <c r="A228" t="n">
+        <v>227</v>
       </c>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="inlineStr">
@@ -12075,10 +11618,8 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
+      <c r="A229" t="n">
+        <v>228</v>
       </c>
       <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr">
@@ -12126,10 +11667,8 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
+      <c r="A230" t="n">
+        <v>229</v>
       </c>
       <c r="B230" t="inlineStr"/>
       <c r="C230" t="inlineStr">
@@ -12181,10 +11720,8 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="A231" t="n">
+        <v>230</v>
       </c>
       <c r="B231" t="inlineStr"/>
       <c r="C231" t="inlineStr">
@@ -12236,10 +11773,8 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
+      <c r="A232" t="n">
+        <v>231</v>
       </c>
       <c r="B232" t="inlineStr"/>
       <c r="C232" t="inlineStr">
@@ -12291,10 +11826,8 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
+      <c r="A233" t="n">
+        <v>232</v>
       </c>
       <c r="B233" t="inlineStr"/>
       <c r="C233" t="inlineStr">
@@ -12346,10 +11879,8 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
+      <c r="A234" t="n">
+        <v>233</v>
       </c>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="inlineStr">
@@ -12401,10 +11932,8 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
+      <c r="A235" t="n">
+        <v>234</v>
       </c>
       <c r="B235" t="inlineStr"/>
       <c r="C235" t="inlineStr">
@@ -12456,10 +11985,8 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
+      <c r="A236" t="n">
+        <v>235</v>
       </c>
       <c r="B236" t="inlineStr"/>
       <c r="C236" t="inlineStr">
@@ -12511,10 +12038,8 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
+      <c r="A237" t="n">
+        <v>236</v>
       </c>
       <c r="B237" t="inlineStr"/>
       <c r="C237" t="inlineStr">
@@ -12566,10 +12091,8 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
+      <c r="A238" t="n">
+        <v>237</v>
       </c>
       <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr">
@@ -12621,10 +12144,8 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
+      <c r="A239" t="n">
+        <v>238</v>
       </c>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="inlineStr">
@@ -12676,10 +12197,8 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
+      <c r="A240" t="n">
+        <v>239</v>
       </c>
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr">
@@ -12731,10 +12250,8 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="A241" t="n">
+        <v>240</v>
       </c>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr">
@@ -12786,10 +12303,8 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
+      <c r="A242" t="n">
+        <v>241</v>
       </c>
       <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr">
@@ -12841,10 +12356,8 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
+      <c r="A243" t="n">
+        <v>242</v>
       </c>
       <c r="B243" t="inlineStr"/>
       <c r="C243" t="inlineStr">
@@ -12896,10 +12409,8 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
+      <c r="A244" t="n">
+        <v>243</v>
       </c>
       <c r="B244" t="inlineStr"/>
       <c r="C244" t="inlineStr">
@@ -12951,10 +12462,8 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
+      <c r="A245" t="n">
+        <v>244</v>
       </c>
       <c r="B245" t="inlineStr"/>
       <c r="C245" t="inlineStr">
@@ -13002,10 +12511,8 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
+      <c r="A246" t="n">
+        <v>245</v>
       </c>
       <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr">
@@ -13053,10 +12560,8 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
+      <c r="A247" t="n">
+        <v>246</v>
       </c>
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
@@ -13104,10 +12609,8 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
+      <c r="A248" t="n">
+        <v>247</v>
       </c>
       <c r="B248" t="inlineStr"/>
       <c r="C248" t="inlineStr">
@@ -13159,10 +12662,8 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
+      <c r="A249" t="n">
+        <v>248</v>
       </c>
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="inlineStr">
@@ -13214,10 +12715,8 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
+      <c r="A250" t="n">
+        <v>249</v>
       </c>
       <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr">
@@ -13265,10 +12764,8 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
+      <c r="A251" t="n">
+        <v>250</v>
       </c>
       <c r="B251" t="inlineStr"/>
       <c r="C251" t="inlineStr">
@@ -13320,10 +12817,8 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
+      <c r="A252" t="n">
+        <v>251</v>
       </c>
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr">
@@ -13371,10 +12866,8 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
+      <c r="A253" t="n">
+        <v>252</v>
       </c>
       <c r="B253" t="inlineStr"/>
       <c r="C253" t="inlineStr">
@@ -13422,10 +12915,8 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
+      <c r="A254" t="n">
+        <v>253</v>
       </c>
       <c r="B254" t="inlineStr"/>
       <c r="C254" t="inlineStr">
@@ -13477,10 +12968,8 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
+      <c r="A255" t="n">
+        <v>254</v>
       </c>
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr">
@@ -13532,10 +13021,8 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
+      <c r="A256" t="n">
+        <v>255</v>
       </c>
       <c r="B256" t="inlineStr"/>
       <c r="C256" t="inlineStr">
@@ -13587,10 +13074,8 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
+      <c r="A257" t="n">
+        <v>256</v>
       </c>
       <c r="B257" t="inlineStr"/>
       <c r="C257" t="inlineStr">
@@ -13642,10 +13127,8 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
+      <c r="A258" t="n">
+        <v>257</v>
       </c>
       <c r="B258" t="inlineStr"/>
       <c r="C258" t="inlineStr">
@@ -13697,10 +13180,8 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
+      <c r="A259" t="n">
+        <v>258</v>
       </c>
       <c r="B259" t="inlineStr"/>
       <c r="C259" t="inlineStr">
@@ -13752,10 +13233,8 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
+      <c r="A260" t="n">
+        <v>259</v>
       </c>
       <c r="B260" t="inlineStr"/>
       <c r="C260" t="inlineStr">
@@ -13807,10 +13286,8 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
+      <c r="A261" t="n">
+        <v>260</v>
       </c>
       <c r="B261" t="inlineStr"/>
       <c r="C261" t="inlineStr">
@@ -13858,10 +13335,8 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
+      <c r="A262" t="n">
+        <v>261</v>
       </c>
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="inlineStr">
@@ -13913,10 +13388,8 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
+      <c r="A263" t="n">
+        <v>262</v>
       </c>
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="inlineStr">
@@ -13968,10 +13441,8 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
+      <c r="A264" t="n">
+        <v>263</v>
       </c>
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="inlineStr">
@@ -14023,10 +13494,8 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
+      <c r="A265" t="n">
+        <v>264</v>
       </c>
       <c r="B265" t="inlineStr"/>
       <c r="C265" t="inlineStr">
@@ -14078,10 +13547,8 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
+      <c r="A266" t="n">
+        <v>265</v>
       </c>
       <c r="B266" t="inlineStr"/>
       <c r="C266" t="inlineStr">
@@ -14133,10 +13600,8 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
+      <c r="A267" t="n">
+        <v>266</v>
       </c>
       <c r="B267" t="inlineStr"/>
       <c r="C267" t="inlineStr">
@@ -14188,10 +13653,8 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
+      <c r="A268" t="n">
+        <v>267</v>
       </c>
       <c r="B268" t="inlineStr"/>
       <c r="C268" t="inlineStr">
@@ -14243,10 +13706,8 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
+      <c r="A269" t="n">
+        <v>268</v>
       </c>
       <c r="B269" t="inlineStr"/>
       <c r="C269" t="inlineStr">
@@ -14298,10 +13759,8 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+      <c r="A270" t="n">
+        <v>269</v>
       </c>
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="inlineStr">
@@ -14353,10 +13812,8 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
+      <c r="A271" t="n">
+        <v>270</v>
       </c>
       <c r="B271" t="inlineStr"/>
       <c r="C271" t="inlineStr">
@@ -14408,10 +13865,8 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
+      <c r="A272" t="n">
+        <v>271</v>
       </c>
       <c r="B272" t="inlineStr"/>
       <c r="C272" t="inlineStr">
@@ -14463,10 +13918,8 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
+      <c r="A273" t="n">
+        <v>272</v>
       </c>
       <c r="B273" t="inlineStr"/>
       <c r="C273" t="inlineStr">
@@ -14518,10 +13971,8 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
+      <c r="A274" t="n">
+        <v>273</v>
       </c>
       <c r="B274" t="inlineStr"/>
       <c r="C274" t="inlineStr">
@@ -14573,10 +14024,8 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
+      <c r="A275" t="n">
+        <v>274</v>
       </c>
       <c r="B275" t="inlineStr"/>
       <c r="C275" t="inlineStr">
@@ -14628,10 +14077,8 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
+      <c r="A276" t="n">
+        <v>275</v>
       </c>
       <c r="B276" t="inlineStr"/>
       <c r="C276" t="inlineStr">
@@ -14683,10 +14130,8 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
+      <c r="A277" t="n">
+        <v>276</v>
       </c>
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="inlineStr">
@@ -14738,10 +14183,8 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
+      <c r="A278" t="n">
+        <v>277</v>
       </c>
       <c r="B278" t="inlineStr"/>
       <c r="C278" t="inlineStr">
@@ -14793,10 +14236,8 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
+      <c r="A279" t="n">
+        <v>278</v>
       </c>
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
@@ -14848,10 +14289,8 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
+      <c r="A280" t="n">
+        <v>279</v>
       </c>
       <c r="B280" t="inlineStr"/>
       <c r="C280" t="inlineStr">
@@ -14903,10 +14342,8 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
+      <c r="A281" t="n">
+        <v>280</v>
       </c>
       <c r="B281" t="inlineStr"/>
       <c r="C281" t="inlineStr">
@@ -14958,10 +14395,8 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
+      <c r="A282" t="n">
+        <v>281</v>
       </c>
       <c r="B282" t="inlineStr"/>
       <c r="C282" t="inlineStr">
@@ -15013,10 +14448,8 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
+      <c r="A283" t="n">
+        <v>282</v>
       </c>
       <c r="B283" t="inlineStr"/>
       <c r="C283" t="inlineStr">
@@ -15068,10 +14501,8 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
+      <c r="A284" t="n">
+        <v>283</v>
       </c>
       <c r="B284" t="inlineStr"/>
       <c r="C284" t="inlineStr">
@@ -15123,10 +14554,8 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
+      <c r="A285" t="n">
+        <v>284</v>
       </c>
       <c r="B285" t="inlineStr"/>
       <c r="C285" t="inlineStr">
@@ -15178,10 +14607,8 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
+      <c r="A286" t="n">
+        <v>285</v>
       </c>
       <c r="B286" t="inlineStr"/>
       <c r="C286" t="inlineStr">
@@ -15233,10 +14660,8 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
+      <c r="A287" t="n">
+        <v>286</v>
       </c>
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="inlineStr">
@@ -15288,10 +14713,8 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
+      <c r="A288" t="n">
+        <v>287</v>
       </c>
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="inlineStr">
@@ -15343,10 +14766,8 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
+      <c r="A289" t="n">
+        <v>288</v>
       </c>
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="inlineStr">
@@ -15398,10 +14819,8 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
+      <c r="A290" t="n">
+        <v>289</v>
       </c>
       <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
@@ -15453,10 +14872,8 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
+      <c r="A291" t="n">
+        <v>290</v>
       </c>
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr">
@@ -15508,10 +14925,8 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
+      <c r="A292" t="n">
+        <v>291</v>
       </c>
       <c r="B292" t="inlineStr"/>
       <c r="C292" t="inlineStr">
@@ -15563,10 +14978,8 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
+      <c r="A293" t="n">
+        <v>292</v>
       </c>
       <c r="B293" t="inlineStr"/>
       <c r="C293" t="inlineStr">
@@ -15618,10 +15031,8 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
+      <c r="A294" t="n">
+        <v>293</v>
       </c>
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
@@ -15673,10 +15084,8 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
+      <c r="A295" t="n">
+        <v>294</v>
       </c>
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
@@ -15728,10 +15137,8 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
+      <c r="A296" t="n">
+        <v>295</v>
       </c>
       <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr">
@@ -15783,10 +15190,8 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
+      <c r="A297" t="n">
+        <v>296</v>
       </c>
       <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr">
@@ -15838,10 +15243,8 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
+      <c r="A298" t="n">
+        <v>297</v>
       </c>
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr">
@@ -15893,10 +15296,8 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
+      <c r="A299" t="n">
+        <v>298</v>
       </c>
       <c r="B299" t="inlineStr"/>
       <c r="C299" t="inlineStr">
@@ -15948,10 +15349,8 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
+      <c r="A300" t="n">
+        <v>299</v>
       </c>
       <c r="B300" t="inlineStr"/>
       <c r="C300" t="inlineStr">
@@ -16003,10 +15402,8 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+      <c r="A301" t="n">
+        <v>300</v>
       </c>
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr">
@@ -16058,10 +15455,8 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
+      <c r="A302" t="n">
+        <v>301</v>
       </c>
       <c r="B302" t="inlineStr"/>
       <c r="C302" t="inlineStr">
@@ -16113,10 +15508,8 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
+      <c r="A303" t="n">
+        <v>302</v>
       </c>
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr">
@@ -16168,10 +15561,8 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
+      <c r="A304" t="n">
+        <v>303</v>
       </c>
       <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
@@ -16223,10 +15614,8 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
+      <c r="A305" t="n">
+        <v>304</v>
       </c>
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr">
@@ -16278,10 +15667,8 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
+      <c r="A306" t="n">
+        <v>305</v>
       </c>
       <c r="B306" t="inlineStr"/>
       <c r="C306" t="inlineStr">
@@ -16333,10 +15720,8 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
+      <c r="A307" t="n">
+        <v>306</v>
       </c>
       <c r="B307" t="inlineStr"/>
       <c r="C307" t="inlineStr">
@@ -16388,10 +15773,8 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
+      <c r="A308" t="n">
+        <v>307</v>
       </c>
       <c r="B308" t="inlineStr"/>
       <c r="C308" t="inlineStr">
@@ -16443,10 +15826,8 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
+      <c r="A309" t="n">
+        <v>308</v>
       </c>
       <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr">
@@ -16498,10 +15879,8 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
+      <c r="A310" t="n">
+        <v>309</v>
       </c>
       <c r="B310" t="inlineStr"/>
       <c r="C310" t="inlineStr">
@@ -16553,10 +15932,8 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
+      <c r="A311" t="n">
+        <v>310</v>
       </c>
       <c r="B311" t="inlineStr"/>
       <c r="C311" t="inlineStr">
@@ -16608,10 +15985,8 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
+      <c r="A312" t="n">
+        <v>311</v>
       </c>
       <c r="B312" t="inlineStr"/>
       <c r="C312" t="inlineStr">
@@ -16663,10 +16038,8 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
+      <c r="A313" t="n">
+        <v>312</v>
       </c>
       <c r="B313" t="inlineStr"/>
       <c r="C313" t="inlineStr">
@@ -16718,10 +16091,8 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
+      <c r="A314" t="n">
+        <v>313</v>
       </c>
       <c r="B314" t="inlineStr"/>
       <c r="C314" t="inlineStr">
@@ -16773,10 +16144,8 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
+      <c r="A315" t="n">
+        <v>314</v>
       </c>
       <c r="B315" t="inlineStr"/>
       <c r="C315" t="inlineStr">
@@ -16828,10 +16197,8 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
+      <c r="A316" t="n">
+        <v>315</v>
       </c>
       <c r="B316" t="inlineStr"/>
       <c r="C316" t="inlineStr">
@@ -16883,10 +16250,8 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
+      <c r="A317" t="n">
+        <v>316</v>
       </c>
       <c r="B317" t="inlineStr"/>
       <c r="C317" t="inlineStr">
@@ -16938,10 +16303,8 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
+      <c r="A318" t="n">
+        <v>317</v>
       </c>
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="inlineStr">
@@ -16993,10 +16356,8 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
+      <c r="A319" t="n">
+        <v>318</v>
       </c>
       <c r="B319" t="inlineStr"/>
       <c r="C319" t="inlineStr">
@@ -17048,10 +16409,8 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
+      <c r="A320" t="n">
+        <v>319</v>
       </c>
       <c r="B320" t="inlineStr"/>
       <c r="C320" t="inlineStr">
@@ -17103,10 +16462,8 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
+      <c r="A321" t="n">
+        <v>320</v>
       </c>
       <c r="B321" t="inlineStr"/>
       <c r="C321" t="inlineStr">
@@ -17158,10 +16515,8 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
+      <c r="A322" t="n">
+        <v>321</v>
       </c>
       <c r="B322" t="inlineStr"/>
       <c r="C322" t="inlineStr">
@@ -17213,10 +16568,8 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
+      <c r="A323" t="n">
+        <v>322</v>
       </c>
       <c r="B323" t="inlineStr"/>
       <c r="C323" t="inlineStr">
@@ -17268,10 +16621,8 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
+      <c r="A324" t="n">
+        <v>323</v>
       </c>
       <c r="B324" t="inlineStr"/>
       <c r="C324" t="inlineStr">
@@ -17323,10 +16674,8 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
+      <c r="A325" t="n">
+        <v>324</v>
       </c>
       <c r="B325" t="inlineStr"/>
       <c r="C325" t="inlineStr">
@@ -17378,10 +16727,8 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
+      <c r="A326" t="n">
+        <v>325</v>
       </c>
       <c r="B326" t="inlineStr"/>
       <c r="C326" t="inlineStr">
@@ -17433,10 +16780,8 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
+      <c r="A327" t="n">
+        <v>326</v>
       </c>
       <c r="B327" t="inlineStr"/>
       <c r="C327" t="inlineStr">
@@ -17488,10 +16833,8 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
+      <c r="A328" t="n">
+        <v>327</v>
       </c>
       <c r="B328" t="inlineStr"/>
       <c r="C328" t="inlineStr">
@@ -17543,10 +16886,8 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="A329" t="n">
+        <v>328</v>
       </c>
       <c r="B329" t="inlineStr"/>
       <c r="C329" t="inlineStr">
@@ -17598,10 +16939,8 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
+      <c r="A330" t="n">
+        <v>329</v>
       </c>
       <c r="B330" t="inlineStr"/>
       <c r="C330" t="inlineStr">
@@ -17653,10 +16992,8 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
+      <c r="A331" t="n">
+        <v>330</v>
       </c>
       <c r="B331" t="inlineStr"/>
       <c r="C331" t="inlineStr">
@@ -17708,10 +17045,8 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
+      <c r="A332" t="n">
+        <v>331</v>
       </c>
       <c r="B332" t="inlineStr"/>
       <c r="C332" t="inlineStr">
@@ -17763,10 +17098,8 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
+      <c r="A333" t="n">
+        <v>332</v>
       </c>
       <c r="B333" t="inlineStr"/>
       <c r="C333" t="inlineStr">
@@ -17818,10 +17151,8 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
+      <c r="A334" t="n">
+        <v>333</v>
       </c>
       <c r="B334" t="inlineStr"/>
       <c r="C334" t="inlineStr">
@@ -17873,10 +17204,8 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
+      <c r="A335" t="n">
+        <v>334</v>
       </c>
       <c r="B335" t="inlineStr"/>
       <c r="C335" t="inlineStr">
@@ -17928,10 +17257,8 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
+      <c r="A336" t="n">
+        <v>335</v>
       </c>
       <c r="B336" t="inlineStr"/>
       <c r="C336" t="inlineStr">
@@ -17983,10 +17310,8 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
+      <c r="A337" t="n">
+        <v>336</v>
       </c>
       <c r="B337" t="inlineStr"/>
       <c r="C337" t="inlineStr">
@@ -18038,10 +17363,8 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
+      <c r="A338" t="n">
+        <v>337</v>
       </c>
       <c r="B338" t="inlineStr"/>
       <c r="C338" t="inlineStr">
@@ -18093,10 +17416,8 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
+      <c r="A339" t="n">
+        <v>338</v>
       </c>
       <c r="B339" t="inlineStr"/>
       <c r="C339" t="inlineStr">
@@ -18148,10 +17469,8 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
+      <c r="A340" t="n">
+        <v>339</v>
       </c>
       <c r="B340" t="inlineStr"/>
       <c r="C340" t="inlineStr">
@@ -18203,10 +17522,8 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
+      <c r="A341" t="n">
+        <v>340</v>
       </c>
       <c r="B341" t="inlineStr"/>
       <c r="C341" t="inlineStr">
@@ -18258,10 +17575,8 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
+      <c r="A342" t="n">
+        <v>341</v>
       </c>
       <c r="B342" t="inlineStr"/>
       <c r="C342" t="inlineStr">
@@ -18313,10 +17628,8 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
+      <c r="A343" t="n">
+        <v>342</v>
       </c>
       <c r="B343" t="inlineStr"/>
       <c r="C343" t="inlineStr">
@@ -18368,10 +17681,8 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
+      <c r="A344" t="n">
+        <v>343</v>
       </c>
       <c r="B344" t="inlineStr"/>
       <c r="C344" t="inlineStr">
@@ -18423,10 +17734,8 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
+      <c r="A345" t="n">
+        <v>344</v>
       </c>
       <c r="B345" t="inlineStr"/>
       <c r="C345" t="inlineStr">
@@ -18478,10 +17787,8 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
+      <c r="A346" t="n">
+        <v>345</v>
       </c>
       <c r="B346" t="inlineStr"/>
       <c r="C346" t="inlineStr">
@@ -18533,10 +17840,8 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
+      <c r="A347" t="n">
+        <v>346</v>
       </c>
       <c r="B347" t="inlineStr"/>
       <c r="C347" t="inlineStr">
@@ -18588,10 +17893,8 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
+      <c r="A348" t="n">
+        <v>347</v>
       </c>
       <c r="B348" t="inlineStr"/>
       <c r="C348" t="inlineStr">
@@ -18643,10 +17946,8 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
+      <c r="A349" t="n">
+        <v>348</v>
       </c>
       <c r="B349" t="inlineStr"/>
       <c r="C349" t="inlineStr">
@@ -18698,10 +17999,8 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
+      <c r="A350" t="n">
+        <v>349</v>
       </c>
       <c r="B350" t="inlineStr"/>
       <c r="C350" t="inlineStr">
@@ -18753,10 +18052,8 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
+      <c r="A351" t="n">
+        <v>350</v>
       </c>
       <c r="B351" t="inlineStr"/>
       <c r="C351" t="inlineStr">
@@ -18808,10 +18105,8 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
+      <c r="A352" t="n">
+        <v>351</v>
       </c>
       <c r="B352" t="inlineStr"/>
       <c r="C352" t="inlineStr">
@@ -18863,10 +18158,8 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
+      <c r="A353" t="n">
+        <v>352</v>
       </c>
       <c r="B353" t="inlineStr"/>
       <c r="C353" t="inlineStr">
@@ -18918,10 +18211,8 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
+      <c r="A354" t="n">
+        <v>353</v>
       </c>
       <c r="B354" t="inlineStr"/>
       <c r="C354" t="inlineStr">
@@ -18973,10 +18264,8 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
+      <c r="A355" t="n">
+        <v>354</v>
       </c>
       <c r="B355" t="inlineStr"/>
       <c r="C355" t="inlineStr">
@@ -19028,10 +18317,8 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
+      <c r="A356" t="n">
+        <v>355</v>
       </c>
       <c r="B356" t="inlineStr"/>
       <c r="C356" t="inlineStr">
@@ -19083,10 +18370,8 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>356</t>
-        </is>
+      <c r="A357" t="n">
+        <v>356</v>
       </c>
       <c r="B357" t="inlineStr"/>
       <c r="C357" t="inlineStr">
@@ -19134,10 +18419,8 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
+      <c r="A358" t="n">
+        <v>357</v>
       </c>
       <c r="B358" t="inlineStr"/>
       <c r="C358" t="inlineStr">
@@ -19189,10 +18472,8 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
+      <c r="A359" t="n">
+        <v>358</v>
       </c>
       <c r="B359" t="inlineStr"/>
       <c r="C359" t="inlineStr">
@@ -19240,10 +18521,8 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
+      <c r="A360" t="n">
+        <v>359</v>
       </c>
       <c r="B360" t="inlineStr"/>
       <c r="C360" t="inlineStr">
@@ -19291,10 +18570,8 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
+      <c r="A361" t="n">
+        <v>360</v>
       </c>
       <c r="B361" t="inlineStr"/>
       <c r="C361" t="inlineStr">
@@ -19342,10 +18619,8 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
+      <c r="A362" t="n">
+        <v>361</v>
       </c>
       <c r="B362" t="inlineStr"/>
       <c r="C362" t="inlineStr">
@@ -19393,10 +18668,8 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
+      <c r="A363" t="n">
+        <v>362</v>
       </c>
       <c r="B363" t="inlineStr"/>
       <c r="C363" t="inlineStr">
@@ -19444,10 +18717,8 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
+      <c r="A364" t="n">
+        <v>363</v>
       </c>
       <c r="B364" t="inlineStr"/>
       <c r="C364" t="inlineStr">
@@ -19495,10 +18766,8 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
+      <c r="A365" t="n">
+        <v>364</v>
       </c>
       <c r="B365" t="inlineStr"/>
       <c r="C365" t="inlineStr">
@@ -19546,10 +18815,8 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
+      <c r="A366" t="n">
+        <v>365</v>
       </c>
       <c r="B366" t="inlineStr"/>
       <c r="C366" t="inlineStr">
@@ -19597,10 +18864,8 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
+      <c r="A367" t="n">
+        <v>366</v>
       </c>
       <c r="B367" t="inlineStr"/>
       <c r="C367" t="inlineStr">
@@ -19648,10 +18913,8 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
+      <c r="A368" t="n">
+        <v>367</v>
       </c>
       <c r="B368" t="inlineStr"/>
       <c r="C368" t="inlineStr">
@@ -19699,10 +18962,8 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
+      <c r="A369" t="n">
+        <v>368</v>
       </c>
       <c r="B369" t="inlineStr"/>
       <c r="C369" t="inlineStr">
@@ -19750,10 +19011,8 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
+      <c r="A370" t="n">
+        <v>369</v>
       </c>
       <c r="B370" t="inlineStr"/>
       <c r="C370" t="inlineStr">
@@ -19801,10 +19060,8 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
+      <c r="A371" t="n">
+        <v>370</v>
       </c>
       <c r="B371" t="inlineStr"/>
       <c r="C371" t="inlineStr">
@@ -19852,10 +19109,8 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
+      <c r="A372" t="n">
+        <v>371</v>
       </c>
       <c r="B372" t="inlineStr"/>
       <c r="C372" t="inlineStr">
@@ -19903,10 +19158,8 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
+      <c r="A373" t="n">
+        <v>372</v>
       </c>
       <c r="B373" t="inlineStr"/>
       <c r="C373" t="inlineStr">
@@ -19954,10 +19207,8 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
+      <c r="A374" t="n">
+        <v>373</v>
       </c>
       <c r="B374" t="inlineStr"/>
       <c r="C374" t="inlineStr">
@@ -20005,10 +19256,8 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
+      <c r="A375" t="n">
+        <v>374</v>
       </c>
       <c r="B375" t="inlineStr"/>
       <c r="C375" t="inlineStr">
@@ -20056,10 +19305,8 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
+      <c r="A376" t="n">
+        <v>375</v>
       </c>
       <c r="B376" t="inlineStr"/>
       <c r="C376" t="inlineStr">
@@ -20111,10 +19358,8 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
+      <c r="A377" t="n">
+        <v>376</v>
       </c>
       <c r="B377" t="inlineStr"/>
       <c r="C377" t="inlineStr">
@@ -20166,10 +19411,8 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
+      <c r="A378" t="n">
+        <v>377</v>
       </c>
       <c r="B378" t="inlineStr"/>
       <c r="C378" t="inlineStr">
@@ -20217,10 +19460,8 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
+      <c r="A379" t="n">
+        <v>378</v>
       </c>
       <c r="B379" t="inlineStr"/>
       <c r="C379" t="inlineStr">
@@ -20268,10 +19509,8 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
+      <c r="A380" t="n">
+        <v>379</v>
       </c>
       <c r="B380" t="inlineStr"/>
       <c r="C380" t="inlineStr">
@@ -20319,10 +19558,8 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
+      <c r="A381" t="n">
+        <v>380</v>
       </c>
       <c r="B381" t="inlineStr"/>
       <c r="C381" t="inlineStr">
@@ -20374,10 +19611,8 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
+      <c r="A382" t="n">
+        <v>381</v>
       </c>
       <c r="B382" t="inlineStr"/>
       <c r="C382" t="inlineStr">
@@ -20429,10 +19664,8 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
+      <c r="A383" t="n">
+        <v>382</v>
       </c>
       <c r="B383" t="inlineStr"/>
       <c r="C383" t="inlineStr">
@@ -20484,10 +19717,8 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>383</t>
-        </is>
+      <c r="A384" t="n">
+        <v>383</v>
       </c>
       <c r="B384" t="inlineStr"/>
       <c r="C384" t="inlineStr">
@@ -20539,10 +19770,8 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
+      <c r="A385" t="n">
+        <v>384</v>
       </c>
       <c r="B385" t="inlineStr"/>
       <c r="C385" t="inlineStr">
@@ -20594,10 +19823,8 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
+      <c r="A386" t="n">
+        <v>385</v>
       </c>
       <c r="B386" t="inlineStr"/>
       <c r="C386" t="inlineStr">
@@ -20649,10 +19876,8 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>386</t>
-        </is>
+      <c r="A387" t="n">
+        <v>386</v>
       </c>
       <c r="B387" t="inlineStr"/>
       <c r="C387" t="inlineStr">
@@ -20704,10 +19929,8 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
+      <c r="A388" t="n">
+        <v>387</v>
       </c>
       <c r="B388" t="inlineStr"/>
       <c r="C388" t="inlineStr">
@@ -20755,10 +19978,8 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
+      <c r="A389" t="n">
+        <v>388</v>
       </c>
       <c r="B389" t="inlineStr"/>
       <c r="C389" t="inlineStr">
@@ -20810,10 +20031,8 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="A390" t="n">
+        <v>389</v>
       </c>
       <c r="B390" t="inlineStr"/>
       <c r="C390" t="inlineStr">
@@ -20865,10 +20084,8 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
+      <c r="A391" t="n">
+        <v>390</v>
       </c>
       <c r="B391" t="inlineStr"/>
       <c r="C391" t="inlineStr">
@@ -20920,10 +20137,8 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
+      <c r="A392" t="n">
+        <v>391</v>
       </c>
       <c r="B392" t="inlineStr"/>
       <c r="C392" t="inlineStr">
@@ -20975,10 +20190,8 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
+      <c r="A393" t="n">
+        <v>392</v>
       </c>
       <c r="B393" t="inlineStr"/>
       <c r="C393" t="inlineStr">
@@ -21030,10 +20243,8 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
+      <c r="A394" t="n">
+        <v>393</v>
       </c>
       <c r="B394" t="inlineStr"/>
       <c r="C394" t="inlineStr">
@@ -21085,10 +20296,8 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
+      <c r="A395" t="n">
+        <v>394</v>
       </c>
       <c r="B395" t="inlineStr"/>
       <c r="C395" t="inlineStr">
@@ -21140,10 +20349,8 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
+      <c r="A396" t="n">
+        <v>395</v>
       </c>
       <c r="B396" t="inlineStr"/>
       <c r="C396" t="inlineStr">
@@ -21195,10 +20402,8 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
+      <c r="A397" t="n">
+        <v>396</v>
       </c>
       <c r="B397" t="inlineStr"/>
       <c r="C397" t="inlineStr">
@@ -21250,10 +20455,8 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
+      <c r="A398" t="n">
+        <v>397</v>
       </c>
       <c r="B398" t="inlineStr"/>
       <c r="C398" t="inlineStr">
@@ -21301,10 +20504,8 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
+      <c r="A399" t="n">
+        <v>398</v>
       </c>
       <c r="B399" t="inlineStr"/>
       <c r="C399" t="inlineStr">
@@ -21356,10 +20557,8 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
+      <c r="A400" t="n">
+        <v>399</v>
       </c>
       <c r="B400" t="inlineStr"/>
       <c r="C400" t="inlineStr">
@@ -21411,10 +20610,8 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+      <c r="A401" t="n">
+        <v>400</v>
       </c>
       <c r="B401" t="inlineStr"/>
       <c r="C401" t="inlineStr">
@@ -21466,10 +20663,8 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
+      <c r="A402" t="n">
+        <v>401</v>
       </c>
       <c r="B402" t="inlineStr"/>
       <c r="C402" t="inlineStr">
@@ -21521,10 +20716,8 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
+      <c r="A403" t="n">
+        <v>402</v>
       </c>
       <c r="B403" t="inlineStr"/>
       <c r="C403" t="inlineStr">
@@ -21576,10 +20769,8 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
+      <c r="A404" t="n">
+        <v>403</v>
       </c>
       <c r="B404" t="inlineStr"/>
       <c r="C404" t="inlineStr">
@@ -21631,10 +20822,8 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
+      <c r="A405" t="n">
+        <v>405</v>
       </c>
       <c r="B405" t="inlineStr"/>
       <c r="C405" t="inlineStr"/>
@@ -21657,7 +20846,9 @@
         </is>
       </c>
       <c r="J405" t="inlineStr"/>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="n">
+        <v>0</v>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>EA</t>
@@ -21680,14 +20871,12 @@
         <v>0</v>
       </c>
       <c r="S405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>406</t>
-        </is>
+      <c r="A406" t="n">
+        <v>406</v>
       </c>
       <c r="B406" t="inlineStr"/>
       <c r="C406" t="inlineStr"/>
@@ -21735,14 +20924,12 @@
         <v>1000</v>
       </c>
       <c r="S406" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
+      <c r="A407" t="n">
+        <v>407</v>
       </c>
       <c r="B407" t="inlineStr"/>
       <c r="C407" t="inlineStr"/>
@@ -21765,7 +20952,9 @@
         </is>
       </c>
       <c r="J407" t="inlineStr"/>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="n">
+        <v>0</v>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>EA</t>
@@ -21792,10 +20981,8 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="A408" t="n">
+        <v>408</v>
       </c>
       <c r="B408" t="inlineStr"/>
       <c r="C408" t="inlineStr"/>
@@ -21814,7 +21001,9 @@
       </c>
       <c r="I408" t="inlineStr"/>
       <c r="J408" t="inlineStr"/>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="n">
+        <v>0</v>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>EA</t>
@@ -21837,10 +21026,8 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
+      <c r="A409" t="n">
+        <v>409</v>
       </c>
       <c r="B409" t="inlineStr"/>
       <c r="C409" t="inlineStr"/>
@@ -21859,7 +21046,9 @@
       </c>
       <c r="I409" t="inlineStr"/>
       <c r="J409" t="inlineStr"/>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="n">
+        <v>0</v>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>EA</t>
@@ -21882,10 +21071,8 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
+      <c r="A410" t="n">
+        <v>410</v>
       </c>
       <c r="B410" t="inlineStr"/>
       <c r="C410" t="inlineStr"/>
@@ -21904,7 +21091,9 @@
       </c>
       <c r="I410" t="inlineStr"/>
       <c r="J410" t="inlineStr"/>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="n">
+        <v>0</v>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>EA</t>
@@ -21923,14 +21112,12 @@
         <v>0</v>
       </c>
       <c r="S410" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
+      <c r="A411" t="n">
+        <v>412</v>
       </c>
       <c r="B411" t="inlineStr"/>
       <c r="C411" t="inlineStr"/>
@@ -21949,7 +21136,9 @@
       </c>
       <c r="I411" t="inlineStr"/>
       <c r="J411" t="inlineStr"/>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="n">
+        <v>0</v>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>EA</t>
@@ -21968,14 +21157,12 @@
         <v>0</v>
       </c>
       <c r="S411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
+      <c r="A412" t="n">
+        <v>413</v>
       </c>
       <c r="B412" t="inlineStr"/>
       <c r="C412" t="inlineStr"/>
@@ -21994,7 +21181,9 @@
       </c>
       <c r="I412" t="inlineStr"/>
       <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="n">
+        <v>0</v>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>EA</t>
@@ -22009,16 +21198,16 @@
       <c r="Q412" t="n">
         <v>5</v>
       </c>
-      <c r="R412" t="inlineStr"/>
+      <c r="R412" t="n">
+        <v>0</v>
+      </c>
       <c r="S412" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
+      <c r="A413" t="n">
+        <v>414</v>
       </c>
       <c r="B413" t="inlineStr"/>
       <c r="C413" t="inlineStr"/>
@@ -22037,7 +21226,9 @@
       </c>
       <c r="I413" t="inlineStr"/>
       <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="n">
+        <v>0</v>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>EA</t>
@@ -22052,16 +21243,16 @@
       <c r="Q413" t="n">
         <v>10</v>
       </c>
-      <c r="R413" t="inlineStr"/>
+      <c r="R413" t="n">
+        <v>0</v>
+      </c>
       <c r="S413" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
+      <c r="A414" t="n">
+        <v>415</v>
       </c>
       <c r="B414" t="inlineStr"/>
       <c r="C414" t="inlineStr"/>
@@ -22080,7 +21271,9 @@
       </c>
       <c r="I414" t="inlineStr"/>
       <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="n">
+        <v>0</v>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>EA</t>
@@ -22095,16 +21288,16 @@
       <c r="Q414" t="n">
         <v>5</v>
       </c>
-      <c r="R414" t="inlineStr"/>
+      <c r="R414" t="n">
+        <v>0</v>
+      </c>
       <c r="S414" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
+      <c r="A415" t="n">
+        <v>416</v>
       </c>
       <c r="B415" t="inlineStr"/>
       <c r="C415" t="inlineStr"/>
@@ -22123,7 +21316,9 @@
       </c>
       <c r="I415" t="inlineStr"/>
       <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="n">
+        <v>0</v>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>EA</t>
@@ -22138,16 +21333,16 @@
       <c r="Q415" t="n">
         <v>10</v>
       </c>
-      <c r="R415" t="inlineStr"/>
+      <c r="R415" t="n">
+        <v>0</v>
+      </c>
       <c r="S415" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
+      <c r="A416" t="n">
+        <v>417</v>
       </c>
       <c r="B416" t="inlineStr"/>
       <c r="C416" t="inlineStr"/>
@@ -22166,7 +21361,9 @@
       </c>
       <c r="I416" t="inlineStr"/>
       <c r="J416" t="inlineStr"/>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="n">
+        <v>0</v>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>EA</t>
@@ -22181,16 +21378,16 @@
       <c r="Q416" t="n">
         <v>10</v>
       </c>
-      <c r="R416" t="inlineStr"/>
+      <c r="R416" t="n">
+        <v>0</v>
+      </c>
       <c r="S416" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
+      <c r="A417" t="n">
+        <v>418</v>
       </c>
       <c r="B417" t="inlineStr"/>
       <c r="C417" t="inlineStr"/>
@@ -22238,10 +21435,8 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
+      <c r="A418" t="n">
+        <v>419</v>
       </c>
       <c r="B418" t="inlineStr"/>
       <c r="C418" t="inlineStr"/>
@@ -22289,10 +21484,8 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
+      <c r="A419" t="n">
+        <v>420</v>
       </c>
       <c r="B419" t="inlineStr"/>
       <c r="C419" t="inlineStr"/>
@@ -22340,10 +21533,8 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
+      <c r="A420" t="n">
+        <v>421</v>
       </c>
       <c r="B420" t="inlineStr"/>
       <c r="C420" t="inlineStr"/>
@@ -22395,10 +21586,8 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
+      <c r="A421" t="n">
+        <v>422</v>
       </c>
       <c r="B421" t="inlineStr"/>
       <c r="C421" t="inlineStr"/>
@@ -22450,10 +21639,8 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
+      <c r="A422" t="n">
+        <v>423</v>
       </c>
       <c r="B422" t="inlineStr"/>
       <c r="C422" t="inlineStr"/>
@@ -22505,10 +21692,8 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
+      <c r="A423" t="n">
+        <v>424</v>
       </c>
       <c r="B423" t="inlineStr"/>
       <c r="C423" t="inlineStr"/>
@@ -22560,10 +21745,8 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
+      <c r="A424" t="n">
+        <v>425</v>
       </c>
       <c r="B424" t="inlineStr"/>
       <c r="C424" t="inlineStr"/>
@@ -22615,10 +21798,8 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
+      <c r="A425" t="n">
+        <v>426</v>
       </c>
       <c r="B425" t="inlineStr"/>
       <c r="C425" t="inlineStr"/>
@@ -22667,6 +21848,59 @@
       </c>
       <c r="S425" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>427</v>
+      </c>
+      <c r="B426" t="inlineStr"/>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Carestream MX125-10*12"</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Carestream MX125-10*12"</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr"/>
+      <c r="I426" t="inlineStr"/>
+      <c r="J426" t="inlineStr"/>
+      <c r="K426" t="n">
+        <v>0</v>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M426" t="n">
+        <v>0</v>
+      </c>
+      <c r="N426" t="inlineStr"/>
+      <c r="O426" t="inlineStr"/>
+      <c r="P426" t="inlineStr"/>
+      <c r="Q426" t="n">
+        <v>10</v>
+      </c>
+      <c r="R426" t="n">
+        <v>0</v>
+      </c>
+      <c r="S426" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -22680,7 +21914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22798,132 +22032,6 @@
         <is>
           <t>수량</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46129.55760175926</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>-50</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>K1 PJT 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>K1 PJT</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>R-RAY</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Carestream MX125-3⅓*12"</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46129.66845252315</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>-60</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>K1 PJT 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>K1 PJT</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>R-RAY</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Carestream MX125-3⅓*12"</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="n">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -22937,7 +22045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22974,6 +22082,16 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>Entry Date</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>MaterialID</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>EntryDate</t>
         </is>
       </c>
     </row>
@@ -22988,7 +22106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN2"/>
+  <dimension ref="A1:BO1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23322,166 +22440,11 @@
           <t>회사코드</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46129</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>K1 PJT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="1" t="n">
-        <v>46129.66845251157</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>R-RAY</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1530000</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>09:00~24:00</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>26,000</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>대리 현해룡</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:00~24:00</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>26,000</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>Carestream MX125-3⅓*12"</t>
-        </is>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="inlineStr"/>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>업체명</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23494,7 +22457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23559,89 +22522,557 @@
         </is>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Spec</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>이사</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>{"\uc774\uc0ac": {"personnel": "", "period": "", "unit_price": "230,208"}, "\ubd80\uc7a5": {"personnel": "", "period": "", "unit_price": "230,208"}, "\ucc28\uc7a5": {"personnel": "", "period": "", "unit_price": "198,625"}, "\uacfc\uc7a5": {"personnel": "", "period": "", "unit_price": "171,542"}, "\ub300\ub9ac": {"personnel": "", "period": "", "unit_price": "158,000"}, "\uacc4\uc7a5": {"personnel": "", "period": "", "unit_price": "144,458"}, "\uc8fc\uc784": {"personnel": "", "period": "", "unit_price": "130,917"}, "\uae30\uc0ac": {"personnel": "", "period": "", "unit_price": "121,875"}, "\uc5f0\uc7a5\uadfc\ubb34": {"personnel": "", "period": "", "unit_price": "4,000"}, "\uc57c\uac04\uadfc\ubb34": {"personnel": "", "period": "", "unit_price": "5,000"}, "\ud734\uc77c\uadfc\ubb34": {"personnel": "", "period": "", "unit_price": "7,500"}}</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>[{"qty": "", "price": "1,500"}, {"qty": "", "price": "2,300"}, {"qty": "", "price": "2,000"}, {"qty": "", "price": "2,350"}, {"qty": "", "price": "1,800"}, {"qty": "", "price": "990"}, {"qty": "", "price": "100,000"}, {"qty": "", "price": "16,500"}, {"qty": "", "price": "16,500"}, {"qty": "", "price": "2,500"}]</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>{"site_expense": [{"cat": "\ucc28\ub7c9\uc720\uc9c0\ube44", "cont": "\uc8fc\uc720, \uc218\ub9ac, \ud1b5\ud589, \uc8fc\ucc28 \ub4f1", "ppl": "N/A", "qty": "12", "unit": "\uac1c\uc6d4", "price": "150,000", "amount": "0"}, {"cat": "\uc18c\ubaa8\ud488\ube44", "cont": "\uc7a5\uac11,\uc77c\ud68c\uc6a9 \uc791\uc5c5\ubcf5\uc678", "ppl": "N/A", "qty": "12", "unit": "\uac1c\uc6d4", "price": "15,000", "amount": "0"}, {"cat": "\ubcf5\ub9ac\ud6c4\uc0dd\ube44", "cont": "\uc0dd\uc218, \uc74c\ub8cc \uc678 \uae30\ud0c0", "ppl": "N/A", "qty": "12", "unit": "\uac1c\uc6d4", "price": "50,000", "amount": "0"}, {"cat": "Se-175", "cont": "\ubc29\uc0ac\uc131\ub3d9\uc704\uc6d0\uc18c \uad6c\ub9e4", "ppl": "N/A", "qty": "1", "unit": "EA", "price": "10,000,000", "amount": "0"}], "rental": [{"cat": "", "spec": "", "qty": "", "period": "", "unit": "", "price": "0", "amount": "0"}, {"cat": "", "spec": "", "qty": "", "period": "", "unit": "", "price": "0", "amount": "0"}, {"cat": "", "spec": "", "qty": "", "period": "", "unit": "", "price": "0", "amount": "0"}], "outsource": [{"cat": "\ucf00\uc774\uc5d4\ub514\uc774", "work": "\ubc29\uc0ac\uc120\ud22c\uacfc\uac80\uc0ac", "count": "0", "price": "15,000", "amount": "0"}, {"cat": "", "work": "", "count": "0", "price": "0", "amount": "0"}, {"cat": "", "work": "", "count": "0", "price": "0", "amount": "0"}], "depreciation": [{"item": "PAUT \uc7a5\ube44", "spec": "", "life": "5", "qty": "1", "days": "0", "rate": "44,444", "amount": "0"}, {"item": "PAUT SCANNER (MANUAL)", "spec": "", "life": "5", "qty": "1", "days": "0", "rate": "5,556", "amount": "0"}, {"item": "PAUT SCANNER (COBRA)", "spec": "", "life": "5", "qty": "1", "days": "0", "rate": "16,667", "amount": "0"}, {"item": "YOKE", "spec": "", "life": "5", "qty": "1", "days": "0", "rate": "222", "amount": "0"}, {"item": "\ud604\uc0c1\uc6a9 \ud0d1\ucc28(5\ub144\uac04 \ubcf4\ud5d8\ube44 \ud3ec\ud568)", "spec": "", "life": "5", "qty": "0", "days": "0", "rate": "16,667", "amount": "0"}, {"item": "\uc2a4\ud0c0\ub809\uc2a4(5\ub144\uac04 \ubcf4\ud5d8\ube44 \ud3ec\ud568)", "spec": "", "life": "5", "qty": "1", "days": "0", "rate": "16,667", "amount": "0"}]}</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>55250000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>롯데현장</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>부장</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>{"\uc774\uc0ac": {"personnel": "", "period": "", "unit_price": "230,208"}, "\ubd80\uc7a5": {"personnel": "", "period": "", "unit_price": "230,208"}, "\ucc28\uc7a5": {"personnel": "", "period": "", "unit_price": "198,625"}, "\uacfc\uc7a5": {"personnel": "", "period": "", "unit_price": "171,542"}, "\ub300\ub9ac": {"personnel": "", "period": "", "unit_price": "158,000"}, "\uacc4\uc7a5": {"personnel": "", "period": "", "unit_price": "144,458"}, "\uc8fc\uc784": {"personnel": "", "period": "", "unit_price": "130,917"}, "\uae30\uc0ac": {"personnel": "", "period": "", "unit_price": "121,875"}, "\uc5f0\uc7a5\uadfc\ubb34": {"personnel": "", "period": "", "unit_price": "4,000"}, "\uc57c\uac04\uadfc\ubb34": {"personnel": "", "period": "", "unit_price": "5,000"}, "\ud734\uc77c\uadfc\ubb34": {"personnel": "", "period": "", "unit_price": "7,500"}}</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>[{"qty": "", "price": "1,500"}, {"qty": "", "price": "2,300"}, {"qty": "", "price": "2,000"}, {"qty": "", "price": "2,350"}, {"qty": "", "price": "1,800"}, {"qty": "", "price": "990"}, {"qty": "", "price": "100,000"}, {"qty": "", "price": "16,500"}, {"qty": "", "price": "16,500"}, {"qty": "", "price": "2,500"}]</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>{"site_expense": [{"cat": "\ucc28\ub7c9\uc720\uc9c0\ube44", "cont": "\uc8fc\uc720, \uc218\ub9ac, \ud1b5\ud589, \uc8fc\ucc28 \ub4f1", "ppl": "N/A", "qty": "12", "unit": "\uac1c\uc6d4", "price": "150,000", "amount": "1,800,000"}, {"cat": "\uc18c\ubaa8\ud488\ube44", "cont": "\uc7a5\uac11,\uc77c\ud68c\uc6a9 \uc791\uc5c5\ubcf5\uc678", "ppl": "N/A", "qty": "12", "unit": "\uac1c\uc6d4", "price": "15,000", "amount": "180,000"}, {"cat": "\ubcf5\ub9ac\ud6c4\uc0dd\ube44", "cont": "\uc0dd\uc218, \uc74c\ub8cc \uc678 \uae30\ud0c0", "ppl": "N/A", "qty": "12", "unit": "\uac1c\uc6d4", "price": "50,000", "amount": "600,000"}, {"cat": "Se-175", "cont": "\ubc29\uc0ac\uc131\ub3d9\uc704\uc6d0\uc18c \uad6c\ub9e4", "ppl": "N/A", "qty": "1", "unit": "EA", "price": "10,000,000", "amount": "10,000,000"}], "rental": [{"cat": "", "spec": "", "qty": "", "period": "", "unit": "", "price": "0", "amount": "0"}, {"cat": "", "spec": "", "qty": "", "period": "", "unit": "", "price": "0", "amount": "0"}, {"cat": "", "spec": "", "qty": "", "period": "", "unit": "", "price": "0", "amount": "0"}], "outsource": [{"cat": "\ucf00\uc774\uc5d4\ub514\uc774", "work": "\ubc29\uc0ac\uc120\ud22c\uacfc\uac80\uc0ac", "count": "0", "price": "15,000", "amount": "0"}, {"cat": "", "work": "", "count": "0", "price": "0", "amount": "0"}, {"cat": "", "work": "", "count": "0", "price": "0", "amount": "0"}], "depreciation": [{"item": "PAUT \uc7a5\ube44", "spec": "", "life": "5", "qty": "1", "days": "0", "rate": "44,444", "amount": "0"}, {"item": "PAUT SCANNER (MANUAL)", "spec": "", "life": "5", "qty": "1", "days": "0", "rate": "5,556", "amount": "0"}, {"item": "PAUT SCANNER (COBRA)", "spec": "", "life": "5", "qty": "1", "days": "0", "rate": "16,667", "amount": "0"}, {"item": "YOKE", "spec": "", "life": "5", "qty": "1", "days": "0", "rate": "222", "amount": "0"}, {"item": "\ud604\uc0c1\uc6a9 \ud0d1\ucc28(5\ub144\uac04 \ubcf4\ud5d8\ube44 \ud3ec\ud568)", "spec": "", "life": "5", "qty": "0", "days": "0", "rate": "16,667", "amount": "0"}, {"item": "\uc2a4\ud0c0\ub809\uc2a4(5\ub144\uac04 \ubcf4\ud5d8\ube44 \ud3ec\ud568)", "spec": "", "life": "5", "qty": "1", "days": "0", "rate": "16,667", "amount": "0"}]}</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>55250000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차장</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>47670000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>과장</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>41170000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대리</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>37920000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>계장</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>34670000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>주임</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>31420000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>기사</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>29250000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PT 약품</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>세척액</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PT 약품</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>침투액</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PT 약품</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>현상액</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MT 약품</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>자분페인트</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MT 약품</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>흑색자분</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>방사선투과검사 필름</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MX125</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>글리세린</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>통</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>필름 현상액</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3L</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>통</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>필름 정착액</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3L</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>통</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>수적방지액</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>200mL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>통</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>차량유지비</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>주유, 수리, 통행, 주차 등</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>소모품비</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>장갑,일회용 작업복외</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>복리후생비</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>생수, 음료 외 기타</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Se-175</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>방사성동위원소 구매</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>35714</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Outsource</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>케이엔디이</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>방사선투과검사</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>공수</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>15000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Settings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -51,8 +54,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -21022,7 +21026,7 @@
         <v>0</v>
       </c>
       <c r="S408" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -21914,7 +21918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22033,6 +22037,69 @@
           <t>수량</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B2" t="n">
+        <v>408</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-50</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>K1-PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>부장 주진철, 대리 우명광</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>탑차 81도4028</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>주유</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22106,7 +22173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO1"/>
+  <dimension ref="A1:BO2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22443,6 +22510,179 @@
       <c r="BO1" t="inlineStr">
         <is>
           <t>업체명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>408</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="1" t="n">
+        <v>46134.92020768519</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>R-RAY</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>(주야간) 09:00~24:00</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>26,000</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>대리 우명광</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>(주야간) 09:00~24:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>26,000</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>탑차 81도4028</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>주유</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
         </is>
       </c>
     </row>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Settings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,11 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -56,10 +54,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S426"/>
+  <dimension ref="A1:S427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21344,7 +21341,7 @@
         <v>0</v>
       </c>
       <c r="S415" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416">
@@ -21907,6 +21904,59 @@
         <v>0</v>
       </c>
       <c r="S426" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>428</v>
+      </c>
+      <c r="B427" t="inlineStr"/>
+      <c r="C427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>PAUT SCANNER(MANUAL)</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>PAUT SCANNER(MANUAL)</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr"/>
+      <c r="I427" t="inlineStr"/>
+      <c r="J427" t="inlineStr"/>
+      <c r="K427" t="n">
+        <v>0</v>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M427" t="n">
+        <v>0</v>
+      </c>
+      <c r="N427" t="inlineStr"/>
+      <c r="O427" t="inlineStr"/>
+      <c r="P427" t="inlineStr"/>
+      <c r="Q427" t="n">
+        <v>10</v>
+      </c>
+      <c r="R427" t="n">
+        <v>0</v>
+      </c>
+      <c r="S427" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21921,7 +21971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22043,10 +22093,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46135</v>
+        <v>45757</v>
       </c>
       <c r="B2" t="n">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -22054,36 +22104,36 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>K1 PJT 현장 사용 (자동 차감)</t>
+          <t>K-1 PJT 현장 사용 (자동 차감)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>부장 주진철, 대리 우명광</t>
+          <t>부장 주진철, 부장 주동기</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>K1 PJT</t>
+          <t>K-1 PJT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>탑차 81도4028</t>
+          <t>스타렉스81루5100</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>주유</t>
+          <t>청결</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -22106,10 +22156,10 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46134</v>
+        <v>45758.97540091435</v>
       </c>
       <c r="B3" t="n">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -22117,21 +22167,21 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-25</v>
+        <v>-3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>K1 PJT 현장 사용 (자동 차감)</t>
+          <t>K-1 PJT 현장 사용 (자동 차감)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>부장 주진철, 주임 김진환</t>
+          <t>부장 주진철, 대리 현해룡, 주임 주유철</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>K1 PJT</t>
+          <t>K-1 PJT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -22150,6 +22200,116 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45758.97540091435</v>
+      </c>
+      <c r="B4" t="n">
+        <v>420</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>K-1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>부장 주진철, 대리 현해룡, 주임 주유철</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>K-1 PJT</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>45758</v>
+      </c>
+      <c r="B5" t="n">
+        <v>416</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-500</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>K-1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>부장 주진철, 대리 현해룡, 주임 주유철</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>K-1 PJT</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>자차</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>청결</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22962,28 +23122,28 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46135</v>
+        <v>45757</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>K1 PJT</t>
+          <t>K-1 PJT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" s="1" t="n">
-        <v>46135.60987545139</v>
+        <v>46136.87854770834</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -23007,14 +23167,14 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>R-RAY</t>
+          <t>PAUT 장비-OMNI2-103918</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q4" t="n">
-        <v>25500</v>
+        <v>18500</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -23023,11 +23183,11 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1275000</v>
+        <v>1850000</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>PAUT</t>
         </is>
       </c>
       <c r="V4" t="n">
@@ -23045,7 +23205,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>대리 우명광</t>
+          <t>부장 주동기</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -23108,23 +23268,23 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>탑차 81도4028</t>
+          <t>스타렉스81루5100</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>주유</t>
+          <t>청결</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="inlineStr">
@@ -23143,34 +23303,29 @@
       <c r="BX4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>46134</v>
+      <c r="A5" s="1" t="n">
+        <v>45758</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>K1 PJT</t>
+          <t>K-1 PJT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(메모: [메모] [2026-04-23 15:28:45]
-REJ 업체 청구)</t>
-        </is>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" s="1" t="n">
-        <v>46135.64552198781</v>
+        <v>46136.97540090277</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23192,16 +23347,12 @@
           <t>부장 주진철</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>R-RAY</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="Q5" t="n">
-        <v>25500</v>
+        <v>4300</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -23210,11 +23361,11 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>637500</v>
+        <v>2150000</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="V5" t="n">
@@ -23222,32 +23373,44 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>(주야간) 09:00~23:00</t>
+          <t>(주간) 09:00~21:00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>주임 김진환</t>
+          <t>대리 현해룡</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>(주야간) 09:00~23:00</t>
+          <t>(주간) 09:00~21:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>21,000</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>주임 주유철</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~21:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
@@ -23282,34 +23445,36 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
-      <c r="BG5" t="inlineStr"/>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>탑차 81도4028</t>
+          <t>자차</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>주유</t>
+          <t>청결</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="inlineStr"/>
       <c r="BM5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="inlineStr">

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -21,9 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -54,9 +56,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S427"/>
+  <dimension ref="A1:S429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21957,7 +21960,113 @@
         <v>0</v>
       </c>
       <c r="S427" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>429</v>
+      </c>
+      <c r="B428" t="inlineStr"/>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>PAUT SCANNER(MANUAL)</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>PAUT SCANNER(MANUAL)</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr"/>
+      <c r="I428" t="inlineStr"/>
+      <c r="J428" t="inlineStr"/>
+      <c r="K428" t="n">
+        <v>0</v>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M428" t="n">
+        <v>0</v>
+      </c>
+      <c r="N428" t="inlineStr"/>
+      <c r="O428" t="inlineStr"/>
+      <c r="P428" t="inlineStr"/>
+      <c r="Q428" t="n">
+        <v>10</v>
+      </c>
+      <c r="R428" t="n">
+        <v>0</v>
+      </c>
+      <c r="S428" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>430</v>
+      </c>
+      <c r="B429" t="inlineStr"/>
+      <c r="C429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>PAUT SCANNER(MANUAL)</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>PAUT SCANNER(MANUAL)</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>수정등록</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr"/>
+      <c r="I429" t="inlineStr"/>
+      <c r="J429" t="inlineStr"/>
+      <c r="K429" t="n">
+        <v>0</v>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M429" t="n">
+        <v>0</v>
+      </c>
+      <c r="N429" t="inlineStr"/>
+      <c r="O429" t="inlineStr"/>
+      <c r="P429" t="inlineStr"/>
+      <c r="Q429" t="n">
+        <v>10</v>
+      </c>
+      <c r="R429" t="n">
+        <v>0</v>
+      </c>
+      <c r="S429" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -21971,7 +22080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22093,10 +22202,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45757</v>
+        <v>46137</v>
       </c>
       <c r="B2" t="n">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -22153,163 +22262,6 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>45758.97540091435</v>
-      </c>
-      <c r="B3" t="n">
-        <v>418</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>K-1 PJT 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>부장 주진철, 대리 현해룡, 주임 주유철</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>K-1 PJT</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>45758.97540091435</v>
-      </c>
-      <c r="B4" t="n">
-        <v>420</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>K-1 PJT 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>부장 주진철, 대리 현해룡, 주임 주유철</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>K-1 PJT</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>45758</v>
-      </c>
-      <c r="B5" t="n">
-        <v>416</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>-500</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>K-1 PJT 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>부장 주진철, 대리 현해룡, 주임 주유철</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>K-1 PJT</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>자차</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>청결</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23122,7 +23074,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45757</v>
+        <v>46137</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -23130,20 +23082,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="D4" t="n">
         <v>100</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" s="1" t="n">
-        <v>46136.87854770834</v>
+        <v>46137.92250703704</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -23167,14 +23119,14 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PAUT 장비-OMNI2-103918</t>
+          <t>R-RAY</t>
         </is>
       </c>
       <c r="P4" t="n">
         <v>100</v>
       </c>
       <c r="Q4" t="n">
-        <v>18500</v>
+        <v>25500</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -23183,11 +23135,11 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1850000</v>
+        <v>2550000</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>PAUT</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="V4" t="n">
@@ -23195,12 +23147,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>(주야간) 09:00~24:00</t>
+          <t>(휴일) 09:00~24:00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>112,500</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -23210,12 +23162,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>(주야간) 09:00~24:00</t>
+          <t>(휴일) 09:00~24:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>112,500</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -23284,7 +23236,7 @@
       <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="inlineStr">
@@ -23303,23 +23255,25 @@
       <c r="BX4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>45758</v>
+      <c r="A5" s="2" t="n">
+        <v>46120</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>K-1 PJT</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>416</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PAUT SCANNER(MANUAL)</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" s="1" t="n">
-        <v>46136.97540090277</v>
+        <v>46138.00012854956</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -23347,12 +23301,16 @@
           <t>부장 주진철</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>PAUT 장비-OMNI2-103918</t>
+        </is>
+      </c>
       <c r="P5" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="Q5" t="n">
-        <v>4300</v>
+        <v>18500</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -23361,11 +23319,11 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2150000</v>
+        <v>1850000</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PAUT</t>
         </is>
       </c>
       <c r="V5" t="n">
@@ -23373,44 +23331,32 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>(주간) 09:00~21:00</t>
+          <t>(주야간) 09:00~24:00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>대리 현해룡</t>
+          <t>부장 주동기</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>(주간) 09:00~21:00</t>
+          <t>(주야간) 09:00~24:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>12,000</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>주임 주유철</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>(주간) 09:00~21:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>12,000</t>
-        </is>
-      </c>
+          <t>26,000</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
@@ -23445,25 +23391,23 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>자차</t>
+          <t>스타렉스81루5100</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Settings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,11 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -56,10 +54,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S429"/>
+  <dimension ref="A1:S430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22067,6 +22064,59 @@
       </c>
       <c r="S429" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>431</v>
+      </c>
+      <c r="B430" t="inlineStr"/>
+      <c r="C430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>PAUT SCANNER(MANUAL)</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>PAUT SCANNER(MANUAL)</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>수정등록</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr"/>
+      <c r="I430" t="inlineStr"/>
+      <c r="J430" t="inlineStr"/>
+      <c r="K430" t="n">
+        <v>0</v>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M430" t="n">
+        <v>0</v>
+      </c>
+      <c r="N430" t="inlineStr"/>
+      <c r="O430" t="inlineStr"/>
+      <c r="P430" t="inlineStr"/>
+      <c r="Q430" t="n">
+        <v>10</v>
+      </c>
+      <c r="R430" t="n">
+        <v>0</v>
+      </c>
+      <c r="S430" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -22335,7 +22385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX5"/>
+  <dimension ref="A1:BX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23255,7 +23305,7 @@
       <c r="BX4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -23263,17 +23313,13 @@
           <t>K-1 PJT</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>PAUT SCANNER(MANUAL)</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
         <v>100</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" s="1" t="n">
-        <v>46138.00012854956</v>
+        <v>46138.00012855324</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -23399,7 +23445,9 @@
       <c r="BF5" t="n">
         <v>0</v>
       </c>
-      <c r="BG5" t="inlineStr"/>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
       <c r="BH5" t="inlineStr">
         <is>
           <t>스타렉스81루5100</t>
@@ -23435,6 +23483,188 @@
       <c r="BV5" t="inlineStr"/>
       <c r="BW5" t="inlineStr"/>
       <c r="BX5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>K-1 PJT</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>431</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="1" t="n">
+        <v>46138.46185664352</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>PAUT 장비-OMNI2-103918</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>PAUT</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>(휴일) 09:00~24:00</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>112,500</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>부장 주동기</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:00~18:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>112,500</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>스타렉스81루5100</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>청결</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -22130,7 +22130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22252,10 +22252,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46137</v>
+        <v>46139</v>
       </c>
       <c r="B2" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -22263,36 +22263,36 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>K-1 PJT 현장 사용 (자동 차감)</t>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>부장 주진철, 부장 주동기</t>
+          <t>부장 주진철, 과장 유상훈, 계장 장승대</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>K-1 PJT</t>
+          <t>K1 PJT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>스타렉스81루5100</t>
+          <t>스타렉스 0200</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>청결</t>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -22312,6 +22312,69 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B3" t="n">
+        <v>406</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-50</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>부장 주진철, 과장 유상훈, 계장 장승대</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>스타렉스 5100</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22385,7 +22448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX6"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22767,6 +22830,26 @@
       <c r="BX1" t="inlineStr">
         <is>
           <t>RTK_RTK총계</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>검사품명</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>적용코드</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>성적서번호</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>검사자</t>
         </is>
       </c>
     </row>
@@ -22945,6 +23028,10 @@
       <c r="BX2" t="n">
         <v>0</v>
       </c>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -23121,34 +23208,38 @@
       <c r="BX3" t="n">
         <v>0</v>
       </c>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46137</v>
+        <v>46139</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>K-1 PJT</t>
+          <t>K1 PJT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="D4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" s="1" t="n">
-        <v>46137.92250703704</v>
+        <v>46139.51755924769</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -23173,10 +23264,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q4" t="n">
-        <v>25500</v>
+        <v>25000</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -23185,7 +23276,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2550000</v>
+        <v>1250000</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -23197,32 +23288,44 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>(휴일) 09:00~24:00</t>
+          <t>(주야간) 09:00~24:00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>112,500</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>부장 주동기</t>
+          <t>과장 유상훈</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>(휴일) 09:00~24:00</t>
+          <t>(주야간) 09:00~24:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>112,500</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+          <t>26,000</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>계장 장승대</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>(주야간) 09:00~24:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>26,000</t>
+        </is>
+      </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
@@ -23270,17 +23373,13 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>스타렉스81루5100</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>스타렉스 0200</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>청결</t>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr"/>
@@ -23303,32 +23402,46 @@
       <c r="BV4" t="inlineStr"/>
       <c r="BW4" t="inlineStr"/>
       <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46120</v>
+        <v>46139</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>K-1 PJT</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>406</v>
+      </c>
       <c r="D5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" s="1" t="n">
-        <v>46138.00012855324</v>
+        <v>46139.51798733796</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -23349,14 +23462,14 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PAUT 장비-OMNI2-103918</t>
+          <t>R-RAY</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q5" t="n">
-        <v>18500</v>
+        <v>25000</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -23365,42 +23478,30 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1850000</v>
+        <v>1250000</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>PAUT</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>(주야간) 09:00~24:00</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>26,000</t>
-        </is>
-      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>부장 주동기</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>(주야간) 09:00~24:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>26,000</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+          <t>과장 유상훈</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>계장 장승대</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
@@ -23450,23 +23551,19 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>스타렉스81루5100</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>스타렉스 5100</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>청결</t>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="inlineStr"/>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="inlineStr">
@@ -23483,188 +23580,18 @@
       <c r="BV5" t="inlineStr"/>
       <c r="BW5" t="inlineStr"/>
       <c r="BX5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46138</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>K-1 PJT</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>431</v>
-      </c>
-      <c r="D6" t="n">
-        <v>100</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" s="1" t="n">
-        <v>46138.46185664352</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>PAUT 장비-OMNI2-103918</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>PAUT</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>(휴일) 09:00~24:00</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>112,500</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>부장 주동기</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:00~18:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>112,500</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>스타렉스81루5100</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>청결</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
-      <c r="BW6" t="inlineStr"/>
-      <c r="BX6" t="inlineStr"/>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Settings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,11 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -56,10 +54,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -22134,10 +22131,26 @@
           <t>K1 PJT</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>탑차 81도4028</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>주유</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -23143,7 +23156,7 @@
       <c r="BX4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -23164,7 +23177,7 @@
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46135.64552198781</v>
+        <v>46135.64552199074</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -23290,7 +23303,9 @@
       <c r="BF5" t="n">
         <v>0</v>
       </c>
-      <c r="BG5" t="inlineStr"/>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
       <c r="BH5" t="inlineStr">
         <is>
           <t>탑차 81도4028</t>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S430"/>
+  <dimension ref="A1:T433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,11 @@
       <c r="S1" t="inlineStr">
         <is>
           <t>Active</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>상태</t>
         </is>
       </c>
     </row>
@@ -574,6 +579,7 @@
       <c r="S2" t="n">
         <v>1</v>
       </c>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -627,6 +633,7 @@
       <c r="S3" t="n">
         <v>1</v>
       </c>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -680,6 +687,7 @@
       <c r="S4" t="n">
         <v>1</v>
       </c>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -733,6 +741,7 @@
       <c r="S5" t="n">
         <v>1</v>
       </c>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -786,6 +795,7 @@
       <c r="S6" t="n">
         <v>1</v>
       </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -839,6 +849,7 @@
       <c r="S7" t="n">
         <v>1</v>
       </c>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -892,6 +903,7 @@
       <c r="S8" t="n">
         <v>1</v>
       </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -945,6 +957,7 @@
       <c r="S9" t="n">
         <v>1</v>
       </c>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -998,6 +1011,7 @@
       <c r="S10" t="n">
         <v>1</v>
       </c>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1051,6 +1065,7 @@
       <c r="S11" t="n">
         <v>1</v>
       </c>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1104,6 +1119,7 @@
       <c r="S12" t="n">
         <v>1</v>
       </c>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1157,6 +1173,7 @@
       <c r="S13" t="n">
         <v>1</v>
       </c>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1210,6 +1227,7 @@
       <c r="S14" t="n">
         <v>1</v>
       </c>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1263,6 +1281,7 @@
       <c r="S15" t="n">
         <v>1</v>
       </c>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1316,6 +1335,7 @@
       <c r="S16" t="n">
         <v>1</v>
       </c>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1369,6 +1389,7 @@
       <c r="S17" t="n">
         <v>1</v>
       </c>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1422,6 +1443,7 @@
       <c r="S18" t="n">
         <v>1</v>
       </c>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1475,6 +1497,7 @@
       <c r="S19" t="n">
         <v>1</v>
       </c>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1528,6 +1551,7 @@
       <c r="S20" t="n">
         <v>1</v>
       </c>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1581,6 +1605,7 @@
       <c r="S21" t="n">
         <v>1</v>
       </c>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1634,6 +1659,7 @@
       <c r="S22" t="n">
         <v>1</v>
       </c>
+      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1687,6 +1713,7 @@
       <c r="S23" t="n">
         <v>1</v>
       </c>
+      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1740,6 +1767,7 @@
       <c r="S24" t="n">
         <v>1</v>
       </c>
+      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1793,6 +1821,7 @@
       <c r="S25" t="n">
         <v>1</v>
       </c>
+      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1846,6 +1875,7 @@
       <c r="S26" t="n">
         <v>1</v>
       </c>
+      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1899,6 +1929,7 @@
       <c r="S27" t="n">
         <v>1</v>
       </c>
+      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1952,6 +1983,7 @@
       <c r="S28" t="n">
         <v>1</v>
       </c>
+      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2005,6 +2037,7 @@
       <c r="S29" t="n">
         <v>1</v>
       </c>
+      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2058,6 +2091,7 @@
       <c r="S30" t="n">
         <v>1</v>
       </c>
+      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2111,6 +2145,7 @@
       <c r="S31" t="n">
         <v>1</v>
       </c>
+      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2164,6 +2199,7 @@
       <c r="S32" t="n">
         <v>1</v>
       </c>
+      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2217,6 +2253,7 @@
       <c r="S33" t="n">
         <v>1</v>
       </c>
+      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2270,6 +2307,7 @@
       <c r="S34" t="n">
         <v>1</v>
       </c>
+      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2323,6 +2361,7 @@
       <c r="S35" t="n">
         <v>1</v>
       </c>
+      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2376,6 +2415,7 @@
       <c r="S36" t="n">
         <v>1</v>
       </c>
+      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2429,6 +2469,7 @@
       <c r="S37" t="n">
         <v>1</v>
       </c>
+      <c r="T37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2482,6 +2523,7 @@
       <c r="S38" t="n">
         <v>1</v>
       </c>
+      <c r="T38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2535,6 +2577,7 @@
       <c r="S39" t="n">
         <v>1</v>
       </c>
+      <c r="T39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2588,6 +2631,7 @@
       <c r="S40" t="n">
         <v>1</v>
       </c>
+      <c r="T40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2641,6 +2685,7 @@
       <c r="S41" t="n">
         <v>1</v>
       </c>
+      <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2694,6 +2739,7 @@
       <c r="S42" t="n">
         <v>1</v>
       </c>
+      <c r="T42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2747,6 +2793,7 @@
       <c r="S43" t="n">
         <v>1</v>
       </c>
+      <c r="T43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2800,6 +2847,7 @@
       <c r="S44" t="n">
         <v>1</v>
       </c>
+      <c r="T44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2853,6 +2901,7 @@
       <c r="S45" t="n">
         <v>1</v>
       </c>
+      <c r="T45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2906,6 +2955,7 @@
       <c r="S46" t="n">
         <v>1</v>
       </c>
+      <c r="T46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2959,6 +3009,7 @@
       <c r="S47" t="n">
         <v>1</v>
       </c>
+      <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3008,6 +3059,7 @@
       <c r="S48" t="n">
         <v>1</v>
       </c>
+      <c r="T48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3057,6 +3109,7 @@
       <c r="S49" t="n">
         <v>1</v>
       </c>
+      <c r="T49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3106,6 +3159,7 @@
       <c r="S50" t="n">
         <v>1</v>
       </c>
+      <c r="T50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3155,6 +3209,7 @@
       <c r="S51" t="n">
         <v>1</v>
       </c>
+      <c r="T51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3204,6 +3259,7 @@
       <c r="S52" t="n">
         <v>1</v>
       </c>
+      <c r="T52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3257,6 +3313,7 @@
       <c r="S53" t="n">
         <v>1</v>
       </c>
+      <c r="T53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3310,6 +3367,7 @@
       <c r="S54" t="n">
         <v>1</v>
       </c>
+      <c r="T54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3363,6 +3421,7 @@
       <c r="S55" t="n">
         <v>1</v>
       </c>
+      <c r="T55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3416,6 +3475,7 @@
       <c r="S56" t="n">
         <v>1</v>
       </c>
+      <c r="T56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3469,6 +3529,7 @@
       <c r="S57" t="n">
         <v>1</v>
       </c>
+      <c r="T57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3522,6 +3583,7 @@
       <c r="S58" t="n">
         <v>1</v>
       </c>
+      <c r="T58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3575,6 +3637,7 @@
       <c r="S59" t="n">
         <v>1</v>
       </c>
+      <c r="T59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3628,6 +3691,7 @@
       <c r="S60" t="n">
         <v>1</v>
       </c>
+      <c r="T60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3681,6 +3745,7 @@
       <c r="S61" t="n">
         <v>1</v>
       </c>
+      <c r="T61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3734,6 +3799,7 @@
       <c r="S62" t="n">
         <v>1</v>
       </c>
+      <c r="T62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3787,6 +3853,7 @@
       <c r="S63" t="n">
         <v>1</v>
       </c>
+      <c r="T63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3840,6 +3907,7 @@
       <c r="S64" t="n">
         <v>1</v>
       </c>
+      <c r="T64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3893,6 +3961,7 @@
       <c r="S65" t="n">
         <v>1</v>
       </c>
+      <c r="T65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3946,6 +4015,7 @@
       <c r="S66" t="n">
         <v>1</v>
       </c>
+      <c r="T66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3995,6 +4065,7 @@
       <c r="S67" t="n">
         <v>1</v>
       </c>
+      <c r="T67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4044,6 +4115,7 @@
       <c r="S68" t="n">
         <v>1</v>
       </c>
+      <c r="T68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4097,6 +4169,7 @@
       <c r="S69" t="n">
         <v>1</v>
       </c>
+      <c r="T69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4150,6 +4223,7 @@
       <c r="S70" t="n">
         <v>1</v>
       </c>
+      <c r="T70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4203,6 +4277,7 @@
       <c r="S71" t="n">
         <v>1</v>
       </c>
+      <c r="T71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4256,6 +4331,7 @@
       <c r="S72" t="n">
         <v>1</v>
       </c>
+      <c r="T72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4309,6 +4385,7 @@
       <c r="S73" t="n">
         <v>1</v>
       </c>
+      <c r="T73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4362,6 +4439,7 @@
       <c r="S74" t="n">
         <v>1</v>
       </c>
+      <c r="T74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4415,6 +4493,7 @@
       <c r="S75" t="n">
         <v>1</v>
       </c>
+      <c r="T75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4468,6 +4547,7 @@
       <c r="S76" t="n">
         <v>1</v>
       </c>
+      <c r="T76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4517,6 +4597,7 @@
       <c r="S77" t="n">
         <v>1</v>
       </c>
+      <c r="T77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4570,6 +4651,7 @@
       <c r="S78" t="n">
         <v>1</v>
       </c>
+      <c r="T78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4623,6 +4705,7 @@
       <c r="S79" t="n">
         <v>1</v>
       </c>
+      <c r="T79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4676,6 +4759,7 @@
       <c r="S80" t="n">
         <v>1</v>
       </c>
+      <c r="T80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4729,6 +4813,7 @@
       <c r="S81" t="n">
         <v>1</v>
       </c>
+      <c r="T81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4782,6 +4867,7 @@
       <c r="S82" t="n">
         <v>1</v>
       </c>
+      <c r="T82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4835,6 +4921,7 @@
       <c r="S83" t="n">
         <v>1</v>
       </c>
+      <c r="T83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4888,6 +4975,7 @@
       <c r="S84" t="n">
         <v>1</v>
       </c>
+      <c r="T84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4941,6 +5029,7 @@
       <c r="S85" t="n">
         <v>1</v>
       </c>
+      <c r="T85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4990,6 +5079,7 @@
       <c r="S86" t="n">
         <v>1</v>
       </c>
+      <c r="T86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5039,6 +5129,7 @@
       <c r="S87" t="n">
         <v>1</v>
       </c>
+      <c r="T87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5092,6 +5183,7 @@
       <c r="S88" t="n">
         <v>1</v>
       </c>
+      <c r="T88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5145,6 +5237,7 @@
       <c r="S89" t="n">
         <v>1</v>
       </c>
+      <c r="T89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5198,6 +5291,7 @@
       <c r="S90" t="n">
         <v>1</v>
       </c>
+      <c r="T90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5251,6 +5345,7 @@
       <c r="S91" t="n">
         <v>1</v>
       </c>
+      <c r="T91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5300,6 +5395,7 @@
       <c r="S92" t="n">
         <v>1</v>
       </c>
+      <c r="T92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5353,6 +5449,7 @@
       <c r="S93" t="n">
         <v>1</v>
       </c>
+      <c r="T93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5402,6 +5499,7 @@
       <c r="S94" t="n">
         <v>1</v>
       </c>
+      <c r="T94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5455,6 +5553,7 @@
       <c r="S95" t="n">
         <v>1</v>
       </c>
+      <c r="T95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5508,6 +5607,7 @@
       <c r="S96" t="n">
         <v>1</v>
       </c>
+      <c r="T96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5553,6 +5653,7 @@
       <c r="S97" t="n">
         <v>1</v>
       </c>
+      <c r="T97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5598,6 +5699,7 @@
       <c r="S98" t="n">
         <v>1</v>
       </c>
+      <c r="T98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -5643,6 +5745,7 @@
       <c r="S99" t="n">
         <v>1</v>
       </c>
+      <c r="T99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -5688,6 +5791,7 @@
       <c r="S100" t="n">
         <v>1</v>
       </c>
+      <c r="T100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -5733,6 +5837,7 @@
       <c r="S101" t="n">
         <v>1</v>
       </c>
+      <c r="T101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -5778,6 +5883,7 @@
       <c r="S102" t="n">
         <v>1</v>
       </c>
+      <c r="T102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -5823,6 +5929,7 @@
       <c r="S103" t="n">
         <v>1</v>
       </c>
+      <c r="T103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5868,6 +5975,7 @@
       <c r="S104" t="n">
         <v>1</v>
       </c>
+      <c r="T104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5913,6 +6021,7 @@
       <c r="S105" t="n">
         <v>1</v>
       </c>
+      <c r="T105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5958,6 +6067,7 @@
       <c r="S106" t="n">
         <v>1</v>
       </c>
+      <c r="T106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6003,6 +6113,7 @@
       <c r="S107" t="n">
         <v>1</v>
       </c>
+      <c r="T107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6048,6 +6159,7 @@
       <c r="S108" t="n">
         <v>1</v>
       </c>
+      <c r="T108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6093,6 +6205,7 @@
       <c r="S109" t="n">
         <v>1</v>
       </c>
+      <c r="T109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6138,6 +6251,7 @@
       <c r="S110" t="n">
         <v>1</v>
       </c>
+      <c r="T110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6183,6 +6297,7 @@
       <c r="S111" t="n">
         <v>1</v>
       </c>
+      <c r="T111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6228,6 +6343,7 @@
       <c r="S112" t="n">
         <v>1</v>
       </c>
+      <c r="T112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6273,6 +6389,7 @@
       <c r="S113" t="n">
         <v>1</v>
       </c>
+      <c r="T113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -6318,6 +6435,7 @@
       <c r="S114" t="n">
         <v>1</v>
       </c>
+      <c r="T114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -6363,6 +6481,7 @@
       <c r="S115" t="n">
         <v>1</v>
       </c>
+      <c r="T115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -6408,6 +6527,7 @@
       <c r="S116" t="n">
         <v>1</v>
       </c>
+      <c r="T116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -6453,6 +6573,7 @@
       <c r="S117" t="n">
         <v>1</v>
       </c>
+      <c r="T117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -6498,6 +6619,7 @@
       <c r="S118" t="n">
         <v>1</v>
       </c>
+      <c r="T118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -6543,6 +6665,7 @@
       <c r="S119" t="n">
         <v>1</v>
       </c>
+      <c r="T119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -6588,6 +6711,7 @@
       <c r="S120" t="n">
         <v>1</v>
       </c>
+      <c r="T120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -6633,6 +6757,7 @@
       <c r="S121" t="n">
         <v>1</v>
       </c>
+      <c r="T121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -6678,6 +6803,7 @@
       <c r="S122" t="n">
         <v>1</v>
       </c>
+      <c r="T122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -6723,6 +6849,7 @@
       <c r="S123" t="n">
         <v>1</v>
       </c>
+      <c r="T123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -6768,6 +6895,7 @@
       <c r="S124" t="n">
         <v>1</v>
       </c>
+      <c r="T124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -6813,6 +6941,7 @@
       <c r="S125" t="n">
         <v>1</v>
       </c>
+      <c r="T125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -6858,6 +6987,7 @@
       <c r="S126" t="n">
         <v>1</v>
       </c>
+      <c r="T126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -6903,6 +7033,7 @@
       <c r="S127" t="n">
         <v>1</v>
       </c>
+      <c r="T127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -6948,6 +7079,7 @@
       <c r="S128" t="n">
         <v>1</v>
       </c>
+      <c r="T128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -6993,6 +7125,7 @@
       <c r="S129" t="n">
         <v>1</v>
       </c>
+      <c r="T129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7038,6 +7171,7 @@
       <c r="S130" t="n">
         <v>1</v>
       </c>
+      <c r="T130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7083,6 +7217,7 @@
       <c r="S131" t="n">
         <v>1</v>
       </c>
+      <c r="T131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7128,6 +7263,7 @@
       <c r="S132" t="n">
         <v>1</v>
       </c>
+      <c r="T132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -7173,6 +7309,7 @@
       <c r="S133" t="n">
         <v>1</v>
       </c>
+      <c r="T133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -7218,6 +7355,7 @@
       <c r="S134" t="n">
         <v>1</v>
       </c>
+      <c r="T134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -7263,6 +7401,7 @@
       <c r="S135" t="n">
         <v>1</v>
       </c>
+      <c r="T135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -7308,6 +7447,7 @@
       <c r="S136" t="n">
         <v>1</v>
       </c>
+      <c r="T136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -7353,6 +7493,7 @@
       <c r="S137" t="n">
         <v>1</v>
       </c>
+      <c r="T137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -7398,6 +7539,7 @@
       <c r="S138" t="n">
         <v>1</v>
       </c>
+      <c r="T138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -7443,6 +7585,7 @@
       <c r="S139" t="n">
         <v>1</v>
       </c>
+      <c r="T139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -7488,6 +7631,7 @@
       <c r="S140" t="n">
         <v>1</v>
       </c>
+      <c r="T140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -7533,6 +7677,7 @@
       <c r="S141" t="n">
         <v>1</v>
       </c>
+      <c r="T141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -7578,6 +7723,7 @@
       <c r="S142" t="n">
         <v>1</v>
       </c>
+      <c r="T142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -7623,6 +7769,7 @@
       <c r="S143" t="n">
         <v>1</v>
       </c>
+      <c r="T143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -7668,6 +7815,7 @@
       <c r="S144" t="n">
         <v>1</v>
       </c>
+      <c r="T144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -7713,6 +7861,7 @@
       <c r="S145" t="n">
         <v>1</v>
       </c>
+      <c r="T145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -7758,6 +7907,7 @@
       <c r="S146" t="n">
         <v>1</v>
       </c>
+      <c r="T146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -7803,6 +7953,7 @@
       <c r="S147" t="n">
         <v>1</v>
       </c>
+      <c r="T147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -7848,6 +7999,7 @@
       <c r="S148" t="n">
         <v>1</v>
       </c>
+      <c r="T148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -7893,6 +8045,7 @@
       <c r="S149" t="n">
         <v>1</v>
       </c>
+      <c r="T149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -7938,6 +8091,7 @@
       <c r="S150" t="n">
         <v>1</v>
       </c>
+      <c r="T150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -7983,6 +8137,7 @@
       <c r="S151" t="n">
         <v>1</v>
       </c>
+      <c r="T151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -8028,6 +8183,7 @@
       <c r="S152" t="n">
         <v>1</v>
       </c>
+      <c r="T152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -8073,6 +8229,7 @@
       <c r="S153" t="n">
         <v>1</v>
       </c>
+      <c r="T153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -8118,6 +8275,7 @@
       <c r="S154" t="n">
         <v>1</v>
       </c>
+      <c r="T154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -8163,6 +8321,7 @@
       <c r="S155" t="n">
         <v>1</v>
       </c>
+      <c r="T155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -8208,6 +8367,7 @@
       <c r="S156" t="n">
         <v>1</v>
       </c>
+      <c r="T156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -8253,6 +8413,7 @@
       <c r="S157" t="n">
         <v>1</v>
       </c>
+      <c r="T157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -8298,6 +8459,7 @@
       <c r="S158" t="n">
         <v>1</v>
       </c>
+      <c r="T158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -8343,6 +8505,7 @@
       <c r="S159" t="n">
         <v>1</v>
       </c>
+      <c r="T159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -8388,6 +8551,7 @@
       <c r="S160" t="n">
         <v>1</v>
       </c>
+      <c r="T160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -8433,6 +8597,7 @@
       <c r="S161" t="n">
         <v>1</v>
       </c>
+      <c r="T161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -8478,6 +8643,7 @@
       <c r="S162" t="n">
         <v>1</v>
       </c>
+      <c r="T162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -8523,6 +8689,7 @@
       <c r="S163" t="n">
         <v>1</v>
       </c>
+      <c r="T163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -8568,6 +8735,7 @@
       <c r="S164" t="n">
         <v>1</v>
       </c>
+      <c r="T164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -8613,6 +8781,7 @@
       <c r="S165" t="n">
         <v>1</v>
       </c>
+      <c r="T165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -8658,6 +8827,7 @@
       <c r="S166" t="n">
         <v>1</v>
       </c>
+      <c r="T166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -8703,6 +8873,7 @@
       <c r="S167" t="n">
         <v>1</v>
       </c>
+      <c r="T167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -8748,6 +8919,7 @@
       <c r="S168" t="n">
         <v>1</v>
       </c>
+      <c r="T168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -8793,6 +8965,7 @@
       <c r="S169" t="n">
         <v>1</v>
       </c>
+      <c r="T169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -8838,6 +9011,7 @@
       <c r="S170" t="n">
         <v>1</v>
       </c>
+      <c r="T170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -8883,6 +9057,7 @@
       <c r="S171" t="n">
         <v>1</v>
       </c>
+      <c r="T171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -8928,6 +9103,7 @@
       <c r="S172" t="n">
         <v>1</v>
       </c>
+      <c r="T172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -8973,6 +9149,7 @@
       <c r="S173" t="n">
         <v>1</v>
       </c>
+      <c r="T173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -9022,6 +9199,7 @@
       <c r="S174" t="n">
         <v>1</v>
       </c>
+      <c r="T174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -9075,6 +9253,7 @@
       <c r="S175" t="n">
         <v>1</v>
       </c>
+      <c r="T175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -9128,6 +9307,7 @@
       <c r="S176" t="n">
         <v>1</v>
       </c>
+      <c r="T176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -9173,6 +9353,7 @@
       <c r="S177" t="n">
         <v>1</v>
       </c>
+      <c r="T177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -9218,6 +9399,7 @@
       <c r="S178" t="n">
         <v>1</v>
       </c>
+      <c r="T178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -9263,6 +9445,7 @@
       <c r="S179" t="n">
         <v>1</v>
       </c>
+      <c r="T179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -9308,6 +9491,7 @@
       <c r="S180" t="n">
         <v>1</v>
       </c>
+      <c r="T180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -9353,6 +9537,7 @@
       <c r="S181" t="n">
         <v>1</v>
       </c>
+      <c r="T181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -9398,6 +9583,7 @@
       <c r="S182" t="n">
         <v>1</v>
       </c>
+      <c r="T182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -9443,6 +9629,7 @@
       <c r="S183" t="n">
         <v>1</v>
       </c>
+      <c r="T183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -9488,6 +9675,7 @@
       <c r="S184" t="n">
         <v>1</v>
       </c>
+      <c r="T184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -9533,6 +9721,7 @@
       <c r="S185" t="n">
         <v>1</v>
       </c>
+      <c r="T185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -9578,6 +9767,7 @@
       <c r="S186" t="n">
         <v>1</v>
       </c>
+      <c r="T186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -9623,6 +9813,7 @@
       <c r="S187" t="n">
         <v>1</v>
       </c>
+      <c r="T187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -9668,6 +9859,7 @@
       <c r="S188" t="n">
         <v>1</v>
       </c>
+      <c r="T188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -9713,6 +9905,7 @@
       <c r="S189" t="n">
         <v>1</v>
       </c>
+      <c r="T189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -9758,6 +9951,7 @@
       <c r="S190" t="n">
         <v>1</v>
       </c>
+      <c r="T190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -9803,6 +9997,7 @@
       <c r="S191" t="n">
         <v>1</v>
       </c>
+      <c r="T191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -9848,6 +10043,7 @@
       <c r="S192" t="n">
         <v>1</v>
       </c>
+      <c r="T192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -9893,6 +10089,7 @@
       <c r="S193" t="n">
         <v>1</v>
       </c>
+      <c r="T193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -9938,6 +10135,7 @@
       <c r="S194" t="n">
         <v>1</v>
       </c>
+      <c r="T194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -9983,6 +10181,7 @@
       <c r="S195" t="n">
         <v>1</v>
       </c>
+      <c r="T195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -10028,6 +10227,7 @@
       <c r="S196" t="n">
         <v>1</v>
       </c>
+      <c r="T196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -10073,6 +10273,7 @@
       <c r="S197" t="n">
         <v>1</v>
       </c>
+      <c r="T197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -10118,6 +10319,7 @@
       <c r="S198" t="n">
         <v>1</v>
       </c>
+      <c r="T198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -10163,6 +10365,7 @@
       <c r="S199" t="n">
         <v>1</v>
       </c>
+      <c r="T199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -10208,6 +10411,7 @@
       <c r="S200" t="n">
         <v>1</v>
       </c>
+      <c r="T200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -10253,6 +10457,7 @@
       <c r="S201" t="n">
         <v>1</v>
       </c>
+      <c r="T201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -10298,6 +10503,7 @@
       <c r="S202" t="n">
         <v>1</v>
       </c>
+      <c r="T202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -10343,6 +10549,7 @@
       <c r="S203" t="n">
         <v>1</v>
       </c>
+      <c r="T203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -10388,6 +10595,7 @@
       <c r="S204" t="n">
         <v>1</v>
       </c>
+      <c r="T204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -10433,6 +10641,7 @@
       <c r="S205" t="n">
         <v>1</v>
       </c>
+      <c r="T205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -10478,6 +10687,7 @@
       <c r="S206" t="n">
         <v>1</v>
       </c>
+      <c r="T206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -10523,6 +10733,7 @@
       <c r="S207" t="n">
         <v>1</v>
       </c>
+      <c r="T207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -10568,6 +10779,7 @@
       <c r="S208" t="n">
         <v>1</v>
       </c>
+      <c r="T208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -10613,6 +10825,7 @@
       <c r="S209" t="n">
         <v>1</v>
       </c>
+      <c r="T209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -10666,6 +10879,7 @@
       <c r="S210" t="n">
         <v>1</v>
       </c>
+      <c r="T210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -10719,6 +10933,7 @@
       <c r="S211" t="n">
         <v>1</v>
       </c>
+      <c r="T211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -10772,6 +10987,7 @@
       <c r="S212" t="n">
         <v>1</v>
       </c>
+      <c r="T212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -10825,6 +11041,7 @@
       <c r="S213" t="n">
         <v>1</v>
       </c>
+      <c r="T213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -10878,6 +11095,7 @@
       <c r="S214" t="n">
         <v>1</v>
       </c>
+      <c r="T214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -10931,6 +11149,7 @@
       <c r="S215" t="n">
         <v>1</v>
       </c>
+      <c r="T215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -10984,6 +11203,7 @@
       <c r="S216" t="n">
         <v>1</v>
       </c>
+      <c r="T216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -11037,6 +11257,7 @@
       <c r="S217" t="n">
         <v>1</v>
       </c>
+      <c r="T217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -11090,6 +11311,7 @@
       <c r="S218" t="n">
         <v>1</v>
       </c>
+      <c r="T218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -11143,6 +11365,7 @@
       <c r="S219" t="n">
         <v>1</v>
       </c>
+      <c r="T219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -11196,6 +11419,7 @@
       <c r="S220" t="n">
         <v>1</v>
       </c>
+      <c r="T220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -11249,6 +11473,7 @@
       <c r="S221" t="n">
         <v>1</v>
       </c>
+      <c r="T221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -11302,6 +11527,7 @@
       <c r="S222" t="n">
         <v>1</v>
       </c>
+      <c r="T222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -11355,6 +11581,7 @@
       <c r="S223" t="n">
         <v>1</v>
       </c>
+      <c r="T223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -11408,6 +11635,7 @@
       <c r="S224" t="n">
         <v>1</v>
       </c>
+      <c r="T224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -11461,6 +11689,7 @@
       <c r="S225" t="n">
         <v>1</v>
       </c>
+      <c r="T225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -11514,6 +11743,7 @@
       <c r="S226" t="n">
         <v>1</v>
       </c>
+      <c r="T226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -11567,6 +11797,7 @@
       <c r="S227" t="n">
         <v>1</v>
       </c>
+      <c r="T227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -11620,6 +11851,7 @@
       <c r="S228" t="n">
         <v>1</v>
       </c>
+      <c r="T228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -11669,6 +11901,7 @@
       <c r="S229" t="n">
         <v>1</v>
       </c>
+      <c r="T229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -11722,6 +11955,7 @@
       <c r="S230" t="n">
         <v>1</v>
       </c>
+      <c r="T230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -11775,6 +12009,7 @@
       <c r="S231" t="n">
         <v>1</v>
       </c>
+      <c r="T231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -11828,6 +12063,7 @@
       <c r="S232" t="n">
         <v>1</v>
       </c>
+      <c r="T232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -11881,6 +12117,7 @@
       <c r="S233" t="n">
         <v>1</v>
       </c>
+      <c r="T233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -11934,6 +12171,7 @@
       <c r="S234" t="n">
         <v>1</v>
       </c>
+      <c r="T234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -11987,6 +12225,7 @@
       <c r="S235" t="n">
         <v>1</v>
       </c>
+      <c r="T235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -12040,6 +12279,7 @@
       <c r="S236" t="n">
         <v>1</v>
       </c>
+      <c r="T236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -12093,6 +12333,7 @@
       <c r="S237" t="n">
         <v>1</v>
       </c>
+      <c r="T237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -12146,6 +12387,7 @@
       <c r="S238" t="n">
         <v>1</v>
       </c>
+      <c r="T238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -12199,6 +12441,7 @@
       <c r="S239" t="n">
         <v>1</v>
       </c>
+      <c r="T239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -12252,6 +12495,7 @@
       <c r="S240" t="n">
         <v>1</v>
       </c>
+      <c r="T240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -12305,6 +12549,7 @@
       <c r="S241" t="n">
         <v>1</v>
       </c>
+      <c r="T241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -12358,6 +12603,7 @@
       <c r="S242" t="n">
         <v>1</v>
       </c>
+      <c r="T242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -12411,6 +12657,7 @@
       <c r="S243" t="n">
         <v>1</v>
       </c>
+      <c r="T243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -12464,6 +12711,7 @@
       <c r="S244" t="n">
         <v>1</v>
       </c>
+      <c r="T244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -12513,6 +12761,7 @@
       <c r="S245" t="n">
         <v>1</v>
       </c>
+      <c r="T245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -12562,6 +12811,7 @@
       <c r="S246" t="n">
         <v>1</v>
       </c>
+      <c r="T246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -12611,6 +12861,7 @@
       <c r="S247" t="n">
         <v>1</v>
       </c>
+      <c r="T247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -12664,6 +12915,7 @@
       <c r="S248" t="n">
         <v>1</v>
       </c>
+      <c r="T248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -12717,6 +12969,7 @@
       <c r="S249" t="n">
         <v>1</v>
       </c>
+      <c r="T249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -12766,6 +13019,7 @@
       <c r="S250" t="n">
         <v>1</v>
       </c>
+      <c r="T250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -12819,6 +13073,7 @@
       <c r="S251" t="n">
         <v>1</v>
       </c>
+      <c r="T251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -12868,6 +13123,7 @@
       <c r="S252" t="n">
         <v>1</v>
       </c>
+      <c r="T252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -12917,6 +13173,7 @@
       <c r="S253" t="n">
         <v>1</v>
       </c>
+      <c r="T253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -12970,6 +13227,7 @@
       <c r="S254" t="n">
         <v>1</v>
       </c>
+      <c r="T254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -13023,6 +13281,7 @@
       <c r="S255" t="n">
         <v>1</v>
       </c>
+      <c r="T255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -13076,6 +13335,7 @@
       <c r="S256" t="n">
         <v>1</v>
       </c>
+      <c r="T256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -13129,6 +13389,7 @@
       <c r="S257" t="n">
         <v>1</v>
       </c>
+      <c r="T257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -13182,6 +13443,7 @@
       <c r="S258" t="n">
         <v>1</v>
       </c>
+      <c r="T258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -13235,6 +13497,7 @@
       <c r="S259" t="n">
         <v>1</v>
       </c>
+      <c r="T259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -13288,6 +13551,7 @@
       <c r="S260" t="n">
         <v>1</v>
       </c>
+      <c r="T260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -13337,6 +13601,7 @@
       <c r="S261" t="n">
         <v>1</v>
       </c>
+      <c r="T261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -13390,6 +13655,7 @@
       <c r="S262" t="n">
         <v>1</v>
       </c>
+      <c r="T262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -13443,6 +13709,7 @@
       <c r="S263" t="n">
         <v>1</v>
       </c>
+      <c r="T263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -13496,6 +13763,7 @@
       <c r="S264" t="n">
         <v>1</v>
       </c>
+      <c r="T264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -13549,6 +13817,7 @@
       <c r="S265" t="n">
         <v>1</v>
       </c>
+      <c r="T265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -13602,6 +13871,7 @@
       <c r="S266" t="n">
         <v>1</v>
       </c>
+      <c r="T266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -13655,6 +13925,7 @@
       <c r="S267" t="n">
         <v>1</v>
       </c>
+      <c r="T267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -13708,6 +13979,7 @@
       <c r="S268" t="n">
         <v>1</v>
       </c>
+      <c r="T268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -13761,6 +14033,7 @@
       <c r="S269" t="n">
         <v>1</v>
       </c>
+      <c r="T269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -13814,6 +14087,7 @@
       <c r="S270" t="n">
         <v>1</v>
       </c>
+      <c r="T270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -13867,6 +14141,7 @@
       <c r="S271" t="n">
         <v>1</v>
       </c>
+      <c r="T271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -13920,6 +14195,7 @@
       <c r="S272" t="n">
         <v>1</v>
       </c>
+      <c r="T272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -13973,6 +14249,7 @@
       <c r="S273" t="n">
         <v>1</v>
       </c>
+      <c r="T273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -14026,6 +14303,7 @@
       <c r="S274" t="n">
         <v>1</v>
       </c>
+      <c r="T274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -14079,6 +14357,7 @@
       <c r="S275" t="n">
         <v>1</v>
       </c>
+      <c r="T275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -14132,6 +14411,7 @@
       <c r="S276" t="n">
         <v>1</v>
       </c>
+      <c r="T276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -14185,6 +14465,7 @@
       <c r="S277" t="n">
         <v>1</v>
       </c>
+      <c r="T277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -14238,6 +14519,7 @@
       <c r="S278" t="n">
         <v>1</v>
       </c>
+      <c r="T278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -14291,6 +14573,7 @@
       <c r="S279" t="n">
         <v>1</v>
       </c>
+      <c r="T279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -14344,6 +14627,7 @@
       <c r="S280" t="n">
         <v>1</v>
       </c>
+      <c r="T280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -14397,6 +14681,7 @@
       <c r="S281" t="n">
         <v>1</v>
       </c>
+      <c r="T281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -14450,6 +14735,7 @@
       <c r="S282" t="n">
         <v>1</v>
       </c>
+      <c r="T282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -14503,6 +14789,7 @@
       <c r="S283" t="n">
         <v>1</v>
       </c>
+      <c r="T283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -14556,6 +14843,7 @@
       <c r="S284" t="n">
         <v>1</v>
       </c>
+      <c r="T284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -14609,6 +14897,7 @@
       <c r="S285" t="n">
         <v>1</v>
       </c>
+      <c r="T285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -14662,6 +14951,7 @@
       <c r="S286" t="n">
         <v>1</v>
       </c>
+      <c r="T286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -14715,6 +15005,7 @@
       <c r="S287" t="n">
         <v>1</v>
       </c>
+      <c r="T287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -14768,6 +15059,7 @@
       <c r="S288" t="n">
         <v>1</v>
       </c>
+      <c r="T288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -14821,6 +15113,7 @@
       <c r="S289" t="n">
         <v>1</v>
       </c>
+      <c r="T289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -14874,6 +15167,7 @@
       <c r="S290" t="n">
         <v>1</v>
       </c>
+      <c r="T290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -14927,6 +15221,7 @@
       <c r="S291" t="n">
         <v>1</v>
       </c>
+      <c r="T291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -14980,6 +15275,7 @@
       <c r="S292" t="n">
         <v>1</v>
       </c>
+      <c r="T292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -15033,6 +15329,7 @@
       <c r="S293" t="n">
         <v>1</v>
       </c>
+      <c r="T293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -15086,6 +15383,7 @@
       <c r="S294" t="n">
         <v>1</v>
       </c>
+      <c r="T294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -15139,6 +15437,7 @@
       <c r="S295" t="n">
         <v>1</v>
       </c>
+      <c r="T295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -15192,6 +15491,7 @@
       <c r="S296" t="n">
         <v>1</v>
       </c>
+      <c r="T296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -15245,6 +15545,7 @@
       <c r="S297" t="n">
         <v>1</v>
       </c>
+      <c r="T297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -15298,6 +15599,7 @@
       <c r="S298" t="n">
         <v>1</v>
       </c>
+      <c r="T298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -15351,6 +15653,7 @@
       <c r="S299" t="n">
         <v>1</v>
       </c>
+      <c r="T299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -15404,6 +15707,7 @@
       <c r="S300" t="n">
         <v>1</v>
       </c>
+      <c r="T300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -15457,6 +15761,7 @@
       <c r="S301" t="n">
         <v>1</v>
       </c>
+      <c r="T301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -15510,6 +15815,7 @@
       <c r="S302" t="n">
         <v>1</v>
       </c>
+      <c r="T302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -15563,6 +15869,7 @@
       <c r="S303" t="n">
         <v>1</v>
       </c>
+      <c r="T303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -15616,6 +15923,7 @@
       <c r="S304" t="n">
         <v>1</v>
       </c>
+      <c r="T304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -15669,6 +15977,7 @@
       <c r="S305" t="n">
         <v>1</v>
       </c>
+      <c r="T305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -15722,6 +16031,7 @@
       <c r="S306" t="n">
         <v>1</v>
       </c>
+      <c r="T306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -15775,6 +16085,7 @@
       <c r="S307" t="n">
         <v>1</v>
       </c>
+      <c r="T307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -15828,6 +16139,7 @@
       <c r="S308" t="n">
         <v>1</v>
       </c>
+      <c r="T308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -15881,6 +16193,7 @@
       <c r="S309" t="n">
         <v>1</v>
       </c>
+      <c r="T309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -15934,6 +16247,7 @@
       <c r="S310" t="n">
         <v>1</v>
       </c>
+      <c r="T310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -15987,6 +16301,7 @@
       <c r="S311" t="n">
         <v>1</v>
       </c>
+      <c r="T311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -16040,6 +16355,7 @@
       <c r="S312" t="n">
         <v>1</v>
       </c>
+      <c r="T312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -16093,6 +16409,7 @@
       <c r="S313" t="n">
         <v>1</v>
       </c>
+      <c r="T313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -16146,6 +16463,7 @@
       <c r="S314" t="n">
         <v>1</v>
       </c>
+      <c r="T314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -16199,6 +16517,7 @@
       <c r="S315" t="n">
         <v>1</v>
       </c>
+      <c r="T315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -16252,6 +16571,7 @@
       <c r="S316" t="n">
         <v>1</v>
       </c>
+      <c r="T316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -16305,6 +16625,7 @@
       <c r="S317" t="n">
         <v>1</v>
       </c>
+      <c r="T317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -16358,6 +16679,7 @@
       <c r="S318" t="n">
         <v>1</v>
       </c>
+      <c r="T318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -16411,6 +16733,7 @@
       <c r="S319" t="n">
         <v>1</v>
       </c>
+      <c r="T319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -16464,6 +16787,7 @@
       <c r="S320" t="n">
         <v>1</v>
       </c>
+      <c r="T320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -16517,6 +16841,7 @@
       <c r="S321" t="n">
         <v>1</v>
       </c>
+      <c r="T321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -16570,6 +16895,7 @@
       <c r="S322" t="n">
         <v>1</v>
       </c>
+      <c r="T322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -16623,6 +16949,7 @@
       <c r="S323" t="n">
         <v>1</v>
       </c>
+      <c r="T323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -16676,6 +17003,7 @@
       <c r="S324" t="n">
         <v>1</v>
       </c>
+      <c r="T324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -16729,6 +17057,7 @@
       <c r="S325" t="n">
         <v>1</v>
       </c>
+      <c r="T325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -16782,6 +17111,7 @@
       <c r="S326" t="n">
         <v>1</v>
       </c>
+      <c r="T326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -16835,6 +17165,7 @@
       <c r="S327" t="n">
         <v>1</v>
       </c>
+      <c r="T327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -16888,6 +17219,7 @@
       <c r="S328" t="n">
         <v>1</v>
       </c>
+      <c r="T328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -16941,6 +17273,7 @@
       <c r="S329" t="n">
         <v>1</v>
       </c>
+      <c r="T329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -16994,6 +17327,7 @@
       <c r="S330" t="n">
         <v>1</v>
       </c>
+      <c r="T330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -17047,6 +17381,7 @@
       <c r="S331" t="n">
         <v>1</v>
       </c>
+      <c r="T331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -17100,6 +17435,7 @@
       <c r="S332" t="n">
         <v>1</v>
       </c>
+      <c r="T332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -17153,6 +17489,7 @@
       <c r="S333" t="n">
         <v>1</v>
       </c>
+      <c r="T333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -17206,6 +17543,7 @@
       <c r="S334" t="n">
         <v>1</v>
       </c>
+      <c r="T334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -17259,6 +17597,7 @@
       <c r="S335" t="n">
         <v>1</v>
       </c>
+      <c r="T335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -17312,6 +17651,7 @@
       <c r="S336" t="n">
         <v>1</v>
       </c>
+      <c r="T336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -17365,6 +17705,7 @@
       <c r="S337" t="n">
         <v>1</v>
       </c>
+      <c r="T337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -17418,6 +17759,7 @@
       <c r="S338" t="n">
         <v>1</v>
       </c>
+      <c r="T338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -17471,6 +17813,7 @@
       <c r="S339" t="n">
         <v>1</v>
       </c>
+      <c r="T339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -17524,6 +17867,7 @@
       <c r="S340" t="n">
         <v>1</v>
       </c>
+      <c r="T340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -17577,6 +17921,7 @@
       <c r="S341" t="n">
         <v>1</v>
       </c>
+      <c r="T341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -17630,6 +17975,7 @@
       <c r="S342" t="n">
         <v>1</v>
       </c>
+      <c r="T342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -17683,6 +18029,7 @@
       <c r="S343" t="n">
         <v>1</v>
       </c>
+      <c r="T343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -17736,6 +18083,7 @@
       <c r="S344" t="n">
         <v>1</v>
       </c>
+      <c r="T344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -17789,6 +18137,7 @@
       <c r="S345" t="n">
         <v>1</v>
       </c>
+      <c r="T345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -17842,6 +18191,7 @@
       <c r="S346" t="n">
         <v>1</v>
       </c>
+      <c r="T346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -17895,6 +18245,7 @@
       <c r="S347" t="n">
         <v>1</v>
       </c>
+      <c r="T347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -17948,6 +18299,7 @@
       <c r="S348" t="n">
         <v>1</v>
       </c>
+      <c r="T348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -18001,6 +18353,7 @@
       <c r="S349" t="n">
         <v>1</v>
       </c>
+      <c r="T349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -18054,6 +18407,7 @@
       <c r="S350" t="n">
         <v>1</v>
       </c>
+      <c r="T350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -18107,6 +18461,7 @@
       <c r="S351" t="n">
         <v>1</v>
       </c>
+      <c r="T351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -18160,6 +18515,7 @@
       <c r="S352" t="n">
         <v>1</v>
       </c>
+      <c r="T352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -18213,6 +18569,7 @@
       <c r="S353" t="n">
         <v>1</v>
       </c>
+      <c r="T353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -18266,6 +18623,7 @@
       <c r="S354" t="n">
         <v>1</v>
       </c>
+      <c r="T354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -18319,6 +18677,7 @@
       <c r="S355" t="n">
         <v>1</v>
       </c>
+      <c r="T355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -18372,6 +18731,7 @@
       <c r="S356" t="n">
         <v>1</v>
       </c>
+      <c r="T356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -18421,6 +18781,7 @@
       <c r="S357" t="n">
         <v>1</v>
       </c>
+      <c r="T357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -18474,6 +18835,7 @@
       <c r="S358" t="n">
         <v>1</v>
       </c>
+      <c r="T358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -18523,6 +18885,7 @@
       <c r="S359" t="n">
         <v>1</v>
       </c>
+      <c r="T359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -18572,6 +18935,7 @@
       <c r="S360" t="n">
         <v>1</v>
       </c>
+      <c r="T360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -18621,6 +18985,7 @@
       <c r="S361" t="n">
         <v>1</v>
       </c>
+      <c r="T361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -18670,6 +19035,7 @@
       <c r="S362" t="n">
         <v>1</v>
       </c>
+      <c r="T362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -18719,6 +19085,7 @@
       <c r="S363" t="n">
         <v>1</v>
       </c>
+      <c r="T363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -18768,6 +19135,7 @@
       <c r="S364" t="n">
         <v>1</v>
       </c>
+      <c r="T364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -18817,6 +19185,7 @@
       <c r="S365" t="n">
         <v>1</v>
       </c>
+      <c r="T365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -18866,6 +19235,7 @@
       <c r="S366" t="n">
         <v>1</v>
       </c>
+      <c r="T366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -18915,6 +19285,7 @@
       <c r="S367" t="n">
         <v>1</v>
       </c>
+      <c r="T367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -18964,6 +19335,7 @@
       <c r="S368" t="n">
         <v>1</v>
       </c>
+      <c r="T368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -19013,6 +19385,7 @@
       <c r="S369" t="n">
         <v>1</v>
       </c>
+      <c r="T369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -19062,6 +19435,7 @@
       <c r="S370" t="n">
         <v>1</v>
       </c>
+      <c r="T370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -19111,6 +19485,7 @@
       <c r="S371" t="n">
         <v>1</v>
       </c>
+      <c r="T371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -19160,6 +19535,7 @@
       <c r="S372" t="n">
         <v>1</v>
       </c>
+      <c r="T372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -19209,6 +19585,7 @@
       <c r="S373" t="n">
         <v>1</v>
       </c>
+      <c r="T373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -19258,6 +19635,7 @@
       <c r="S374" t="n">
         <v>1</v>
       </c>
+      <c r="T374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -19307,6 +19685,7 @@
       <c r="S375" t="n">
         <v>1</v>
       </c>
+      <c r="T375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -19360,6 +19739,7 @@
       <c r="S376" t="n">
         <v>1</v>
       </c>
+      <c r="T376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -19413,6 +19793,7 @@
       <c r="S377" t="n">
         <v>1</v>
       </c>
+      <c r="T377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -19462,6 +19843,7 @@
       <c r="S378" t="n">
         <v>1</v>
       </c>
+      <c r="T378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -19511,6 +19893,7 @@
       <c r="S379" t="n">
         <v>1</v>
       </c>
+      <c r="T379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -19560,6 +19943,7 @@
       <c r="S380" t="n">
         <v>1</v>
       </c>
+      <c r="T380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -19613,6 +19997,7 @@
       <c r="S381" t="n">
         <v>1</v>
       </c>
+      <c r="T381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -19666,6 +20051,7 @@
       <c r="S382" t="n">
         <v>1</v>
       </c>
+      <c r="T382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -19719,6 +20105,7 @@
       <c r="S383" t="n">
         <v>1</v>
       </c>
+      <c r="T383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -19772,6 +20159,7 @@
       <c r="S384" t="n">
         <v>1</v>
       </c>
+      <c r="T384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -19825,6 +20213,7 @@
       <c r="S385" t="n">
         <v>1</v>
       </c>
+      <c r="T385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -19878,6 +20267,7 @@
       <c r="S386" t="n">
         <v>1</v>
       </c>
+      <c r="T386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -19931,6 +20321,7 @@
       <c r="S387" t="n">
         <v>1</v>
       </c>
+      <c r="T387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -19980,6 +20371,7 @@
       <c r="S388" t="n">
         <v>1</v>
       </c>
+      <c r="T388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -20033,6 +20425,7 @@
       <c r="S389" t="n">
         <v>1</v>
       </c>
+      <c r="T389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -20086,6 +20479,7 @@
       <c r="S390" t="n">
         <v>1</v>
       </c>
+      <c r="T390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -20139,6 +20533,7 @@
       <c r="S391" t="n">
         <v>1</v>
       </c>
+      <c r="T391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -20192,6 +20587,7 @@
       <c r="S392" t="n">
         <v>1</v>
       </c>
+      <c r="T392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -20245,6 +20641,7 @@
       <c r="S393" t="n">
         <v>1</v>
       </c>
+      <c r="T393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -20298,6 +20695,7 @@
       <c r="S394" t="n">
         <v>1</v>
       </c>
+      <c r="T394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -20351,6 +20749,7 @@
       <c r="S395" t="n">
         <v>1</v>
       </c>
+      <c r="T395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -20404,6 +20803,7 @@
       <c r="S396" t="n">
         <v>1</v>
       </c>
+      <c r="T396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -20457,6 +20857,7 @@
       <c r="S397" t="n">
         <v>1</v>
       </c>
+      <c r="T397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -20506,6 +20907,7 @@
       <c r="S398" t="n">
         <v>1</v>
       </c>
+      <c r="T398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -20559,6 +20961,7 @@
       <c r="S399" t="n">
         <v>1</v>
       </c>
+      <c r="T399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -20612,6 +21015,7 @@
       <c r="S400" t="n">
         <v>1</v>
       </c>
+      <c r="T400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -20665,6 +21069,7 @@
       <c r="S401" t="n">
         <v>1</v>
       </c>
+      <c r="T401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -20718,6 +21123,7 @@
       <c r="S402" t="n">
         <v>1</v>
       </c>
+      <c r="T402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -20771,6 +21177,7 @@
       <c r="S403" t="n">
         <v>1</v>
       </c>
+      <c r="T403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -20824,6 +21231,7 @@
       <c r="S404" t="n">
         <v>1</v>
       </c>
+      <c r="T404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -20877,6 +21285,7 @@
       <c r="S405" t="n">
         <v>1</v>
       </c>
+      <c r="T405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -20930,6 +21339,7 @@
       <c r="S406" t="n">
         <v>1</v>
       </c>
+      <c r="T406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -20983,6 +21393,7 @@
       <c r="S407" t="n">
         <v>0</v>
       </c>
+      <c r="T407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -21028,6 +21439,7 @@
       <c r="S408" t="n">
         <v>0</v>
       </c>
+      <c r="T408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -21073,6 +21485,7 @@
       <c r="S409" t="n">
         <v>0</v>
       </c>
+      <c r="T409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -21118,6 +21531,7 @@
       <c r="S410" t="n">
         <v>1</v>
       </c>
+      <c r="T410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -21163,6 +21577,7 @@
       <c r="S411" t="n">
         <v>1</v>
       </c>
+      <c r="T411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -21208,6 +21623,7 @@
       <c r="S412" t="n">
         <v>0</v>
       </c>
+      <c r="T412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -21253,6 +21669,7 @@
       <c r="S413" t="n">
         <v>0</v>
       </c>
+      <c r="T413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -21298,6 +21715,7 @@
       <c r="S414" t="n">
         <v>0</v>
       </c>
+      <c r="T414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -21343,6 +21761,7 @@
       <c r="S415" t="n">
         <v>1</v>
       </c>
+      <c r="T415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -21388,6 +21807,7 @@
       <c r="S416" t="n">
         <v>0</v>
       </c>
+      <c r="T416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -21403,7 +21823,7 @@
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>세척제</t>
+          <t>PT 세척제</t>
         </is>
       </c>
       <c r="G417" t="inlineStr"/>
@@ -21437,6 +21857,7 @@
       <c r="S417" t="n">
         <v>0</v>
       </c>
+      <c r="T417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -21452,7 +21873,7 @@
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>침투제</t>
+          <t>PT 침투제</t>
         </is>
       </c>
       <c r="G418" t="inlineStr"/>
@@ -21486,6 +21907,7 @@
       <c r="S418" t="n">
         <v>0</v>
       </c>
+      <c r="T418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -21501,7 +21923,7 @@
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
-          <t>현상제</t>
+          <t>PT 현상제</t>
         </is>
       </c>
       <c r="G419" t="inlineStr"/>
@@ -21535,6 +21957,7 @@
       <c r="S419" t="n">
         <v>0</v>
       </c>
+      <c r="T419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -21588,6 +22011,7 @@
       <c r="S420" t="n">
         <v>0</v>
       </c>
+      <c r="T420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -21641,6 +22065,7 @@
       <c r="S421" t="n">
         <v>0</v>
       </c>
+      <c r="T421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -21694,6 +22119,7 @@
       <c r="S422" t="n">
         <v>0</v>
       </c>
+      <c r="T422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -21747,6 +22173,7 @@
       <c r="S423" t="n">
         <v>0</v>
       </c>
+      <c r="T423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -21800,6 +22227,7 @@
       <c r="S424" t="n">
         <v>0</v>
       </c>
+      <c r="T424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -21853,6 +22281,7 @@
       <c r="S425" t="n">
         <v>0</v>
       </c>
+      <c r="T425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -21906,6 +22335,7 @@
       <c r="S426" t="n">
         <v>1</v>
       </c>
+      <c r="T426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -21959,6 +22389,7 @@
       <c r="S427" t="n">
         <v>0</v>
       </c>
+      <c r="T427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -22012,6 +22443,7 @@
       <c r="S428" t="n">
         <v>0</v>
       </c>
+      <c r="T428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -22065,6 +22497,7 @@
       <c r="S429" t="n">
         <v>0</v>
       </c>
+      <c r="T429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -22117,6 +22550,169 @@
       </c>
       <c r="S430" t="n">
         <v>1</v>
+      </c>
+      <c r="T430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>433</v>
+      </c>
+      <c r="B431" t="inlineStr"/>
+      <c r="C431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>MT약품</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>MT 흑색자분</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr"/>
+      <c r="I431" t="inlineStr"/>
+      <c r="J431" t="inlineStr"/>
+      <c r="K431" t="n">
+        <v>0</v>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M431" t="n">
+        <v>0</v>
+      </c>
+      <c r="N431" t="inlineStr"/>
+      <c r="O431" t="inlineStr"/>
+      <c r="P431" t="inlineStr"/>
+      <c r="Q431" t="n">
+        <v>10</v>
+      </c>
+      <c r="R431" t="n">
+        <v>0</v>
+      </c>
+      <c r="S431" t="n">
+        <v>1</v>
+      </c>
+      <c r="T431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>434</v>
+      </c>
+      <c r="B432" t="inlineStr"/>
+      <c r="C432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>MT약품</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>MT 백색페인트</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr"/>
+      <c r="I432" t="inlineStr"/>
+      <c r="J432" t="inlineStr"/>
+      <c r="K432" t="n">
+        <v>0</v>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M432" t="n">
+        <v>0</v>
+      </c>
+      <c r="N432" t="inlineStr"/>
+      <c r="O432" t="inlineStr"/>
+      <c r="P432" t="inlineStr"/>
+      <c r="Q432" t="n">
+        <v>10</v>
+      </c>
+      <c r="R432" t="n">
+        <v>0</v>
+      </c>
+      <c r="S432" t="n">
+        <v>1</v>
+      </c>
+      <c r="T432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" t="inlineStr"/>
+      <c r="C433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>MT약품</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr"/>
+      <c r="I433" t="inlineStr"/>
+      <c r="J433" t="inlineStr"/>
+      <c r="K433" t="n">
+        <v>0</v>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M433" t="n">
+        <v>0</v>
+      </c>
+      <c r="N433" t="inlineStr"/>
+      <c r="O433" t="inlineStr"/>
+      <c r="P433" t="inlineStr"/>
+      <c r="Q433" t="n">
+        <v>0</v>
+      </c>
+      <c r="R433" t="n">
+        <v>0</v>
+      </c>
+      <c r="S433" t="n">
+        <v>0</v>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>사용가능</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -22130,7 +22726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22375,6 +22971,100 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46128.89430152778</v>
+      </c>
+      <c r="B4" t="n">
+        <v>433</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>K-1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>부장 주진철, 대리 우명광</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>K-1 PJT</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46128.89430152778</v>
+      </c>
+      <c r="B5" t="n">
+        <v>434</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>K-1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>부장 주진철, 대리 우명광</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>K-1 PJT</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22448,7 +23138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23593,6 +24283,188 @@
       <c r="CA5" t="inlineStr"/>
       <c r="CB5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>K-1 PJT</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>432</v>
+      </c>
+      <c r="D6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="1" t="n">
+        <v>46139.8943015162</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>YOKE AC-NW1301154</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4300</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>215000</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~18:00</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>대리 우명광</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~18:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>스타렉스81루5100</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T433"/>
+  <dimension ref="A1:T438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22707,13 +22707,283 @@
         <v>0</v>
       </c>
       <c r="S433" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T433" t="inlineStr">
         <is>
           <t>사용가능</t>
         </is>
       </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>435</v>
+      </c>
+      <c r="B434" t="inlineStr"/>
+      <c r="C434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr"/>
+      <c r="I434" t="inlineStr"/>
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="n">
+        <v>0</v>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M434" t="n">
+        <v>0</v>
+      </c>
+      <c r="N434" t="inlineStr"/>
+      <c r="O434" t="inlineStr"/>
+      <c r="P434" t="inlineStr"/>
+      <c r="Q434" t="n">
+        <v>10</v>
+      </c>
+      <c r="R434" t="n">
+        <v>0</v>
+      </c>
+      <c r="S434" t="n">
+        <v>1</v>
+      </c>
+      <c r="T434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>436</v>
+      </c>
+      <c r="B435" t="inlineStr"/>
+      <c r="C435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr"/>
+      <c r="I435" t="inlineStr"/>
+      <c r="J435" t="inlineStr"/>
+      <c r="K435" t="n">
+        <v>0</v>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M435" t="n">
+        <v>0</v>
+      </c>
+      <c r="N435" t="inlineStr"/>
+      <c r="O435" t="inlineStr"/>
+      <c r="P435" t="inlineStr"/>
+      <c r="Q435" t="n">
+        <v>10</v>
+      </c>
+      <c r="R435" t="n">
+        <v>0</v>
+      </c>
+      <c r="S435" t="n">
+        <v>1</v>
+      </c>
+      <c r="T435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>437</v>
+      </c>
+      <c r="B436" t="inlineStr"/>
+      <c r="C436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr"/>
+      <c r="I436" t="inlineStr"/>
+      <c r="J436" t="inlineStr"/>
+      <c r="K436" t="n">
+        <v>0</v>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M436" t="n">
+        <v>0</v>
+      </c>
+      <c r="N436" t="inlineStr"/>
+      <c r="O436" t="inlineStr"/>
+      <c r="P436" t="inlineStr"/>
+      <c r="Q436" t="n">
+        <v>10</v>
+      </c>
+      <c r="R436" t="n">
+        <v>0</v>
+      </c>
+      <c r="S436" t="n">
+        <v>1</v>
+      </c>
+      <c r="T436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>438</v>
+      </c>
+      <c r="B437" t="inlineStr"/>
+      <c r="C437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr"/>
+      <c r="I437" t="inlineStr"/>
+      <c r="J437" t="inlineStr"/>
+      <c r="K437" t="n">
+        <v>0</v>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M437" t="n">
+        <v>0</v>
+      </c>
+      <c r="N437" t="inlineStr"/>
+      <c r="O437" t="inlineStr"/>
+      <c r="P437" t="inlineStr"/>
+      <c r="Q437" t="n">
+        <v>10</v>
+      </c>
+      <c r="R437" t="n">
+        <v>0</v>
+      </c>
+      <c r="S437" t="n">
+        <v>1</v>
+      </c>
+      <c r="T437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>439</v>
+      </c>
+      <c r="B438" t="inlineStr"/>
+      <c r="C438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr"/>
+      <c r="I438" t="inlineStr"/>
+      <c r="J438" t="inlineStr"/>
+      <c r="K438" t="n">
+        <v>0</v>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="M438" t="n">
+        <v>0</v>
+      </c>
+      <c r="N438" t="inlineStr"/>
+      <c r="O438" t="inlineStr"/>
+      <c r="P438" t="inlineStr"/>
+      <c r="Q438" t="n">
+        <v>10</v>
+      </c>
+      <c r="R438" t="n">
+        <v>0</v>
+      </c>
+      <c r="S438" t="n">
+        <v>1</v>
+      </c>
+      <c r="T438" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22726,7 +22996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22848,10 +23118,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46139</v>
+        <v>46128.89430152778</v>
       </c>
       <c r="B2" t="n">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -22859,43 +23129,27 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-50</v>
+        <v>-1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>K1 PJT 현장 사용 (자동 차감)</t>
+          <t>K-1 PJT 현장 사용 (자동 차감)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>부장 주진철, 과장 유상훈, 계장 장승대</t>
+          <t>부장 주진철, 대리 우명광</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>K1 PJT</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>스타렉스 0200</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>K-1 PJT</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -22911,10 +23165,10 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46139</v>
+        <v>46128.89430152778</v>
       </c>
       <c r="B3" t="n">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -22922,43 +23176,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-50</v>
+        <v>-1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>K1 PJT 현장 사용 (자동 차감)</t>
+          <t>K-1 PJT 현장 사용 (자동 차감)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>부장 주진철, 과장 유상훈, 계장 장승대</t>
+          <t>부장 주진철, 대리 우명광</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>K1 PJT</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>스타렉스 5100</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>K-1 PJT</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -22971,100 +23209,6 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46128.89430152778</v>
-      </c>
-      <c r="B4" t="n">
-        <v>433</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>K-1 PJT 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>부장 주진철, 대리 우명광</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>K-1 PJT</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46128.89430152778</v>
-      </c>
-      <c r="B5" t="n">
-        <v>434</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>K-1 PJT 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>부장 주진철, 대리 우명광</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>K-1 PJT</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23138,7 +23282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23540,6 +23684,11 @@
       <c r="CB1" t="inlineStr">
         <is>
           <t>검사자</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>Unit</t>
         </is>
       </c>
     </row>
@@ -23722,6 +23871,7 @@
       <c r="BZ2" t="inlineStr"/>
       <c r="CA2" t="inlineStr"/>
       <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -23902,6 +24052,7 @@
       <c r="BZ3" t="inlineStr"/>
       <c r="CA3" t="inlineStr"/>
       <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -24104,6 +24255,11 @@
       </c>
       <c r="CA4" t="inlineStr"/>
       <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -24282,6 +24438,7 @@
       </c>
       <c r="CA5" t="inlineStr"/>
       <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -24464,6 +24621,218 @@
       <c r="BZ6" t="inlineStr"/>
       <c r="CA6" t="inlineStr"/>
       <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>432</v>
+      </c>
+      <c r="D7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" s="1" t="n">
+        <v>46140.92188907407</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>YOKE AC-NW1301154</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4300</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>215000</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>(주야간) 09:00~24:00</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>26,000</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>과장 유상훈</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>(주야간) 09:00~24:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>26,000</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>계장 장승대</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>(주야간) 09:00~24:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>26,000</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>09:00~18:00</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>스타렉스 0200</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>I/D</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Settings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,10 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -54,9 +51,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -21637,7 +21633,11 @@
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr">
         <is>
@@ -21729,7 +21729,11 @@
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr">
         <is>
@@ -21823,7 +21827,7 @@
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>PT 세척제</t>
+          <t>세척제</t>
         </is>
       </c>
       <c r="G417" t="inlineStr"/>
@@ -21873,7 +21877,7 @@
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>PT 침투제</t>
+          <t>침투제</t>
         </is>
       </c>
       <c r="G418" t="inlineStr"/>
@@ -21923,7 +21927,7 @@
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
-          <t>PT 현상제</t>
+          <t>현상제</t>
         </is>
       </c>
       <c r="G419" t="inlineStr"/>
@@ -22549,7 +22553,7 @@
         <v>0</v>
       </c>
       <c r="S430" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T430" t="inlineStr"/>
     </row>
@@ -22571,7 +22575,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>MT 흑색자분</t>
+          <t>흑색자분</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -22625,7 +22629,7 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>MT 백색페인트</t>
+          <t>백색페인트</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
@@ -22677,7 +22681,11 @@
           <t>현장</t>
         </is>
       </c>
-      <c r="F433" t="inlineStr"/>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="G433" t="inlineStr">
         <is>
           <t>자동등록</t>
@@ -22707,7 +22715,7 @@
         <v>0</v>
       </c>
       <c r="S433" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T433" t="inlineStr">
         <is>
@@ -22765,7 +22773,7 @@
         <v>0</v>
       </c>
       <c r="S434" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T434" t="inlineStr"/>
     </row>
@@ -22819,7 +22827,7 @@
         <v>0</v>
       </c>
       <c r="S435" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T435" t="inlineStr"/>
     </row>
@@ -22873,7 +22881,7 @@
         <v>0</v>
       </c>
       <c r="S436" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T436" t="inlineStr"/>
     </row>
@@ -22927,7 +22935,7 @@
         <v>0</v>
       </c>
       <c r="S437" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T437" t="inlineStr"/>
     </row>
@@ -22981,7 +22989,7 @@
         <v>0</v>
       </c>
       <c r="S438" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T438" t="inlineStr"/>
     </row>
@@ -22996,7 +23004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23115,100 +23123,6 @@
           <t>수량</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46128.89430152778</v>
-      </c>
-      <c r="B2" t="n">
-        <v>433</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>K-1 PJT 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>부장 주진철, 대리 우명광</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>K-1 PJT</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46128.89430152778</v>
-      </c>
-      <c r="B3" t="n">
-        <v>434</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>K-1 PJT 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>부장 주진철, 대리 우명광</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>K-1 PJT</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23282,7 +23196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC7"/>
+  <dimension ref="A1:CC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24054,786 +23968,6 @@
       <c r="CB3" t="inlineStr"/>
       <c r="CC3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46139</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>K1 PJT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>405</v>
-      </c>
-      <c r="D4" t="n">
-        <v>50</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" s="1" t="n">
-        <v>46139.51755924769</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>R-RAY</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>25000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1250000</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>(주야간) 09:00~24:00</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>26,000</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>과장 유상훈</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>(주야간) 09:00~24:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>26,000</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>계장 장승대</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>(주야간) 09:00~24:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>26,000</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>스타렉스 0200</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
-      <c r="BW4" t="inlineStr"/>
-      <c r="BX4" t="inlineStr"/>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="inlineStr"/>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46139</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>K1 PJT</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>406</v>
-      </c>
-      <c r="D5" t="n">
-        <v>50</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" s="1" t="n">
-        <v>46139.51798733796</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>R-RAY</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>25000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1250000</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>과장 유상훈</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>계장 장승대</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>스타렉스 5100</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
-      <c r="BW5" t="inlineStr"/>
-      <c r="BX5" t="inlineStr"/>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="inlineStr"/>
-      <c r="CC5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>K-1 PJT</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>432</v>
-      </c>
-      <c r="D6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" s="1" t="n">
-        <v>46139.8943015162</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>YOKE AC-NW1301154</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4300</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>215000</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>MT</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>(주간) 09:00~18:00</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>대리 우명광</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>(주간) 09:00~18:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>스타렉스81루5100</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
-      <c r="BW6" t="inlineStr"/>
-      <c r="BX6" t="inlineStr"/>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr"/>
-      <c r="CA6" t="inlineStr"/>
-      <c r="CB6" t="inlineStr"/>
-      <c r="CC6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46139</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>K1 PJT</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>432</v>
-      </c>
-      <c r="D7" t="n">
-        <v>50</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" s="1" t="n">
-        <v>46140.92188907407</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>YOKE AC-NW1301154</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4300</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>215000</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>MT</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>(주야간) 09:00~24:00</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>26,000</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>과장 유상훈</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>(주야간) 09:00~24:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>26,000</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>계장 장승대</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>(주야간) 09:00~24:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>26,000</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>09:00~18:00</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>스타렉스 0200</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN7" t="inlineStr"/>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr"/>
-      <c r="BR7" t="inlineStr"/>
-      <c r="BS7" t="inlineStr"/>
-      <c r="BT7" t="inlineStr"/>
-      <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr"/>
-      <c r="BW7" t="inlineStr"/>
-      <c r="BX7" t="inlineStr"/>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr"/>
-      <c r="CB7" t="inlineStr"/>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>I/D</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Settings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr"/>
     </row>
@@ -627,7 +627,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr"/>
     </row>
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr"/>
     </row>
@@ -735,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr"/>
     </row>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr"/>
     </row>
@@ -843,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr"/>
     </row>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr"/>
     </row>
@@ -951,7 +951,7 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr"/>
     </row>
@@ -1005,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr"/>
     </row>
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr"/>
     </row>
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr"/>
     </row>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr"/>
     </row>
@@ -1221,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr"/>
     </row>
@@ -1275,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr"/>
     </row>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr"/>
     </row>
@@ -1383,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr"/>
     </row>
@@ -1437,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr"/>
     </row>
@@ -1491,7 +1491,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr"/>
     </row>
@@ -1545,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr"/>
     </row>
@@ -1599,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr"/>
     </row>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr"/>
     </row>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr"/>
     </row>
@@ -1761,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr"/>
     </row>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr"/>
     </row>
@@ -1869,7 +1869,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr"/>
     </row>
@@ -1923,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr"/>
     </row>
@@ -1977,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr"/>
     </row>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="inlineStr"/>
     </row>
@@ -2085,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="inlineStr"/>
     </row>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr"/>
     </row>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T32" t="inlineStr"/>
     </row>
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" t="inlineStr"/>
     </row>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T34" t="inlineStr"/>
     </row>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T35" t="inlineStr"/>
     </row>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T36" t="inlineStr"/>
     </row>
@@ -2463,7 +2463,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr"/>
     </row>
@@ -2517,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T38" t="inlineStr"/>
     </row>
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr"/>
     </row>
@@ -2625,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T40" t="inlineStr"/>
     </row>
@@ -2679,7 +2679,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" t="inlineStr"/>
     </row>
@@ -2733,7 +2733,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T42" t="inlineStr"/>
     </row>
@@ -2787,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T43" t="inlineStr"/>
     </row>
@@ -2841,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T44" t="inlineStr"/>
     </row>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" t="inlineStr"/>
     </row>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46" t="inlineStr"/>
     </row>
@@ -3003,7 +3003,7 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" t="inlineStr"/>
     </row>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" t="inlineStr"/>
     </row>
@@ -3153,7 +3153,7 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50" t="inlineStr"/>
     </row>
@@ -3203,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51" t="inlineStr"/>
     </row>
@@ -3253,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T52" t="inlineStr"/>
     </row>
@@ -3307,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53" t="inlineStr"/>
     </row>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T54" t="inlineStr"/>
     </row>
@@ -3415,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T55" t="inlineStr"/>
     </row>
@@ -3469,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T56" t="inlineStr"/>
     </row>
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T57" t="inlineStr"/>
     </row>
@@ -3577,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T58" t="inlineStr"/>
     </row>
@@ -3631,7 +3631,7 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T59" t="inlineStr"/>
     </row>
@@ -3685,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T60" t="inlineStr"/>
     </row>
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T61" t="inlineStr"/>
     </row>
@@ -3793,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T62" t="inlineStr"/>
     </row>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T63" t="inlineStr"/>
     </row>
@@ -3901,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T64" t="inlineStr"/>
     </row>
@@ -3955,7 +3955,7 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T65" t="inlineStr"/>
     </row>
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T66" t="inlineStr"/>
     </row>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T67" t="inlineStr"/>
     </row>
@@ -4109,7 +4109,7 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T68" t="inlineStr"/>
     </row>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T69" t="inlineStr"/>
     </row>
@@ -4217,7 +4217,7 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T70" t="inlineStr"/>
     </row>
@@ -4271,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T71" t="inlineStr"/>
     </row>
@@ -4325,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T72" t="inlineStr"/>
     </row>
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr"/>
     </row>
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr"/>
     </row>
@@ -4487,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T75" t="inlineStr"/>
     </row>
@@ -4541,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T76" t="inlineStr"/>
     </row>
@@ -4591,7 +4591,7 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T77" t="inlineStr"/>
     </row>
@@ -4645,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T78" t="inlineStr"/>
     </row>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T79" t="inlineStr"/>
     </row>
@@ -4753,7 +4753,7 @@
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T80" t="inlineStr"/>
     </row>
@@ -4807,7 +4807,7 @@
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr"/>
     </row>
@@ -4861,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T82" t="inlineStr"/>
     </row>
@@ -4915,7 +4915,7 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T83" t="inlineStr"/>
     </row>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T84" t="inlineStr"/>
     </row>
@@ -5023,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T85" t="inlineStr"/>
     </row>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T86" t="inlineStr"/>
     </row>
@@ -5123,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T88" t="inlineStr"/>
     </row>
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T89" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T90" t="inlineStr"/>
     </row>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T91" t="inlineStr"/>
     </row>
@@ -5389,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T92" t="inlineStr"/>
     </row>
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T93" t="inlineStr"/>
     </row>
@@ -5493,7 +5493,7 @@
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T94" t="inlineStr"/>
     </row>
@@ -5547,7 +5547,7 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T95" t="inlineStr"/>
     </row>
@@ -5601,7 +5601,7 @@
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T96" t="inlineStr"/>
     </row>
@@ -5647,7 +5647,7 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T97" t="inlineStr"/>
     </row>
@@ -5693,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T98" t="inlineStr"/>
     </row>
@@ -5739,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T99" t="inlineStr"/>
     </row>
@@ -5785,7 +5785,7 @@
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T100" t="inlineStr"/>
     </row>
@@ -5831,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T101" t="inlineStr"/>
     </row>
@@ -5877,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr"/>
     </row>
@@ -5923,7 +5923,7 @@
         <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T103" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T104" t="inlineStr"/>
     </row>
@@ -6015,7 +6015,7 @@
         <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T105" t="inlineStr"/>
     </row>
@@ -6061,7 +6061,7 @@
         <v>0</v>
       </c>
       <c r="S106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T106" t="inlineStr"/>
     </row>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T107" t="inlineStr"/>
     </row>
@@ -6153,7 +6153,7 @@
         <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T108" t="inlineStr"/>
     </row>
@@ -6199,7 +6199,7 @@
         <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr"/>
     </row>
@@ -6245,7 +6245,7 @@
         <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T110" t="inlineStr"/>
     </row>
@@ -6291,7 +6291,7 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T111" t="inlineStr"/>
     </row>
@@ -6337,7 +6337,7 @@
         <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T112" t="inlineStr"/>
     </row>
@@ -6383,7 +6383,7 @@
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T113" t="inlineStr"/>
     </row>
@@ -6429,7 +6429,7 @@
         <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T114" t="inlineStr"/>
     </row>
@@ -6475,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T115" t="inlineStr"/>
     </row>
@@ -6521,7 +6521,7 @@
         <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T116" t="inlineStr"/>
     </row>
@@ -6567,7 +6567,7 @@
         <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T117" t="inlineStr"/>
     </row>
@@ -6889,7 +6889,7 @@
         <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T124" t="inlineStr"/>
     </row>
@@ -6935,7 +6935,7 @@
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T125" t="inlineStr"/>
     </row>
@@ -6981,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T126" t="inlineStr"/>
     </row>
@@ -7027,7 +7027,7 @@
         <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T127" t="inlineStr"/>
     </row>
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T128" t="inlineStr"/>
     </row>
@@ -7119,7 +7119,7 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T129" t="inlineStr"/>
     </row>
@@ -7165,7 +7165,7 @@
         <v>0</v>
       </c>
       <c r="S130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T130" t="inlineStr"/>
     </row>
@@ -7211,7 +7211,7 @@
         <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T131" t="inlineStr"/>
     </row>
@@ -7257,7 +7257,7 @@
         <v>0</v>
       </c>
       <c r="S132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T132" t="inlineStr"/>
     </row>
@@ -7303,7 +7303,7 @@
         <v>0</v>
       </c>
       <c r="S133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T133" t="inlineStr"/>
     </row>
@@ -7349,7 +7349,7 @@
         <v>0</v>
       </c>
       <c r="S134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T134" t="inlineStr"/>
     </row>
@@ -7395,7 +7395,7 @@
         <v>0</v>
       </c>
       <c r="S135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T135" t="inlineStr"/>
     </row>
@@ -7441,7 +7441,7 @@
         <v>0</v>
       </c>
       <c r="S136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T136" t="inlineStr"/>
     </row>
@@ -7487,7 +7487,7 @@
         <v>0</v>
       </c>
       <c r="S137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T137" t="inlineStr"/>
     </row>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="S138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T138" t="inlineStr"/>
     </row>
@@ -7579,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T139" t="inlineStr"/>
     </row>
@@ -7625,7 +7625,7 @@
         <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T140" t="inlineStr"/>
     </row>
@@ -7671,7 +7671,7 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T141" t="inlineStr"/>
     </row>
@@ -7717,7 +7717,7 @@
         <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T142" t="inlineStr"/>
     </row>
@@ -7763,7 +7763,7 @@
         <v>0</v>
       </c>
       <c r="S143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T143" t="inlineStr"/>
     </row>
@@ -7809,7 +7809,7 @@
         <v>0</v>
       </c>
       <c r="S144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T144" t="inlineStr"/>
     </row>
@@ -7855,7 +7855,7 @@
         <v>0</v>
       </c>
       <c r="S145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T145" t="inlineStr"/>
     </row>
@@ -7901,7 +7901,7 @@
         <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T146" t="inlineStr"/>
     </row>
@@ -7947,7 +7947,7 @@
         <v>0</v>
       </c>
       <c r="S147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T147" t="inlineStr"/>
     </row>
@@ -7993,7 +7993,7 @@
         <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T148" t="inlineStr"/>
     </row>
@@ -8039,7 +8039,7 @@
         <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T149" t="inlineStr"/>
     </row>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="S150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T150" t="inlineStr"/>
     </row>
@@ -8131,7 +8131,7 @@
         <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T151" t="inlineStr"/>
     </row>
@@ -8177,7 +8177,7 @@
         <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T152" t="inlineStr"/>
     </row>
@@ -8223,7 +8223,7 @@
         <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T153" t="inlineStr"/>
     </row>
@@ -8269,7 +8269,7 @@
         <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T154" t="inlineStr"/>
     </row>
@@ -8315,7 +8315,7 @@
         <v>0</v>
       </c>
       <c r="S155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T155" t="inlineStr"/>
     </row>
@@ -8361,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T156" t="inlineStr"/>
     </row>
@@ -8407,7 +8407,7 @@
         <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T157" t="inlineStr"/>
     </row>
@@ -8453,7 +8453,7 @@
         <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T158" t="inlineStr"/>
     </row>
@@ -8499,7 +8499,7 @@
         <v>0</v>
       </c>
       <c r="S159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T159" t="inlineStr"/>
     </row>
@@ -8545,7 +8545,7 @@
         <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T160" t="inlineStr"/>
     </row>
@@ -8591,7 +8591,7 @@
         <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T161" t="inlineStr"/>
     </row>
@@ -8637,7 +8637,7 @@
         <v>0</v>
       </c>
       <c r="S162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T162" t="inlineStr"/>
     </row>
@@ -8683,7 +8683,7 @@
         <v>0</v>
       </c>
       <c r="S163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T163" t="inlineStr"/>
     </row>
@@ -8729,7 +8729,7 @@
         <v>0</v>
       </c>
       <c r="S164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T164" t="inlineStr"/>
     </row>
@@ -8775,7 +8775,7 @@
         <v>0</v>
       </c>
       <c r="S165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T165" t="inlineStr"/>
     </row>
@@ -8821,7 +8821,7 @@
         <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T166" t="inlineStr"/>
     </row>
@@ -8867,7 +8867,7 @@
         <v>0</v>
       </c>
       <c r="S167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T167" t="inlineStr"/>
     </row>
@@ -8913,7 +8913,7 @@
         <v>0</v>
       </c>
       <c r="S168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T168" t="inlineStr"/>
     </row>
@@ -8959,7 +8959,7 @@
         <v>0</v>
       </c>
       <c r="S169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T169" t="inlineStr"/>
     </row>
@@ -9005,7 +9005,7 @@
         <v>0</v>
       </c>
       <c r="S170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T170" t="inlineStr"/>
     </row>
@@ -9051,7 +9051,7 @@
         <v>0</v>
       </c>
       <c r="S171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T171" t="inlineStr"/>
     </row>
@@ -9097,7 +9097,7 @@
         <v>0</v>
       </c>
       <c r="S172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T172" t="inlineStr"/>
     </row>
@@ -9143,7 +9143,7 @@
         <v>0</v>
       </c>
       <c r="S173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T173" t="inlineStr"/>
     </row>
@@ -9193,7 +9193,7 @@
         <v>0</v>
       </c>
       <c r="S174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T174" t="inlineStr"/>
     </row>
@@ -9247,7 +9247,7 @@
         <v>0</v>
       </c>
       <c r="S175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T175" t="inlineStr"/>
     </row>
@@ -9301,7 +9301,7 @@
         <v>0</v>
       </c>
       <c r="S176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T176" t="inlineStr"/>
     </row>
@@ -9347,7 +9347,7 @@
         <v>0</v>
       </c>
       <c r="S177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T177" t="inlineStr"/>
     </row>
@@ -9393,7 +9393,7 @@
         <v>0</v>
       </c>
       <c r="S178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T178" t="inlineStr"/>
     </row>
@@ -9439,7 +9439,7 @@
         <v>0</v>
       </c>
       <c r="S179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T179" t="inlineStr"/>
     </row>
@@ -9485,7 +9485,7 @@
         <v>0</v>
       </c>
       <c r="S180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T180" t="inlineStr"/>
     </row>
@@ -9531,7 +9531,7 @@
         <v>0</v>
       </c>
       <c r="S181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T181" t="inlineStr"/>
     </row>
@@ -9577,7 +9577,7 @@
         <v>0</v>
       </c>
       <c r="S182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T182" t="inlineStr"/>
     </row>
@@ -9623,7 +9623,7 @@
         <v>0</v>
       </c>
       <c r="S183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T183" t="inlineStr"/>
     </row>
@@ -9669,7 +9669,7 @@
         <v>0</v>
       </c>
       <c r="S184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T184" t="inlineStr"/>
     </row>
@@ -9715,7 +9715,7 @@
         <v>0</v>
       </c>
       <c r="S185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T185" t="inlineStr"/>
     </row>
@@ -9761,7 +9761,7 @@
         <v>0</v>
       </c>
       <c r="S186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T186" t="inlineStr"/>
     </row>
@@ -9807,7 +9807,7 @@
         <v>0</v>
       </c>
       <c r="S187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T187" t="inlineStr"/>
     </row>
@@ -9853,7 +9853,7 @@
         <v>0</v>
       </c>
       <c r="S188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T188" t="inlineStr"/>
     </row>
@@ -9899,7 +9899,7 @@
         <v>0</v>
       </c>
       <c r="S189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T189" t="inlineStr"/>
     </row>
@@ -9945,7 +9945,7 @@
         <v>0</v>
       </c>
       <c r="S190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T190" t="inlineStr"/>
     </row>
@@ -9991,7 +9991,7 @@
         <v>0</v>
       </c>
       <c r="S191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T191" t="inlineStr"/>
     </row>
@@ -10037,7 +10037,7 @@
         <v>0</v>
       </c>
       <c r="S192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T192" t="inlineStr"/>
     </row>
@@ -10083,7 +10083,7 @@
         <v>0</v>
       </c>
       <c r="S193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T193" t="inlineStr"/>
     </row>
@@ -10129,7 +10129,7 @@
         <v>0</v>
       </c>
       <c r="S194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T194" t="inlineStr"/>
     </row>
@@ -10175,7 +10175,7 @@
         <v>0</v>
       </c>
       <c r="S195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T195" t="inlineStr"/>
     </row>
@@ -10221,7 +10221,7 @@
         <v>0</v>
       </c>
       <c r="S196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T196" t="inlineStr"/>
     </row>
@@ -10267,7 +10267,7 @@
         <v>0</v>
       </c>
       <c r="S197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T197" t="inlineStr"/>
     </row>
@@ -10313,7 +10313,7 @@
         <v>0</v>
       </c>
       <c r="S198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T198" t="inlineStr"/>
     </row>
@@ -10359,7 +10359,7 @@
         <v>0</v>
       </c>
       <c r="S199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T199" t="inlineStr"/>
     </row>
@@ -10405,7 +10405,7 @@
         <v>0</v>
       </c>
       <c r="S200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T200" t="inlineStr"/>
     </row>
@@ -10451,7 +10451,7 @@
         <v>0</v>
       </c>
       <c r="S201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T201" t="inlineStr"/>
     </row>
@@ -10497,7 +10497,7 @@
         <v>0</v>
       </c>
       <c r="S202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T202" t="inlineStr"/>
     </row>
@@ -10543,7 +10543,7 @@
         <v>0</v>
       </c>
       <c r="S203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T203" t="inlineStr"/>
     </row>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="S204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T204" t="inlineStr"/>
     </row>
@@ -10635,7 +10635,7 @@
         <v>0</v>
       </c>
       <c r="S205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T205" t="inlineStr"/>
     </row>
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="S206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T206" t="inlineStr"/>
     </row>
@@ -10727,7 +10727,7 @@
         <v>0</v>
       </c>
       <c r="S207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T207" t="inlineStr"/>
     </row>
@@ -10773,7 +10773,7 @@
         <v>0</v>
       </c>
       <c r="S208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T208" t="inlineStr"/>
     </row>
@@ -10819,7 +10819,7 @@
         <v>0</v>
       </c>
       <c r="S209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T209" t="inlineStr"/>
     </row>
@@ -10873,7 +10873,7 @@
         <v>0</v>
       </c>
       <c r="S210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T210" t="inlineStr"/>
     </row>
@@ -10927,7 +10927,7 @@
         <v>0</v>
       </c>
       <c r="S211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T211" t="inlineStr"/>
     </row>
@@ -10981,7 +10981,7 @@
         <v>0</v>
       </c>
       <c r="S212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T212" t="inlineStr"/>
     </row>
@@ -11035,7 +11035,7 @@
         <v>0</v>
       </c>
       <c r="S213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T213" t="inlineStr"/>
     </row>
@@ -11089,7 +11089,7 @@
         <v>0</v>
       </c>
       <c r="S214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T214" t="inlineStr"/>
     </row>
@@ -11143,7 +11143,7 @@
         <v>0</v>
       </c>
       <c r="S215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T215" t="inlineStr"/>
     </row>
@@ -11197,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="S216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T216" t="inlineStr"/>
     </row>
@@ -11251,7 +11251,7 @@
         <v>0</v>
       </c>
       <c r="S217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T217" t="inlineStr"/>
     </row>
@@ -11305,7 +11305,7 @@
         <v>0</v>
       </c>
       <c r="S218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T218" t="inlineStr"/>
     </row>
@@ -11359,7 +11359,7 @@
         <v>0</v>
       </c>
       <c r="S219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T219" t="inlineStr"/>
     </row>
@@ -11413,7 +11413,7 @@
         <v>0</v>
       </c>
       <c r="S220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T220" t="inlineStr"/>
     </row>
@@ -11467,7 +11467,7 @@
         <v>0</v>
       </c>
       <c r="S221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T221" t="inlineStr"/>
     </row>
@@ -11521,7 +11521,7 @@
         <v>0</v>
       </c>
       <c r="S222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T222" t="inlineStr"/>
     </row>
@@ -11575,7 +11575,7 @@
         <v>0</v>
       </c>
       <c r="S223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T223" t="inlineStr"/>
     </row>
@@ -11629,7 +11629,7 @@
         <v>0</v>
       </c>
       <c r="S224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T224" t="inlineStr"/>
     </row>
@@ -11683,7 +11683,7 @@
         <v>0</v>
       </c>
       <c r="S225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T225" t="inlineStr"/>
     </row>
@@ -11737,7 +11737,7 @@
         <v>0</v>
       </c>
       <c r="S226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T226" t="inlineStr"/>
     </row>
@@ -11791,7 +11791,7 @@
         <v>0</v>
       </c>
       <c r="S227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T227" t="inlineStr"/>
     </row>
@@ -11845,7 +11845,7 @@
         <v>0</v>
       </c>
       <c r="S228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T228" t="inlineStr"/>
     </row>
@@ -11895,7 +11895,7 @@
         <v>0</v>
       </c>
       <c r="S229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T229" t="inlineStr"/>
     </row>
@@ -11949,7 +11949,7 @@
         <v>0</v>
       </c>
       <c r="S230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T230" t="inlineStr"/>
     </row>
@@ -12003,7 +12003,7 @@
         <v>0</v>
       </c>
       <c r="S231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T231" t="inlineStr"/>
     </row>
@@ -12057,7 +12057,7 @@
         <v>0</v>
       </c>
       <c r="S232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T232" t="inlineStr"/>
     </row>
@@ -12111,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="S233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T233" t="inlineStr"/>
     </row>
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="S234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T234" t="inlineStr"/>
     </row>
@@ -12219,7 +12219,7 @@
         <v>0</v>
       </c>
       <c r="S235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T235" t="inlineStr"/>
     </row>
@@ -12273,7 +12273,7 @@
         <v>0</v>
       </c>
       <c r="S236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T236" t="inlineStr"/>
     </row>
@@ -12327,7 +12327,7 @@
         <v>0</v>
       </c>
       <c r="S237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T237" t="inlineStr"/>
     </row>
@@ -12381,7 +12381,7 @@
         <v>0</v>
       </c>
       <c r="S238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T238" t="inlineStr"/>
     </row>
@@ -12435,7 +12435,7 @@
         <v>0</v>
       </c>
       <c r="S239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T239" t="inlineStr"/>
     </row>
@@ -12489,7 +12489,7 @@
         <v>0</v>
       </c>
       <c r="S240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T240" t="inlineStr"/>
     </row>
@@ -12543,7 +12543,7 @@
         <v>0</v>
       </c>
       <c r="S241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T241" t="inlineStr"/>
     </row>
@@ -12597,7 +12597,7 @@
         <v>0</v>
       </c>
       <c r="S242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T242" t="inlineStr"/>
     </row>
@@ -12651,7 +12651,7 @@
         <v>0</v>
       </c>
       <c r="S243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T243" t="inlineStr"/>
     </row>
@@ -12705,7 +12705,7 @@
         <v>0</v>
       </c>
       <c r="S244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T244" t="inlineStr"/>
     </row>
@@ -12755,7 +12755,7 @@
         <v>0</v>
       </c>
       <c r="S245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T245" t="inlineStr"/>
     </row>
@@ -12805,7 +12805,7 @@
         <v>0</v>
       </c>
       <c r="S246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T246" t="inlineStr"/>
     </row>
@@ -12855,7 +12855,7 @@
         <v>0</v>
       </c>
       <c r="S247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T247" t="inlineStr"/>
     </row>
@@ -12909,7 +12909,7 @@
         <v>0</v>
       </c>
       <c r="S248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T248" t="inlineStr"/>
     </row>
@@ -12963,7 +12963,7 @@
         <v>0</v>
       </c>
       <c r="S249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T249" t="inlineStr"/>
     </row>
@@ -13013,7 +13013,7 @@
         <v>0</v>
       </c>
       <c r="S250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T250" t="inlineStr"/>
     </row>
@@ -13067,7 +13067,7 @@
         <v>0</v>
       </c>
       <c r="S251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T251" t="inlineStr"/>
     </row>
@@ -13117,7 +13117,7 @@
         <v>0</v>
       </c>
       <c r="S252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T252" t="inlineStr"/>
     </row>
@@ -13167,7 +13167,7 @@
         <v>0</v>
       </c>
       <c r="S253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T253" t="inlineStr"/>
     </row>
@@ -13221,7 +13221,7 @@
         <v>0</v>
       </c>
       <c r="S254" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T254" t="inlineStr"/>
     </row>
@@ -13275,7 +13275,7 @@
         <v>0</v>
       </c>
       <c r="S255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T255" t="inlineStr"/>
     </row>
@@ -13329,7 +13329,7 @@
         <v>0</v>
       </c>
       <c r="S256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T256" t="inlineStr"/>
     </row>
@@ -13383,7 +13383,7 @@
         <v>0</v>
       </c>
       <c r="S257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T257" t="inlineStr"/>
     </row>
@@ -13437,7 +13437,7 @@
         <v>0</v>
       </c>
       <c r="S258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T258" t="inlineStr"/>
     </row>
@@ -13491,7 +13491,7 @@
         <v>0</v>
       </c>
       <c r="S259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T259" t="inlineStr"/>
     </row>
@@ -13545,7 +13545,7 @@
         <v>0</v>
       </c>
       <c r="S260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T260" t="inlineStr"/>
     </row>
@@ -13595,7 +13595,7 @@
         <v>0</v>
       </c>
       <c r="S261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T261" t="inlineStr"/>
     </row>
@@ -13649,7 +13649,7 @@
         <v>0</v>
       </c>
       <c r="S262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T262" t="inlineStr"/>
     </row>
@@ -13703,7 +13703,7 @@
         <v>0</v>
       </c>
       <c r="S263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T263" t="inlineStr"/>
     </row>
@@ -13757,7 +13757,7 @@
         <v>0</v>
       </c>
       <c r="S264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T264" t="inlineStr"/>
     </row>
@@ -13811,7 +13811,7 @@
         <v>0</v>
       </c>
       <c r="S265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T265" t="inlineStr"/>
     </row>
@@ -13865,7 +13865,7 @@
         <v>0</v>
       </c>
       <c r="S266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T266" t="inlineStr"/>
     </row>
@@ -13919,7 +13919,7 @@
         <v>0</v>
       </c>
       <c r="S267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T267" t="inlineStr"/>
     </row>
@@ -13973,7 +13973,7 @@
         <v>0</v>
       </c>
       <c r="S268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T268" t="inlineStr"/>
     </row>
@@ -14027,7 +14027,7 @@
         <v>0</v>
       </c>
       <c r="S269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T269" t="inlineStr"/>
     </row>
@@ -14081,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="S270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T270" t="inlineStr"/>
     </row>
@@ -14135,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="S271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T271" t="inlineStr"/>
     </row>
@@ -14189,7 +14189,7 @@
         <v>0</v>
       </c>
       <c r="S272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T272" t="inlineStr"/>
     </row>
@@ -14243,7 +14243,7 @@
         <v>0</v>
       </c>
       <c r="S273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T273" t="inlineStr"/>
     </row>
@@ -14297,7 +14297,7 @@
         <v>0</v>
       </c>
       <c r="S274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T274" t="inlineStr"/>
     </row>
@@ -14351,7 +14351,7 @@
         <v>0</v>
       </c>
       <c r="S275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T275" t="inlineStr"/>
     </row>
@@ -14405,7 +14405,7 @@
         <v>0</v>
       </c>
       <c r="S276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T276" t="inlineStr"/>
     </row>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="S277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T277" t="inlineStr"/>
     </row>
@@ -14513,7 +14513,7 @@
         <v>0</v>
       </c>
       <c r="S278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T278" t="inlineStr"/>
     </row>
@@ -14567,7 +14567,7 @@
         <v>0</v>
       </c>
       <c r="S279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T279" t="inlineStr"/>
     </row>
@@ -14621,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="S280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T280" t="inlineStr"/>
     </row>
@@ -14675,7 +14675,7 @@
         <v>0</v>
       </c>
       <c r="S281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T281" t="inlineStr"/>
     </row>
@@ -14729,7 +14729,7 @@
         <v>0</v>
       </c>
       <c r="S282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T282" t="inlineStr"/>
     </row>
@@ -14783,7 +14783,7 @@
         <v>0</v>
       </c>
       <c r="S283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T283" t="inlineStr"/>
     </row>
@@ -14837,7 +14837,7 @@
         <v>0</v>
       </c>
       <c r="S284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T284" t="inlineStr"/>
     </row>
@@ -14891,7 +14891,7 @@
         <v>0</v>
       </c>
       <c r="S285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T285" t="inlineStr"/>
     </row>
@@ -14945,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="S286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T286" t="inlineStr"/>
     </row>
@@ -14999,7 +14999,7 @@
         <v>0</v>
       </c>
       <c r="S287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T287" t="inlineStr"/>
     </row>
@@ -15053,7 +15053,7 @@
         <v>0</v>
       </c>
       <c r="S288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T288" t="inlineStr"/>
     </row>
@@ -15107,7 +15107,7 @@
         <v>0</v>
       </c>
       <c r="S289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T289" t="inlineStr"/>
     </row>
@@ -15161,7 +15161,7 @@
         <v>0</v>
       </c>
       <c r="S290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T290" t="inlineStr"/>
     </row>
@@ -15215,7 +15215,7 @@
         <v>0</v>
       </c>
       <c r="S291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T291" t="inlineStr"/>
     </row>
@@ -15269,7 +15269,7 @@
         <v>0</v>
       </c>
       <c r="S292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T292" t="inlineStr"/>
     </row>
@@ -15323,7 +15323,7 @@
         <v>0</v>
       </c>
       <c r="S293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T293" t="inlineStr"/>
     </row>
@@ -15377,7 +15377,7 @@
         <v>0</v>
       </c>
       <c r="S294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T294" t="inlineStr"/>
     </row>
@@ -15431,7 +15431,7 @@
         <v>0</v>
       </c>
       <c r="S295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T295" t="inlineStr"/>
     </row>
@@ -15485,7 +15485,7 @@
         <v>0</v>
       </c>
       <c r="S296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T296" t="inlineStr"/>
     </row>
@@ -15539,7 +15539,7 @@
         <v>0</v>
       </c>
       <c r="S297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T297" t="inlineStr"/>
     </row>
@@ -15593,7 +15593,7 @@
         <v>0</v>
       </c>
       <c r="S298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T298" t="inlineStr"/>
     </row>
@@ -15647,7 +15647,7 @@
         <v>0</v>
       </c>
       <c r="S299" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T299" t="inlineStr"/>
     </row>
@@ -15701,7 +15701,7 @@
         <v>0</v>
       </c>
       <c r="S300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T300" t="inlineStr"/>
     </row>
@@ -15755,7 +15755,7 @@
         <v>0</v>
       </c>
       <c r="S301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T301" t="inlineStr"/>
     </row>
@@ -15809,7 +15809,7 @@
         <v>0</v>
       </c>
       <c r="S302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T302" t="inlineStr"/>
     </row>
@@ -15863,7 +15863,7 @@
         <v>0</v>
       </c>
       <c r="S303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T303" t="inlineStr"/>
     </row>
@@ -15917,7 +15917,7 @@
         <v>0</v>
       </c>
       <c r="S304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T304" t="inlineStr"/>
     </row>
@@ -15971,7 +15971,7 @@
         <v>0</v>
       </c>
       <c r="S305" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T305" t="inlineStr"/>
     </row>
@@ -16025,7 +16025,7 @@
         <v>0</v>
       </c>
       <c r="S306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T306" t="inlineStr"/>
     </row>
@@ -16079,7 +16079,7 @@
         <v>0</v>
       </c>
       <c r="S307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T307" t="inlineStr"/>
     </row>
@@ -16133,7 +16133,7 @@
         <v>0</v>
       </c>
       <c r="S308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T308" t="inlineStr"/>
     </row>
@@ -16187,7 +16187,7 @@
         <v>0</v>
       </c>
       <c r="S309" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T309" t="inlineStr"/>
     </row>
@@ -16241,7 +16241,7 @@
         <v>0</v>
       </c>
       <c r="S310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T310" t="inlineStr"/>
     </row>
@@ -16295,7 +16295,7 @@
         <v>0</v>
       </c>
       <c r="S311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T311" t="inlineStr"/>
     </row>
@@ -16349,7 +16349,7 @@
         <v>0</v>
       </c>
       <c r="S312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T312" t="inlineStr"/>
     </row>
@@ -16403,7 +16403,7 @@
         <v>0</v>
       </c>
       <c r="S313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T313" t="inlineStr"/>
     </row>
@@ -16457,7 +16457,7 @@
         <v>0</v>
       </c>
       <c r="S314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T314" t="inlineStr"/>
     </row>
@@ -16511,7 +16511,7 @@
         <v>0</v>
       </c>
       <c r="S315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T315" t="inlineStr"/>
     </row>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="S316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T316" t="inlineStr"/>
     </row>
@@ -16619,7 +16619,7 @@
         <v>0</v>
       </c>
       <c r="S317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T317" t="inlineStr"/>
     </row>
@@ -16673,7 +16673,7 @@
         <v>0</v>
       </c>
       <c r="S318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T318" t="inlineStr"/>
     </row>
@@ -16727,7 +16727,7 @@
         <v>0</v>
       </c>
       <c r="S319" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T319" t="inlineStr"/>
     </row>
@@ -16781,7 +16781,7 @@
         <v>0</v>
       </c>
       <c r="S320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T320" t="inlineStr"/>
     </row>
@@ -16835,7 +16835,7 @@
         <v>0</v>
       </c>
       <c r="S321" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T321" t="inlineStr"/>
     </row>
@@ -16889,7 +16889,7 @@
         <v>0</v>
       </c>
       <c r="S322" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T322" t="inlineStr"/>
     </row>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="S323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T323" t="inlineStr"/>
     </row>
@@ -16997,7 +16997,7 @@
         <v>0</v>
       </c>
       <c r="S324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T324" t="inlineStr"/>
     </row>
@@ -17051,7 +17051,7 @@
         <v>0</v>
       </c>
       <c r="S325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T325" t="inlineStr"/>
     </row>
@@ -17105,7 +17105,7 @@
         <v>0</v>
       </c>
       <c r="S326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T326" t="inlineStr"/>
     </row>
@@ -17159,7 +17159,7 @@
         <v>0</v>
       </c>
       <c r="S327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T327" t="inlineStr"/>
     </row>
@@ -17213,7 +17213,7 @@
         <v>0</v>
       </c>
       <c r="S328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T328" t="inlineStr"/>
     </row>
@@ -17267,7 +17267,7 @@
         <v>0</v>
       </c>
       <c r="S329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T329" t="inlineStr"/>
     </row>
@@ -17321,7 +17321,7 @@
         <v>0</v>
       </c>
       <c r="S330" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T330" t="inlineStr"/>
     </row>
@@ -17375,7 +17375,7 @@
         <v>0</v>
       </c>
       <c r="S331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T331" t="inlineStr"/>
     </row>
@@ -17429,7 +17429,7 @@
         <v>0</v>
       </c>
       <c r="S332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T332" t="inlineStr"/>
     </row>
@@ -17483,7 +17483,7 @@
         <v>0</v>
       </c>
       <c r="S333" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T333" t="inlineStr"/>
     </row>
@@ -17537,7 +17537,7 @@
         <v>0</v>
       </c>
       <c r="S334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T334" t="inlineStr"/>
     </row>
@@ -17591,7 +17591,7 @@
         <v>0</v>
       </c>
       <c r="S335" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T335" t="inlineStr"/>
     </row>
@@ -17645,7 +17645,7 @@
         <v>0</v>
       </c>
       <c r="S336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T336" t="inlineStr"/>
     </row>
@@ -17699,7 +17699,7 @@
         <v>0</v>
       </c>
       <c r="S337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T337" t="inlineStr"/>
     </row>
@@ -17753,7 +17753,7 @@
         <v>0</v>
       </c>
       <c r="S338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T338" t="inlineStr"/>
     </row>
@@ -17807,7 +17807,7 @@
         <v>0</v>
       </c>
       <c r="S339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T339" t="inlineStr"/>
     </row>
@@ -17861,7 +17861,7 @@
         <v>0</v>
       </c>
       <c r="S340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T340" t="inlineStr"/>
     </row>
@@ -17915,7 +17915,7 @@
         <v>0</v>
       </c>
       <c r="S341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T341" t="inlineStr"/>
     </row>
@@ -17969,7 +17969,7 @@
         <v>0</v>
       </c>
       <c r="S342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T342" t="inlineStr"/>
     </row>
@@ -18023,7 +18023,7 @@
         <v>0</v>
       </c>
       <c r="S343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T343" t="inlineStr"/>
     </row>
@@ -18077,7 +18077,7 @@
         <v>0</v>
       </c>
       <c r="S344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T344" t="inlineStr"/>
     </row>
@@ -18131,7 +18131,7 @@
         <v>0</v>
       </c>
       <c r="S345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T345" t="inlineStr"/>
     </row>
@@ -18185,7 +18185,7 @@
         <v>0</v>
       </c>
       <c r="S346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T346" t="inlineStr"/>
     </row>
@@ -18239,7 +18239,7 @@
         <v>0</v>
       </c>
       <c r="S347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T347" t="inlineStr"/>
     </row>
@@ -18293,7 +18293,7 @@
         <v>0</v>
       </c>
       <c r="S348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T348" t="inlineStr"/>
     </row>
@@ -18347,7 +18347,7 @@
         <v>0</v>
       </c>
       <c r="S349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T349" t="inlineStr"/>
     </row>
@@ -18401,7 +18401,7 @@
         <v>0</v>
       </c>
       <c r="S350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T350" t="inlineStr"/>
     </row>
@@ -18455,7 +18455,7 @@
         <v>0</v>
       </c>
       <c r="S351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T351" t="inlineStr"/>
     </row>
@@ -18509,7 +18509,7 @@
         <v>0</v>
       </c>
       <c r="S352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T352" t="inlineStr"/>
     </row>
@@ -18563,7 +18563,7 @@
         <v>0</v>
       </c>
       <c r="S353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T353" t="inlineStr"/>
     </row>
@@ -18617,7 +18617,7 @@
         <v>0</v>
       </c>
       <c r="S354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T354" t="inlineStr"/>
     </row>
@@ -18671,7 +18671,7 @@
         <v>0</v>
       </c>
       <c r="S355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T355" t="inlineStr"/>
     </row>
@@ -18725,7 +18725,7 @@
         <v>0</v>
       </c>
       <c r="S356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T356" t="inlineStr"/>
     </row>
@@ -18775,7 +18775,7 @@
         <v>0</v>
       </c>
       <c r="S357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T357" t="inlineStr"/>
     </row>
@@ -18829,7 +18829,7 @@
         <v>0</v>
       </c>
       <c r="S358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T358" t="inlineStr"/>
     </row>
@@ -18879,7 +18879,7 @@
         <v>0</v>
       </c>
       <c r="S359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T359" t="inlineStr"/>
     </row>
@@ -18929,7 +18929,7 @@
         <v>0</v>
       </c>
       <c r="S360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T360" t="inlineStr"/>
     </row>
@@ -18979,7 +18979,7 @@
         <v>0</v>
       </c>
       <c r="S361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T361" t="inlineStr"/>
     </row>
@@ -19029,7 +19029,7 @@
         <v>0</v>
       </c>
       <c r="S362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T362" t="inlineStr"/>
     </row>
@@ -19079,7 +19079,7 @@
         <v>0</v>
       </c>
       <c r="S363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T363" t="inlineStr"/>
     </row>
@@ -19129,7 +19129,7 @@
         <v>0</v>
       </c>
       <c r="S364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T364" t="inlineStr"/>
     </row>
@@ -19179,7 +19179,7 @@
         <v>0</v>
       </c>
       <c r="S365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T365" t="inlineStr"/>
     </row>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="S366" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T366" t="inlineStr"/>
     </row>
@@ -19279,7 +19279,7 @@
         <v>0</v>
       </c>
       <c r="S367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T367" t="inlineStr"/>
     </row>
@@ -19329,7 +19329,7 @@
         <v>0</v>
       </c>
       <c r="S368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T368" t="inlineStr"/>
     </row>
@@ -19379,7 +19379,7 @@
         <v>0</v>
       </c>
       <c r="S369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T369" t="inlineStr"/>
     </row>
@@ -19429,7 +19429,7 @@
         <v>0</v>
       </c>
       <c r="S370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T370" t="inlineStr"/>
     </row>
@@ -19479,7 +19479,7 @@
         <v>0</v>
       </c>
       <c r="S371" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T371" t="inlineStr"/>
     </row>
@@ -19529,7 +19529,7 @@
         <v>0</v>
       </c>
       <c r="S372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T372" t="inlineStr"/>
     </row>
@@ -19579,7 +19579,7 @@
         <v>0</v>
       </c>
       <c r="S373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T373" t="inlineStr"/>
     </row>
@@ -19629,7 +19629,7 @@
         <v>0</v>
       </c>
       <c r="S374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T374" t="inlineStr"/>
     </row>
@@ -19679,7 +19679,7 @@
         <v>0</v>
       </c>
       <c r="S375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T375" t="inlineStr"/>
     </row>
@@ -19733,7 +19733,7 @@
         <v>0</v>
       </c>
       <c r="S376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T376" t="inlineStr"/>
     </row>
@@ -19787,7 +19787,7 @@
         <v>0</v>
       </c>
       <c r="S377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T377" t="inlineStr"/>
     </row>
@@ -19837,7 +19837,7 @@
         <v>0</v>
       </c>
       <c r="S378" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T378" t="inlineStr"/>
     </row>
@@ -19887,7 +19887,7 @@
         <v>0</v>
       </c>
       <c r="S379" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T379" t="inlineStr"/>
     </row>
@@ -19937,7 +19937,7 @@
         <v>0</v>
       </c>
       <c r="S380" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T380" t="inlineStr"/>
     </row>
@@ -19991,7 +19991,7 @@
         <v>0</v>
       </c>
       <c r="S381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T381" t="inlineStr"/>
     </row>
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="S382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T382" t="inlineStr"/>
     </row>
@@ -20099,7 +20099,7 @@
         <v>0</v>
       </c>
       <c r="S383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T383" t="inlineStr"/>
     </row>
@@ -20153,7 +20153,7 @@
         <v>0</v>
       </c>
       <c r="S384" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T384" t="inlineStr"/>
     </row>
@@ -20207,7 +20207,7 @@
         <v>0</v>
       </c>
       <c r="S385" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T385" t="inlineStr"/>
     </row>
@@ -20261,7 +20261,7 @@
         <v>0</v>
       </c>
       <c r="S386" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T386" t="inlineStr"/>
     </row>
@@ -20315,7 +20315,7 @@
         <v>0</v>
       </c>
       <c r="S387" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T387" t="inlineStr"/>
     </row>
@@ -20365,7 +20365,7 @@
         <v>0</v>
       </c>
       <c r="S388" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T388" t="inlineStr"/>
     </row>
@@ -20419,7 +20419,7 @@
         <v>0</v>
       </c>
       <c r="S389" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T389" t="inlineStr"/>
     </row>
@@ -20473,7 +20473,7 @@
         <v>0</v>
       </c>
       <c r="S390" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T390" t="inlineStr"/>
     </row>
@@ -20527,7 +20527,7 @@
         <v>0</v>
       </c>
       <c r="S391" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T391" t="inlineStr"/>
     </row>
@@ -20581,7 +20581,7 @@
         <v>0</v>
       </c>
       <c r="S392" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T392" t="inlineStr"/>
     </row>
@@ -20635,7 +20635,7 @@
         <v>0</v>
       </c>
       <c r="S393" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T393" t="inlineStr"/>
     </row>
@@ -20689,7 +20689,7 @@
         <v>0</v>
       </c>
       <c r="S394" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T394" t="inlineStr"/>
     </row>
@@ -20743,7 +20743,7 @@
         <v>0</v>
       </c>
       <c r="S395" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T395" t="inlineStr"/>
     </row>
@@ -20797,7 +20797,7 @@
         <v>0</v>
       </c>
       <c r="S396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T396" t="inlineStr"/>
     </row>
@@ -20851,7 +20851,7 @@
         <v>0</v>
       </c>
       <c r="S397" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T397" t="inlineStr"/>
     </row>
@@ -20901,7 +20901,7 @@
         <v>0</v>
       </c>
       <c r="S398" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T398" t="inlineStr"/>
     </row>
@@ -20955,7 +20955,7 @@
         <v>0</v>
       </c>
       <c r="S399" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T399" t="inlineStr"/>
     </row>
@@ -21009,7 +21009,7 @@
         <v>0</v>
       </c>
       <c r="S400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T400" t="inlineStr"/>
     </row>
@@ -21063,7 +21063,7 @@
         <v>0</v>
       </c>
       <c r="S401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T401" t="inlineStr"/>
     </row>
@@ -21117,7 +21117,7 @@
         <v>0</v>
       </c>
       <c r="S402" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T402" t="inlineStr"/>
     </row>
@@ -21171,7 +21171,7 @@
         <v>0</v>
       </c>
       <c r="S403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T403" t="inlineStr"/>
     </row>
@@ -21225,7 +21225,7 @@
         <v>0</v>
       </c>
       <c r="S404" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T404" t="inlineStr"/>
     </row>
@@ -21633,11 +21633,7 @@
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr">
         <is>
@@ -21729,11 +21725,7 @@
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr">
         <is>
@@ -21763,7 +21755,7 @@
         <v>0</v>
       </c>
       <c r="S415" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T415" t="inlineStr"/>
     </row>
@@ -22607,7 +22599,7 @@
         <v>0</v>
       </c>
       <c r="S431" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T431" t="inlineStr"/>
     </row>
@@ -22661,7 +22653,7 @@
         <v>0</v>
       </c>
       <c r="S432" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T432" t="inlineStr"/>
     </row>
@@ -22681,11 +22673,7 @@
           <t>현장</t>
         </is>
       </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr">
         <is>
           <t>자동등록</t>
@@ -23723,10 +23711,8 @@
           <t>탑차 81도4028</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="BI2" t="n">
+        <v>25</v>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
@@ -23904,10 +23890,8 @@
           <t>탑차 81도4028</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="BI3" t="n">
+        <v>25</v>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Settings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S458"/>
+  <dimension ref="A1:S462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -893,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1052,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1105,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1158,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1211,7 +1211,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1370,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1423,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1529,7 +1529,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1582,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1688,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1847,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1953,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2006,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2059,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2112,7 +2112,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2218,7 +2218,7 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2377,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2430,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2483,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2536,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2642,7 +2642,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2695,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2801,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2854,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3009,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3058,7 +3058,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3107,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3205,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3258,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3311,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3364,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3470,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3576,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3629,7 +3629,7 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3735,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3788,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -3996,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4045,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4098,7 +4098,7 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4151,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4257,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4469,7 +4469,7 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4522,7 +4522,7 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4575,7 +4575,7 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4628,7 +4628,7 @@
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4681,7 +4681,7 @@
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -4734,7 +4734,7 @@
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -4787,7 +4787,7 @@
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -4840,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -4999,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5052,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -5158,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -5264,7 +5264,7 @@
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5317,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -5370,7 +5370,7 @@
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -5472,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5525,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -5578,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -5684,7 +5684,7 @@
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -5737,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -5790,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -5843,7 +5843,7 @@
         <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -5896,7 +5896,7 @@
         <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -5949,7 +5949,7 @@
         <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -6002,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -6055,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="S106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -6104,7 +6104,7 @@
         <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -6153,7 +6153,7 @@
         <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -6251,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -6300,7 +6300,7 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -6349,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -6398,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -6447,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -6496,7 +6496,7 @@
         <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -6545,7 +6545,7 @@
         <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -6594,7 +6594,7 @@
         <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -6643,7 +6643,7 @@
         <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -6692,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="S119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -6741,7 +6741,7 @@
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -6790,7 +6790,7 @@
         <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -6839,7 +6839,7 @@
         <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -6888,7 +6888,7 @@
         <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -6937,7 +6937,7 @@
         <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -7035,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -7084,7 +7084,7 @@
         <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -7133,7 +7133,7 @@
         <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -7231,7 +7231,7 @@
         <v>0</v>
       </c>
       <c r="S130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -7280,7 +7280,7 @@
         <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -7329,7 +7329,7 @@
         <v>0</v>
       </c>
       <c r="S132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -7378,7 +7378,7 @@
         <v>0</v>
       </c>
       <c r="S133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -7427,7 +7427,7 @@
         <v>0</v>
       </c>
       <c r="S134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -7476,7 +7476,7 @@
         <v>0</v>
       </c>
       <c r="S135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -7525,7 +7525,7 @@
         <v>0</v>
       </c>
       <c r="S136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -7574,7 +7574,7 @@
         <v>0</v>
       </c>
       <c r="S137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -7623,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="S138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -7672,7 +7672,7 @@
         <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -7721,7 +7721,7 @@
         <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -7770,7 +7770,7 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -7819,7 +7819,7 @@
         <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -7868,7 +7868,7 @@
         <v>0</v>
       </c>
       <c r="S143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -7917,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="S144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -7966,7 +7966,7 @@
         <v>0</v>
       </c>
       <c r="S145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -8015,7 +8015,7 @@
         <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -8064,7 +8064,7 @@
         <v>0</v>
       </c>
       <c r="S147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -8113,7 +8113,7 @@
         <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -8162,7 +8162,7 @@
         <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -8211,7 +8211,7 @@
         <v>0</v>
       </c>
       <c r="S150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -8260,7 +8260,7 @@
         <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -8309,7 +8309,7 @@
         <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -8358,7 +8358,7 @@
         <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -8407,7 +8407,7 @@
         <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -8456,7 +8456,7 @@
         <v>0</v>
       </c>
       <c r="S155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -8505,7 +8505,7 @@
         <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -8554,7 +8554,7 @@
         <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -8603,7 +8603,7 @@
         <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -8652,7 +8652,7 @@
         <v>0</v>
       </c>
       <c r="S159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -8701,7 +8701,7 @@
         <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -8750,7 +8750,7 @@
         <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -8799,7 +8799,7 @@
         <v>0</v>
       </c>
       <c r="S162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -8848,7 +8848,7 @@
         <v>0</v>
       </c>
       <c r="S163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -8897,7 +8897,7 @@
         <v>0</v>
       </c>
       <c r="S164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -8946,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="S165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -8995,7 +8995,7 @@
         <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -9044,7 +9044,7 @@
         <v>0</v>
       </c>
       <c r="S167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -9093,7 +9093,7 @@
         <v>0</v>
       </c>
       <c r="S168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -9142,7 +9142,7 @@
         <v>0</v>
       </c>
       <c r="S169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -9191,7 +9191,7 @@
         <v>0</v>
       </c>
       <c r="S170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -9240,7 +9240,7 @@
         <v>0</v>
       </c>
       <c r="S171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -9289,7 +9289,7 @@
         <v>0</v>
       </c>
       <c r="S172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -9338,7 +9338,7 @@
         <v>0</v>
       </c>
       <c r="S173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -9387,7 +9387,7 @@
         <v>0</v>
       </c>
       <c r="S174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -9440,7 +9440,7 @@
         <v>0</v>
       </c>
       <c r="S175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -9493,7 +9493,7 @@
         <v>0</v>
       </c>
       <c r="S176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -9542,7 +9542,7 @@
         <v>0</v>
       </c>
       <c r="S177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -9591,7 +9591,7 @@
         <v>0</v>
       </c>
       <c r="S178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -9640,7 +9640,7 @@
         <v>0</v>
       </c>
       <c r="S179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="S180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -9738,7 +9738,7 @@
         <v>0</v>
       </c>
       <c r="S181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -9787,7 +9787,7 @@
         <v>0</v>
       </c>
       <c r="S182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -9836,7 +9836,7 @@
         <v>0</v>
       </c>
       <c r="S183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -9885,7 +9885,7 @@
         <v>0</v>
       </c>
       <c r="S184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -9934,7 +9934,7 @@
         <v>0</v>
       </c>
       <c r="S185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -9983,7 +9983,7 @@
         <v>0</v>
       </c>
       <c r="S186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -10032,7 +10032,7 @@
         <v>0</v>
       </c>
       <c r="S187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -10081,7 +10081,7 @@
         <v>0</v>
       </c>
       <c r="S188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="S189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -10179,7 +10179,7 @@
         <v>0</v>
       </c>
       <c r="S190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -10228,7 +10228,7 @@
         <v>0</v>
       </c>
       <c r="S191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -10277,7 +10277,7 @@
         <v>0</v>
       </c>
       <c r="S192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -10326,7 +10326,7 @@
         <v>0</v>
       </c>
       <c r="S193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="S194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -10424,7 +10424,7 @@
         <v>0</v>
       </c>
       <c r="S195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -10473,7 +10473,7 @@
         <v>0</v>
       </c>
       <c r="S196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -10522,7 +10522,7 @@
         <v>0</v>
       </c>
       <c r="S197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -10571,7 +10571,7 @@
         <v>0</v>
       </c>
       <c r="S198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -10620,7 +10620,7 @@
         <v>0</v>
       </c>
       <c r="S199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -10669,7 +10669,7 @@
         <v>0</v>
       </c>
       <c r="S200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -10718,7 +10718,7 @@
         <v>0</v>
       </c>
       <c r="S201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -10767,7 +10767,7 @@
         <v>0</v>
       </c>
       <c r="S202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -10816,7 +10816,7 @@
         <v>0</v>
       </c>
       <c r="S203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -10865,7 +10865,7 @@
         <v>0</v>
       </c>
       <c r="S204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -10914,7 +10914,7 @@
         <v>0</v>
       </c>
       <c r="S205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -10963,7 +10963,7 @@
         <v>0</v>
       </c>
       <c r="S206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -11012,7 +11012,7 @@
         <v>0</v>
       </c>
       <c r="S207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -11061,7 +11061,7 @@
         <v>0</v>
       </c>
       <c r="S208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -11110,7 +11110,7 @@
         <v>0</v>
       </c>
       <c r="S209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -11163,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="S210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -11216,7 +11216,7 @@
         <v>0</v>
       </c>
       <c r="S211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -11269,7 +11269,7 @@
         <v>0</v>
       </c>
       <c r="S212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -11322,7 +11322,7 @@
         <v>0</v>
       </c>
       <c r="S213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -11375,7 +11375,7 @@
         <v>0</v>
       </c>
       <c r="S214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -11428,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="S215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -11481,7 +11481,7 @@
         <v>0</v>
       </c>
       <c r="S216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -11534,7 +11534,7 @@
         <v>0</v>
       </c>
       <c r="S217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -11587,7 +11587,7 @@
         <v>0</v>
       </c>
       <c r="S218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -11640,7 +11640,7 @@
         <v>0</v>
       </c>
       <c r="S219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -11693,7 +11693,7 @@
         <v>0</v>
       </c>
       <c r="S220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -11746,7 +11746,7 @@
         <v>0</v>
       </c>
       <c r="S221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -11799,7 +11799,7 @@
         <v>0</v>
       </c>
       <c r="S222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -11852,7 +11852,7 @@
         <v>0</v>
       </c>
       <c r="S223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -11905,7 +11905,7 @@
         <v>0</v>
       </c>
       <c r="S224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -11958,7 +11958,7 @@
         <v>0</v>
       </c>
       <c r="S225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -12011,7 +12011,7 @@
         <v>0</v>
       </c>
       <c r="S226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -12064,7 +12064,7 @@
         <v>0</v>
       </c>
       <c r="S227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -12117,7 +12117,7 @@
         <v>0</v>
       </c>
       <c r="S228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -12166,7 +12166,7 @@
         <v>0</v>
       </c>
       <c r="S229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -12219,7 +12219,7 @@
         <v>0</v>
       </c>
       <c r="S230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -12272,7 +12272,7 @@
         <v>0</v>
       </c>
       <c r="S231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -12325,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="S232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -12378,7 +12378,7 @@
         <v>0</v>
       </c>
       <c r="S233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -12431,7 +12431,7 @@
         <v>0</v>
       </c>
       <c r="S234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -12484,7 +12484,7 @@
         <v>0</v>
       </c>
       <c r="S235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -12537,7 +12537,7 @@
         <v>0</v>
       </c>
       <c r="S236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -12590,7 +12590,7 @@
         <v>0</v>
       </c>
       <c r="S237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="S238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -12696,7 +12696,7 @@
         <v>0</v>
       </c>
       <c r="S239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -12749,7 +12749,7 @@
         <v>0</v>
       </c>
       <c r="S240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -12802,7 +12802,7 @@
         <v>0</v>
       </c>
       <c r="S241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -12855,7 +12855,7 @@
         <v>0</v>
       </c>
       <c r="S242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -12908,7 +12908,7 @@
         <v>0</v>
       </c>
       <c r="S243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -12961,7 +12961,7 @@
         <v>0</v>
       </c>
       <c r="S244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -13010,7 +13010,7 @@
         <v>0</v>
       </c>
       <c r="S245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -13059,7 +13059,7 @@
         <v>0</v>
       </c>
       <c r="S246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -13108,7 +13108,7 @@
         <v>0</v>
       </c>
       <c r="S247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -13161,7 +13161,7 @@
         <v>0</v>
       </c>
       <c r="S248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -13214,7 +13214,7 @@
         <v>0</v>
       </c>
       <c r="S249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -13263,7 +13263,7 @@
         <v>0</v>
       </c>
       <c r="S250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -13316,7 +13316,7 @@
         <v>0</v>
       </c>
       <c r="S251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -13365,7 +13365,7 @@
         <v>0</v>
       </c>
       <c r="S252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -13414,7 +13414,7 @@
         <v>0</v>
       </c>
       <c r="S253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -13467,7 +13467,7 @@
         <v>0</v>
       </c>
       <c r="S254" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -13520,7 +13520,7 @@
         <v>0</v>
       </c>
       <c r="S255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -13573,7 +13573,7 @@
         <v>0</v>
       </c>
       <c r="S256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -13626,7 +13626,7 @@
         <v>0</v>
       </c>
       <c r="S257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -13679,7 +13679,7 @@
         <v>0</v>
       </c>
       <c r="S258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -13732,7 +13732,7 @@
         <v>0</v>
       </c>
       <c r="S259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -13785,7 +13785,7 @@
         <v>0</v>
       </c>
       <c r="S260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -13834,7 +13834,7 @@
         <v>0</v>
       </c>
       <c r="S261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -13887,7 +13887,7 @@
         <v>0</v>
       </c>
       <c r="S262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -13940,7 +13940,7 @@
         <v>0</v>
       </c>
       <c r="S263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -13993,7 +13993,7 @@
         <v>0</v>
       </c>
       <c r="S264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -14046,7 +14046,7 @@
         <v>0</v>
       </c>
       <c r="S265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -14099,7 +14099,7 @@
         <v>0</v>
       </c>
       <c r="S266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -14152,7 +14152,7 @@
         <v>0</v>
       </c>
       <c r="S267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -14205,7 +14205,7 @@
         <v>0</v>
       </c>
       <c r="S268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -14258,7 +14258,7 @@
         <v>0</v>
       </c>
       <c r="S269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -14311,7 +14311,7 @@
         <v>0</v>
       </c>
       <c r="S270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -14364,7 +14364,7 @@
         <v>0</v>
       </c>
       <c r="S271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -14417,7 +14417,7 @@
         <v>0</v>
       </c>
       <c r="S272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -14470,7 +14470,7 @@
         <v>0</v>
       </c>
       <c r="S273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -14523,7 +14523,7 @@
         <v>0</v>
       </c>
       <c r="S274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -14576,7 +14576,7 @@
         <v>0</v>
       </c>
       <c r="S275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -14629,7 +14629,7 @@
         <v>0</v>
       </c>
       <c r="S276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -14682,7 +14682,7 @@
         <v>0</v>
       </c>
       <c r="S277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -14735,7 +14735,7 @@
         <v>0</v>
       </c>
       <c r="S278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -14788,7 +14788,7 @@
         <v>0</v>
       </c>
       <c r="S279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -14841,7 +14841,7 @@
         <v>0</v>
       </c>
       <c r="S280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
@@ -14894,7 +14894,7 @@
         <v>0</v>
       </c>
       <c r="S281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -14947,7 +14947,7 @@
         <v>0</v>
       </c>
       <c r="S282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -15000,7 +15000,7 @@
         <v>0</v>
       </c>
       <c r="S283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
@@ -15053,7 +15053,7 @@
         <v>0</v>
       </c>
       <c r="S284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -15106,7 +15106,7 @@
         <v>0</v>
       </c>
       <c r="S285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -15159,7 +15159,7 @@
         <v>0</v>
       </c>
       <c r="S286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -15212,7 +15212,7 @@
         <v>0</v>
       </c>
       <c r="S287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -15265,7 +15265,7 @@
         <v>0</v>
       </c>
       <c r="S288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -15318,7 +15318,7 @@
         <v>0</v>
       </c>
       <c r="S289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -15371,7 +15371,7 @@
         <v>0</v>
       </c>
       <c r="S290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -15424,7 +15424,7 @@
         <v>0</v>
       </c>
       <c r="S291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -15477,7 +15477,7 @@
         <v>0</v>
       </c>
       <c r="S292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -15530,7 +15530,7 @@
         <v>0</v>
       </c>
       <c r="S293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="S294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -15636,7 +15636,7 @@
         <v>0</v>
       </c>
       <c r="S295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -15689,7 +15689,7 @@
         <v>0</v>
       </c>
       <c r="S296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -15742,7 +15742,7 @@
         <v>0</v>
       </c>
       <c r="S297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -15795,7 +15795,7 @@
         <v>0</v>
       </c>
       <c r="S298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -15848,7 +15848,7 @@
         <v>0</v>
       </c>
       <c r="S299" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="S300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -15954,7 +15954,7 @@
         <v>0</v>
       </c>
       <c r="S301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -16007,7 +16007,7 @@
         <v>0</v>
       </c>
       <c r="S302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -16060,7 +16060,7 @@
         <v>0</v>
       </c>
       <c r="S303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -16113,7 +16113,7 @@
         <v>0</v>
       </c>
       <c r="S304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -16166,7 +16166,7 @@
         <v>0</v>
       </c>
       <c r="S305" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306">
@@ -16219,7 +16219,7 @@
         <v>0</v>
       </c>
       <c r="S306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307">
@@ -16272,7 +16272,7 @@
         <v>0</v>
       </c>
       <c r="S307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
@@ -16325,7 +16325,7 @@
         <v>0</v>
       </c>
       <c r="S308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
@@ -16378,7 +16378,7 @@
         <v>0</v>
       </c>
       <c r="S309" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
@@ -16431,7 +16431,7 @@
         <v>0</v>
       </c>
       <c r="S310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311">
@@ -16484,7 +16484,7 @@
         <v>0</v>
       </c>
       <c r="S311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -16537,7 +16537,7 @@
         <v>0</v>
       </c>
       <c r="S312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -16590,7 +16590,7 @@
         <v>0</v>
       </c>
       <c r="S313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -16643,7 +16643,7 @@
         <v>0</v>
       </c>
       <c r="S314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
@@ -16696,7 +16696,7 @@
         <v>0</v>
       </c>
       <c r="S315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -16749,7 +16749,7 @@
         <v>0</v>
       </c>
       <c r="S316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -16802,7 +16802,7 @@
         <v>0</v>
       </c>
       <c r="S317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -16855,7 +16855,7 @@
         <v>0</v>
       </c>
       <c r="S318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -16908,7 +16908,7 @@
         <v>0</v>
       </c>
       <c r="S319" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -16961,7 +16961,7 @@
         <v>0</v>
       </c>
       <c r="S320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -17014,7 +17014,7 @@
         <v>0</v>
       </c>
       <c r="S321" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
@@ -17067,7 +17067,7 @@
         <v>0</v>
       </c>
       <c r="S322" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -17120,7 +17120,7 @@
         <v>0</v>
       </c>
       <c r="S323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -17173,7 +17173,7 @@
         <v>0</v>
       </c>
       <c r="S324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
@@ -17226,7 +17226,7 @@
         <v>0</v>
       </c>
       <c r="S325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -17279,7 +17279,7 @@
         <v>0</v>
       </c>
       <c r="S326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -17332,7 +17332,7 @@
         <v>0</v>
       </c>
       <c r="S327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328">
@@ -17385,7 +17385,7 @@
         <v>0</v>
       </c>
       <c r="S328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
@@ -17438,7 +17438,7 @@
         <v>0</v>
       </c>
       <c r="S329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -17491,7 +17491,7 @@
         <v>0</v>
       </c>
       <c r="S330" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
@@ -17544,7 +17544,7 @@
         <v>0</v>
       </c>
       <c r="S331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
@@ -17597,7 +17597,7 @@
         <v>0</v>
       </c>
       <c r="S332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
@@ -17650,7 +17650,7 @@
         <v>0</v>
       </c>
       <c r="S333" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334">
@@ -17703,7 +17703,7 @@
         <v>0</v>
       </c>
       <c r="S334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
@@ -17756,7 +17756,7 @@
         <v>0</v>
       </c>
       <c r="S335" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
@@ -17809,7 +17809,7 @@
         <v>0</v>
       </c>
       <c r="S336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -17862,7 +17862,7 @@
         <v>0</v>
       </c>
       <c r="S337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -17915,7 +17915,7 @@
         <v>0</v>
       </c>
       <c r="S338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
@@ -17968,7 +17968,7 @@
         <v>0</v>
       </c>
       <c r="S339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340">
@@ -18021,7 +18021,7 @@
         <v>0</v>
       </c>
       <c r="S340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -18074,7 +18074,7 @@
         <v>0</v>
       </c>
       <c r="S341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
@@ -18127,7 +18127,7 @@
         <v>0</v>
       </c>
       <c r="S342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
@@ -18180,7 +18180,7 @@
         <v>0</v>
       </c>
       <c r="S343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="344">
@@ -18233,7 +18233,7 @@
         <v>0</v>
       </c>
       <c r="S344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345">
@@ -18286,7 +18286,7 @@
         <v>0</v>
       </c>
       <c r="S345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
@@ -18339,7 +18339,7 @@
         <v>0</v>
       </c>
       <c r="S346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347">
@@ -18392,7 +18392,7 @@
         <v>0</v>
       </c>
       <c r="S347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348">
@@ -18445,7 +18445,7 @@
         <v>0</v>
       </c>
       <c r="S348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349">
@@ -18498,7 +18498,7 @@
         <v>0</v>
       </c>
       <c r="S349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350">
@@ -18551,7 +18551,7 @@
         <v>0</v>
       </c>
       <c r="S350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351">
@@ -18604,7 +18604,7 @@
         <v>0</v>
       </c>
       <c r="S351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352">
@@ -18657,7 +18657,7 @@
         <v>0</v>
       </c>
       <c r="S352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353">
@@ -18710,7 +18710,7 @@
         <v>0</v>
       </c>
       <c r="S353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354">
@@ -18763,7 +18763,7 @@
         <v>0</v>
       </c>
       <c r="S354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -18816,7 +18816,7 @@
         <v>0</v>
       </c>
       <c r="S355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356">
@@ -18869,7 +18869,7 @@
         <v>0</v>
       </c>
       <c r="S356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
@@ -18918,7 +18918,7 @@
         <v>0</v>
       </c>
       <c r="S357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358">
@@ -18971,7 +18971,7 @@
         <v>0</v>
       </c>
       <c r="S358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359">
@@ -19020,7 +19020,7 @@
         <v>0</v>
       </c>
       <c r="S359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360">
@@ -19069,7 +19069,7 @@
         <v>0</v>
       </c>
       <c r="S360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361">
@@ -19118,7 +19118,7 @@
         <v>0</v>
       </c>
       <c r="S361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362">
@@ -19167,7 +19167,7 @@
         <v>0</v>
       </c>
       <c r="S362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363">
@@ -19216,7 +19216,7 @@
         <v>0</v>
       </c>
       <c r="S363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
@@ -19265,7 +19265,7 @@
         <v>0</v>
       </c>
       <c r="S364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="365">
@@ -19314,7 +19314,7 @@
         <v>0</v>
       </c>
       <c r="S365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366">
@@ -19363,7 +19363,7 @@
         <v>0</v>
       </c>
       <c r="S366" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367">
@@ -19412,7 +19412,7 @@
         <v>0</v>
       </c>
       <c r="S367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368">
@@ -19461,7 +19461,7 @@
         <v>0</v>
       </c>
       <c r="S368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="369">
@@ -19510,7 +19510,7 @@
         <v>0</v>
       </c>
       <c r="S369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370">
@@ -19559,7 +19559,7 @@
         <v>0</v>
       </c>
       <c r="S370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371">
@@ -19608,7 +19608,7 @@
         <v>0</v>
       </c>
       <c r="S371" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372">
@@ -19657,7 +19657,7 @@
         <v>0</v>
       </c>
       <c r="S372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
@@ -19706,7 +19706,7 @@
         <v>0</v>
       </c>
       <c r="S373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -19755,7 +19755,7 @@
         <v>0</v>
       </c>
       <c r="S374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="375">
@@ -19804,7 +19804,7 @@
         <v>0</v>
       </c>
       <c r="S375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="376">
@@ -19857,7 +19857,7 @@
         <v>0</v>
       </c>
       <c r="S376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="377">
@@ -19910,7 +19910,7 @@
         <v>0</v>
       </c>
       <c r="S377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="378">
@@ -19959,7 +19959,7 @@
         <v>0</v>
       </c>
       <c r="S378" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379">
@@ -20008,7 +20008,7 @@
         <v>0</v>
       </c>
       <c r="S379" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -20057,7 +20057,7 @@
         <v>0</v>
       </c>
       <c r="S380" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="381">
@@ -20110,7 +20110,7 @@
         <v>0</v>
       </c>
       <c r="S381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
@@ -20163,7 +20163,7 @@
         <v>0</v>
       </c>
       <c r="S382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
@@ -20216,7 +20216,7 @@
         <v>0</v>
       </c>
       <c r="S383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="384">
@@ -20269,7 +20269,7 @@
         <v>0</v>
       </c>
       <c r="S384" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385">
@@ -20322,7 +20322,7 @@
         <v>0</v>
       </c>
       <c r="S385" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="386">
@@ -20375,7 +20375,7 @@
         <v>0</v>
       </c>
       <c r="S386" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
@@ -20428,7 +20428,7 @@
         <v>0</v>
       </c>
       <c r="S387" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
@@ -20477,7 +20477,7 @@
         <v>0</v>
       </c>
       <c r="S388" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="389">
@@ -20530,7 +20530,7 @@
         <v>0</v>
       </c>
       <c r="S389" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="390">
@@ -20583,7 +20583,7 @@
         <v>0</v>
       </c>
       <c r="S390" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="391">
@@ -20636,7 +20636,7 @@
         <v>0</v>
       </c>
       <c r="S391" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392">
@@ -20689,7 +20689,7 @@
         <v>0</v>
       </c>
       <c r="S392" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393">
@@ -20742,7 +20742,7 @@
         <v>0</v>
       </c>
       <c r="S393" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="394">
@@ -20795,7 +20795,7 @@
         <v>0</v>
       </c>
       <c r="S394" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395">
@@ -20848,7 +20848,7 @@
         <v>0</v>
       </c>
       <c r="S395" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="396">
@@ -20901,7 +20901,7 @@
         <v>0</v>
       </c>
       <c r="S396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="397">
@@ -20954,7 +20954,7 @@
         <v>0</v>
       </c>
       <c r="S397" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398">
@@ -21003,7 +21003,7 @@
         <v>0</v>
       </c>
       <c r="S398" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="399">
@@ -21056,7 +21056,7 @@
         <v>0</v>
       </c>
       <c r="S399" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400">
@@ -21109,7 +21109,7 @@
         <v>0</v>
       </c>
       <c r="S400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401">
@@ -21162,7 +21162,7 @@
         <v>0</v>
       </c>
       <c r="S401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402">
@@ -21215,7 +21215,7 @@
         <v>0</v>
       </c>
       <c r="S402" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="403">
@@ -21268,7 +21268,7 @@
         <v>0</v>
       </c>
       <c r="S403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="404">
@@ -21321,7 +21321,7 @@
         <v>0</v>
       </c>
       <c r="S404" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="405">
@@ -21570,7 +21570,7 @@
         <v>0</v>
       </c>
       <c r="S409" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="410">
@@ -21602,7 +21602,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>매</t>
         </is>
       </c>
       <c r="N410" t="inlineStr"/>
@@ -21660,7 +21660,7 @@
         <v>0</v>
       </c>
       <c r="S411" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="412">
@@ -21893,7 +21893,7 @@
         <v>0</v>
       </c>
       <c r="S416" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="417">
@@ -22469,7 +22469,7 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B428" t="inlineStr"/>
       <c r="C428" t="inlineStr"/>
@@ -22490,7 +22490,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>자동등록</t>
+          <t>수정등록</t>
         </is>
       </c>
       <c r="H428" t="inlineStr"/>
@@ -22517,12 +22517,12 @@
         <v>0</v>
       </c>
       <c r="S428" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B429" t="inlineStr"/>
       <c r="C429" t="inlineStr"/>
@@ -22575,13 +22575,13 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B430" t="inlineStr"/>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
-          <t>PAUT SCANNER(MANUAL)</t>
+          <t>MT약품</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -22591,12 +22591,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>PAUT SCANNER(MANUAL)</t>
+          <t>흑색자분</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>수정등록</t>
+          <t>자동등록</t>
         </is>
       </c>
       <c r="H430" t="inlineStr"/>
@@ -22623,12 +22623,12 @@
         <v>0</v>
       </c>
       <c r="S430" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B431" t="inlineStr"/>
       <c r="C431" t="inlineStr"/>
@@ -22644,7 +22644,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>흑색자분</t>
+          <t>백색페인트</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -22681,7 +22681,7 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B432" t="inlineStr"/>
       <c r="C432" t="inlineStr"/>
@@ -22690,14 +22690,10 @@
           <t>MT약품</t>
         </is>
       </c>
-      <c r="E432" t="inlineStr">
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr">
         <is>
           <t>현장</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>백색페인트</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
@@ -22734,19 +22730,23 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B433" t="inlineStr"/>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>MT약품</t>
-        </is>
-      </c>
-      <c r="E433" t="inlineStr"/>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>432</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
@@ -22778,12 +22778,12 @@
         <v>0</v>
       </c>
       <c r="S433" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B434" t="inlineStr"/>
       <c r="C434" t="inlineStr"/>
@@ -22836,7 +22836,7 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B435" t="inlineStr"/>
       <c r="C435" t="inlineStr"/>
@@ -22889,7 +22889,7 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B436" t="inlineStr"/>
       <c r="C436" t="inlineStr"/>
@@ -22942,13 +22942,13 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B437" t="inlineStr"/>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>405</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -22958,7 +22958,7 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>405</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
@@ -22994,33 +22994,27 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" t="n">
-        <v>439</v>
-      </c>
+      <c r="A438" t="inlineStr"/>
       <c r="B438" t="inlineStr"/>
       <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr">
         <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>자동등록</t>
-        </is>
-      </c>
-      <c r="H438" t="inlineStr"/>
-      <c r="I438" t="inlineStr"/>
+          <t>Carestream AA400-10*12"</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>FILM</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Carestream</t>
+        </is>
+      </c>
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="n">
         <v>0</v>
@@ -23030,7 +23024,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>매</t>
         </is>
       </c>
       <c r="N438" t="inlineStr"/>
@@ -23052,22 +23046,14 @@
       <c r="C439" t="inlineStr"/>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Carestream AA400-10*12"</t>
+          <t>Carestream M100-10*12"</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr"/>
-      <c r="H439" t="inlineStr">
-        <is>
-          <t>FILM</t>
-        </is>
-      </c>
-      <c r="I439" t="inlineStr">
-        <is>
-          <t>Carestream</t>
-        </is>
-      </c>
+      <c r="H439" t="inlineStr"/>
+      <c r="I439" t="inlineStr"/>
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="n">
         <v>0</v>
@@ -23075,11 +23061,7 @@
       <c r="L439" t="n">
         <v>0</v>
       </c>
-      <c r="M439" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
+      <c r="M439" t="inlineStr"/>
       <c r="N439" t="inlineStr"/>
       <c r="O439" t="inlineStr"/>
       <c r="P439" t="inlineStr"/>
@@ -23090,7 +23072,7 @@
         <v>0</v>
       </c>
       <c r="S439" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440">
@@ -23099,7 +23081,7 @@
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Carestream M100-10*12"</t>
+          <t>Carestream MX125-3⅓*6"</t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
@@ -23125,7 +23107,7 @@
         <v>0</v>
       </c>
       <c r="S440" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="441">
@@ -23134,7 +23116,7 @@
       <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Carestream MX125-3⅓*6"</t>
+          <t>Carestream MX125-4½*12"</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
@@ -23160,7 +23142,7 @@
         <v>0</v>
       </c>
       <c r="S441" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="442">
@@ -23169,7 +23151,7 @@
       <c r="C442" t="inlineStr"/>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Carestream MX125-4½*12"</t>
+          <t>Carestream MX125-14*17"</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
@@ -23195,7 +23177,7 @@
         <v>0</v>
       </c>
       <c r="S442" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443">
@@ -23204,7 +23186,7 @@
       <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Carestream MX125-14*17"</t>
+          <t>Carestream T200-4½*12"</t>
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
@@ -23230,7 +23212,7 @@
         <v>0</v>
       </c>
       <c r="S443" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="444">
@@ -23239,7 +23221,7 @@
       <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Carestream T200-4½*12"</t>
+          <t>Carestream T200-14*17"</t>
         </is>
       </c>
       <c r="E444" t="inlineStr"/>
@@ -23265,23 +23247,33 @@
         <v>0</v>
       </c>
       <c r="S444" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="445">
-      <c r="A445" t="inlineStr"/>
+      <c r="A445" t="n">
+        <v>440</v>
+      </c>
       <c r="B445" t="inlineStr"/>
       <c r="C445" t="inlineStr"/>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Carestream T200-14*17"</t>
+          <t>MT약품</t>
         </is>
       </c>
       <c r="E445" t="inlineStr"/>
-      <c r="F445" t="inlineStr"/>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>백색페인트</t>
+        </is>
+      </c>
       <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr"/>
-      <c r="I445" t="inlineStr"/>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>NAWOO</t>
+        </is>
+      </c>
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="n">
         <v>0</v>
@@ -23289,7 +23281,11 @@
       <c r="L445" t="n">
         <v>0</v>
       </c>
-      <c r="M445" t="inlineStr"/>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
       <c r="N445" t="inlineStr"/>
       <c r="O445" t="inlineStr"/>
       <c r="P445" t="inlineStr"/>
@@ -23305,19 +23301,19 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B446" t="inlineStr"/>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr">
         <is>
-          <t>MT약품</t>
+          <t>PT약품</t>
         </is>
       </c>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr">
         <is>
-          <t>백색페인트</t>
+          <t>세척제</t>
         </is>
       </c>
       <c r="G446" t="inlineStr"/>
@@ -23349,33 +23345,29 @@
         <v>0</v>
       </c>
       <c r="S446" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B447" t="inlineStr"/>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr">
         <is>
-          <t>PT약품</t>
+          <t>MT약품</t>
         </is>
       </c>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="inlineStr">
         <is>
-          <t>세척제</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr"/>
-      <c r="I447" t="inlineStr">
-        <is>
-          <t>NAWOO</t>
-        </is>
-      </c>
+      <c r="I447" t="inlineStr"/>
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="n">
         <v>0</v>
@@ -23385,7 +23377,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="N447" t="inlineStr"/>
@@ -23398,18 +23390,18 @@
         <v>0</v>
       </c>
       <c r="S447" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B448" t="inlineStr"/>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr">
         <is>
-          <t>MT약품</t>
+          <t>PT약품</t>
         </is>
       </c>
       <c r="E448" t="inlineStr"/>
@@ -23443,26 +23435,22 @@
         <v>0</v>
       </c>
       <c r="S448" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B449" t="inlineStr"/>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
         <is>
-          <t>PT약품</t>
+          <t>PAUT SCANNER(MANUAL)</t>
         </is>
       </c>
       <c r="E449" t="inlineStr"/>
-      <c r="F449" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F449" t="inlineStr"/>
       <c r="G449" t="inlineStr"/>
       <c r="H449" t="inlineStr"/>
       <c r="I449" t="inlineStr"/>
@@ -23488,23 +23476,27 @@
         <v>0</v>
       </c>
       <c r="S449" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B450" t="inlineStr"/>
       <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>PAUT SCANNER(MANUAL)</t>
-        </is>
-      </c>
-      <c r="E450" t="inlineStr"/>
+      <c r="D450" t="inlineStr"/>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
       <c r="F450" t="inlineStr"/>
-      <c r="G450" t="inlineStr"/>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
       <c r="H450" t="inlineStr"/>
       <c r="I450" t="inlineStr"/>
       <c r="J450" t="inlineStr"/>
@@ -23526,7 +23518,7 @@
         <v>0</v>
       </c>
       <c r="R450" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S450" t="n">
         <v>1</v>
@@ -23534,20 +23526,28 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B451" t="inlineStr"/>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>PT약품</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
           <t>현장</t>
         </is>
       </c>
-      <c r="F451" t="inlineStr"/>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>PT약품</t>
+        </is>
+      </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>자동등록</t>
+          <t>수정등록</t>
         </is>
       </c>
       <c r="H451" t="inlineStr"/>
@@ -23574,12 +23574,12 @@
         <v>10</v>
       </c>
       <c r="S451" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B452" t="inlineStr"/>
       <c r="C452" t="inlineStr"/>
@@ -23600,7 +23600,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>수정등록</t>
+          <t>자동등록</t>
         </is>
       </c>
       <c r="H452" t="inlineStr"/>
@@ -23627,18 +23627,18 @@
         <v>10</v>
       </c>
       <c r="S452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B453" t="inlineStr"/>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>PT약품</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -23648,7 +23648,7 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>PT약품</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
@@ -23685,7 +23685,7 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B454" t="inlineStr"/>
       <c r="C454" t="inlineStr"/>
@@ -23706,7 +23706,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>자동등록</t>
+          <t>수정등록</t>
         </is>
       </c>
       <c r="H454" t="inlineStr"/>
@@ -23733,12 +23733,12 @@
         <v>10</v>
       </c>
       <c r="S454" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B455" t="inlineStr"/>
       <c r="C455" t="inlineStr"/>
@@ -23791,30 +23791,22 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B456" t="inlineStr"/>
       <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr">
         <is>
-          <t>PT약품</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
+          <t>PAUT 장비</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr"/>
       <c r="F456" t="inlineStr">
         <is>
-          <t>PT약품</t>
-        </is>
-      </c>
-      <c r="G456" t="inlineStr">
-        <is>
-          <t>수정등록</t>
-        </is>
-      </c>
+          <t>MX2</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr"/>
       <c r="H456" t="inlineStr"/>
       <c r="I456" t="inlineStr"/>
       <c r="J456" t="inlineStr"/>
@@ -23836,7 +23828,7 @@
         <v>0</v>
       </c>
       <c r="R456" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S456" t="n">
         <v>0</v>
@@ -23844,30 +23836,22 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B457" t="inlineStr"/>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
+          <t>PAUT장비</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr"/>
       <c r="F457" t="inlineStr">
         <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="G457" t="inlineStr">
-        <is>
-          <t>자동등록</t>
-        </is>
-      </c>
+          <t>MX2</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr"/>
       <c r="H457" t="inlineStr"/>
       <c r="I457" t="inlineStr"/>
       <c r="J457" t="inlineStr"/>
@@ -23889,7 +23873,7 @@
         <v>0</v>
       </c>
       <c r="R457" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S457" t="n">
         <v>1</v>
@@ -23897,7 +23881,7 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B458" t="inlineStr"/>
       <c r="C458" t="inlineStr"/>
@@ -23945,6 +23929,218 @@
         <v>10</v>
       </c>
       <c r="S458" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>456</v>
+      </c>
+      <c r="B459" t="inlineStr"/>
+      <c r="C459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Carestream AA400-10*12"</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Carestream AA400-10*12"</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr"/>
+      <c r="I459" t="inlineStr"/>
+      <c r="J459" t="inlineStr"/>
+      <c r="K459" t="n">
+        <v>0</v>
+      </c>
+      <c r="L459" t="n">
+        <v>0</v>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr"/>
+      <c r="O459" t="inlineStr"/>
+      <c r="P459" t="inlineStr"/>
+      <c r="Q459" t="n">
+        <v>0</v>
+      </c>
+      <c r="R459" t="n">
+        <v>10</v>
+      </c>
+      <c r="S459" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>457</v>
+      </c>
+      <c r="B460" t="inlineStr"/>
+      <c r="C460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Carestream T200-4½*12"</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Carestream T200-4½*12"</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr"/>
+      <c r="I460" t="inlineStr"/>
+      <c r="J460" t="inlineStr"/>
+      <c r="K460" t="n">
+        <v>0</v>
+      </c>
+      <c r="L460" t="n">
+        <v>0</v>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr"/>
+      <c r="O460" t="inlineStr"/>
+      <c r="P460" t="inlineStr"/>
+      <c r="Q460" t="n">
+        <v>0</v>
+      </c>
+      <c r="R460" t="n">
+        <v>10</v>
+      </c>
+      <c r="S460" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>458</v>
+      </c>
+      <c r="B461" t="inlineStr"/>
+      <c r="C461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Carestream MX125-10*12"</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Carestream MX125-10*12"</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr"/>
+      <c r="I461" t="inlineStr"/>
+      <c r="J461" t="inlineStr"/>
+      <c r="K461" t="n">
+        <v>0</v>
+      </c>
+      <c r="L461" t="n">
+        <v>0</v>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr"/>
+      <c r="O461" t="inlineStr"/>
+      <c r="P461" t="inlineStr"/>
+      <c r="Q461" t="n">
+        <v>0</v>
+      </c>
+      <c r="R461" t="n">
+        <v>10</v>
+      </c>
+      <c r="S461" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>459</v>
+      </c>
+      <c r="B462" t="inlineStr"/>
+      <c r="C462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Carestream MX125-3⅓*6"</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Carestream MX125-3⅓*6"</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr"/>
+      <c r="I462" t="inlineStr"/>
+      <c r="J462" t="inlineStr"/>
+      <c r="K462" t="n">
+        <v>0</v>
+      </c>
+      <c r="L462" t="n">
+        <v>0</v>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr"/>
+      <c r="O462" t="inlineStr"/>
+      <c r="P462" t="inlineStr"/>
+      <c r="Q462" t="n">
+        <v>0</v>
+      </c>
+      <c r="R462" t="n">
+        <v>10</v>
+      </c>
+      <c r="S462" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23959,7 +24155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24081,10 +24277,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46142</v>
+        <v>45778</v>
       </c>
       <c r="B2" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -24092,7 +24288,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -24101,7 +24297,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>부장 주진철, 대리 우명광</t>
+          <t>부장 주진철</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -24109,10 +24305,26 @@
           <t>K1-PJT</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠김|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠김</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -24125,6 +24337,147 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B3" t="n">
+        <v>408</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-100</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>K1-PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B4" t="n">
+        <v>410</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>K1-PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B5" t="n">
+        <v>406</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>K1-PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24198,7 +24551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC2"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24494,123 +24847,118 @@
       </c>
       <c r="BG1" t="inlineStr">
         <is>
+          <t>차량번호</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>주행거리</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>차량점검</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>차량비고</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>품목명</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>RTK_총계</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>회사코드</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>업체명</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>작업자</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>작업시간</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>OT시간</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>OT금액</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>입력시간</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>(Full작업자)</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>RTK_RTK총계</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>검사품명</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>적용코드</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>성적서번호</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>검사자</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
           <t>수량</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>차량번호</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>주행거리</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>차량점검</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>차량비고</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>품목명</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
-        <is>
-          <t>RTK_총계</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>회사코드</t>
-        </is>
-      </c>
-      <c r="BO1" t="inlineStr">
-        <is>
-          <t>업체명</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>날짜</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>작업자</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>작업시간</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>OT시간</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>OT금액</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
-        <is>
-          <t>입력시간</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>(Full작업자)</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>RTK_RTK총계</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>검사품명</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>적용코드</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>성적서번호</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>검사자</t>
-        </is>
-      </c>
-      <c r="CC1" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>46142</v>
+      <c r="A2" s="1" t="n">
+        <v>45778</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -24618,14 +24966,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="1" t="n">
-        <v>46142.73948270857</v>
+        <v>46145.8297972338</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -24655,11 +25003,11 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>R-RAY</t>
+          <t>R-RAY(Se-75)</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q2" t="n">
         <v>25500</v>
@@ -24671,7 +25019,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1275000</v>
+        <v>2550000</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -24686,50 +25034,54 @@
           <t>(주야간) 09:00~24:00</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>26,000</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>대리 우명광</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>(주야간) 09:00~24:00</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>26,000</t>
-        </is>
+      <c r="X2" t="n">
+        <v>26000</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>0</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
@@ -24751,59 +25103,724 @@
       <c r="BF2" t="n">
         <v>0</v>
       </c>
-      <c r="BG2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>스타렉스95가0200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:양호|out_locking:잠김|in_exterior:양호|in_cleanliness:양호|in_cleaning:양호|in_locking:잠김|photo_path:c:\Users\-\OneDrive\바탕 화면\home\data\vehicle_photos\스타렉스81루5100_1777538644.jpg</t>
-        </is>
-      </c>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠김|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠김</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="n">
+      <c r="BL2" t="n">
         <v>2</v>
       </c>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr">
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>롯데건설</t>
         </is>
       </c>
+      <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr"/>
       <c r="BQ2" t="inlineStr"/>
       <c r="BR2" t="inlineStr"/>
       <c r="BS2" t="inlineStr"/>
       <c r="BT2" t="inlineStr"/>
       <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
-      <c r="BW2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
       <c r="BX2" t="inlineStr"/>
-      <c r="BY2" t="inlineStr">
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>Carestream AA400-3⅓*12"</t>
+        </is>
+      </c>
+      <c r="CB2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>408</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>46146.72261082809</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr">
         <is>
           <t>PIPE</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>ASME B31.3</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr"/>
-      <c r="CB2" t="inlineStr"/>
-      <c r="CC2" t="inlineStr">
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>매</t>
         </is>
       </c>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>410</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>46146.72330495642</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>406</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>46146.72381588227</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S462"/>
+  <dimension ref="A1:S464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24141,6 +24141,112 @@
         <v>10</v>
       </c>
       <c r="S462" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>460</v>
+      </c>
+      <c r="B463" t="inlineStr"/>
+      <c r="C463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Carestream M100-10*12"</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Carestream M100-10*12"</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr"/>
+      <c r="I463" t="inlineStr"/>
+      <c r="J463" t="inlineStr"/>
+      <c r="K463" t="n">
+        <v>0</v>
+      </c>
+      <c r="L463" t="n">
+        <v>0</v>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr"/>
+      <c r="O463" t="inlineStr"/>
+      <c r="P463" t="inlineStr"/>
+      <c r="Q463" t="n">
+        <v>0</v>
+      </c>
+      <c r="R463" t="n">
+        <v>10</v>
+      </c>
+      <c r="S463" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>461</v>
+      </c>
+      <c r="B464" t="inlineStr"/>
+      <c r="C464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Carestream MX125-10*12"</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Carestream MX125-10*12"</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr"/>
+      <c r="I464" t="inlineStr"/>
+      <c r="J464" t="inlineStr"/>
+      <c r="K464" t="n">
+        <v>0</v>
+      </c>
+      <c r="L464" t="n">
+        <v>0</v>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr"/>
+      <c r="O464" t="inlineStr"/>
+      <c r="P464" t="inlineStr"/>
+      <c r="Q464" t="n">
+        <v>0</v>
+      </c>
+      <c r="R464" t="n">
+        <v>10</v>
+      </c>
+      <c r="S464" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24155,7 +24261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24312,12 +24418,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠김|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠김</t>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -24343,7 +24449,7 @@
         <v>45778</v>
       </c>
       <c r="B3" t="n">
-        <v>408</v>
+        <v>460</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -24368,10 +24474,26 @@
           <t>K1-PJT</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -24390,7 +24512,7 @@
         <v>45778</v>
       </c>
       <c r="B4" t="n">
-        <v>410</v>
+        <v>461</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -24432,53 +24554,6 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B5" t="n">
-        <v>406</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>-100</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>K1-PJT 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24551,7 +24626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24966,20 +25041,20 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D2" t="n">
         <v>100</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="1" t="n">
-        <v>46145.8297972338</v>
+        <v>46146.72261083333</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -25029,14 +25104,8 @@
       <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>(주야간) 09:00~24:00</t>
-        </is>
-      </c>
-      <c r="X2" t="n">
-        <v>26000</v>
-      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
@@ -25108,20 +25177,16 @@
           <t>스타렉스91주8839</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠김|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠김</t>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="inlineStr">
@@ -25153,17 +25218,13 @@
           <t>매</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>Carestream AA400-3⅓*12"</t>
-        </is>
-      </c>
+      <c r="CA2" t="inlineStr"/>
       <c r="CB2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -25172,18 +25233,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D3" t="n">
         <v>100</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" s="1" t="n">
-        <v>46146.72261082809</v>
+        <v>46146.7233049537</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -25243,66 +25300,48 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA3" t="n">
+        <v>0</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AD3" t="n">
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AG3" t="n">
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AJ3" t="n">
+        <v>0</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AS3" t="n">
+        <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AV3" t="n">
+        <v>0</v>
       </c>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY3" t="n">
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -25341,11 +25380,7 @@
       <c r="BL3" t="n">
         <v>0</v>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="inlineStr">
         <is>
           <t>롯데건설</t>
@@ -25368,11 +25403,7 @@
           <t>ASME B31.3</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="inlineStr">
         <is>
@@ -25380,10 +25411,12 @@
         </is>
       </c>
       <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="inlineStr"/>
+      <c r="CB3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -25392,18 +25425,14 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D4" t="n">
         <v>100</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" s="1" t="n">
-        <v>46146.72330495642</v>
+        <v>46146.72381587963</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -25463,66 +25492,48 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA4" t="n">
+        <v>0</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AD4" t="n">
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AG4" t="n">
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AJ4" t="n">
+        <v>0</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>0</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP4" t="n">
+        <v>0</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AS4" t="n">
+        <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AV4" t="n">
+        <v>0</v>
       </c>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY4" t="n">
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -25561,11 +25572,7 @@
       <c r="BL4" t="n">
         <v>0</v>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="inlineStr">
         <is>
           <t>롯데건설</t>
@@ -25588,11 +25595,7 @@
           <t>ASME B31.3</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="inlineStr">
         <is>
@@ -25600,10 +25603,12 @@
         </is>
       </c>
       <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="inlineStr"/>
+      <c r="CB4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -25612,18 +25617,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D5" t="n">
         <v>100</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" s="1" t="n">
-        <v>46146.72381588227</v>
+        <v>46147.20053241898</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -25683,66 +25684,48 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA5" t="n">
+        <v>0</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AD5" t="n">
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AG5" t="n">
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AJ5" t="n">
+        <v>0</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>0</v>
       </c>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP5" t="n">
+        <v>0</v>
       </c>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AS5" t="n">
+        <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AV5" t="n">
+        <v>0</v>
       </c>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY5" t="n">
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -25781,11 +25764,7 @@
       <c r="BL5" t="n">
         <v>0</v>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="inlineStr">
         <is>
           <t>롯데건설</t>
@@ -25808,11 +25787,7 @@
           <t>ASME B31.3</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="inlineStr">
         <is>
@@ -25820,7 +25795,421 @@
         </is>
       </c>
       <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="inlineStr"/>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>460</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="1" t="n">
+        <v>46147.2070821875</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>461</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>46147.22702630058</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -21,11 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -56,10 +54,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -24109,10 +24106,26 @@
           <t>K1-PJT</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>스타렉스95가0200</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:양호|out_locking:잠김|in_exterior:양호|in_cleanliness:양호|in_cleaning:양호|in_locking:잠김|photo_path:c:\Users\-\OneDrive\바탕 화면\home\data\vehicle_photos\스타렉스81루5100_1777538644.jpg</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -24609,7 +24622,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>46142</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -24625,7 +24638,7 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="1" t="n">
-        <v>46142.73948270857</v>
+        <v>46142.73948270833</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -24751,7 +24764,9 @@
       <c r="BF2" t="n">
         <v>0</v>
       </c>
-      <c r="BG2" t="inlineStr"/>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
       <c r="BH2" t="inlineStr">
         <is>
           <t>스타렉스95가0200</t>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -9,10 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,11 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -56,10 +53,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -21374,7 +21370,7 @@
         <v>0</v>
       </c>
       <c r="S405" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -21427,7 +21423,7 @@
         <v>1000</v>
       </c>
       <c r="S406" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407">
@@ -21480,7 +21476,7 @@
         <v>0</v>
       </c>
       <c r="S407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408">
@@ -21525,7 +21521,7 @@
         <v>0</v>
       </c>
       <c r="S408" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="409">
@@ -21615,7 +21611,7 @@
         <v>0</v>
       </c>
       <c r="S410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411">
@@ -21720,11 +21716,7 @@
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr">
         <is>
@@ -21814,11 +21806,7 @@
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr">
         <is>
@@ -21942,7 +21930,7 @@
         <v>0</v>
       </c>
       <c r="S417" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="418">
@@ -21991,7 +21979,7 @@
         <v>0</v>
       </c>
       <c r="S418" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="419">
@@ -22040,7 +22028,7 @@
         <v>0</v>
       </c>
       <c r="S419" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420">
@@ -22358,7 +22346,7 @@
         <v>0</v>
       </c>
       <c r="S425" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426">
@@ -22411,7 +22399,7 @@
         <v>0</v>
       </c>
       <c r="S426" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="427">
@@ -22464,7 +22452,7 @@
         <v>0</v>
       </c>
       <c r="S427" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="428">
@@ -22623,7 +22611,7 @@
         <v>0</v>
       </c>
       <c r="S430" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="431">
@@ -22676,7 +22664,7 @@
         <v>0</v>
       </c>
       <c r="S431" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="432">
@@ -22725,7 +22713,7 @@
         <v>0</v>
       </c>
       <c r="S432" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="433">
@@ -23296,7 +23284,7 @@
         <v>0</v>
       </c>
       <c r="S445" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="446">
@@ -23360,11 +23348,7 @@
         </is>
       </c>
       <c r="E447" t="inlineStr"/>
-      <c r="F447" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F447" t="inlineStr"/>
       <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr"/>
       <c r="I447" t="inlineStr"/>
@@ -23405,11 +23389,7 @@
         </is>
       </c>
       <c r="E448" t="inlineStr"/>
-      <c r="F448" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr"/>
       <c r="I448" t="inlineStr"/>
@@ -23521,7 +23501,7 @@
         <v>10</v>
       </c>
       <c r="S450" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="451">
@@ -23627,7 +23607,7 @@
         <v>10</v>
       </c>
       <c r="S452" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453">
@@ -23680,7 +23660,7 @@
         <v>10</v>
       </c>
       <c r="S453" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="454">
@@ -23786,7 +23766,7 @@
         <v>10</v>
       </c>
       <c r="S455" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="456">
@@ -23876,7 +23856,7 @@
         <v>0</v>
       </c>
       <c r="S457" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="458">
@@ -23929,7 +23909,7 @@
         <v>10</v>
       </c>
       <c r="S458" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="459">
@@ -23982,7 +23962,7 @@
         <v>10</v>
       </c>
       <c r="S459" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="460">
@@ -24035,7 +24015,7 @@
         <v>10</v>
       </c>
       <c r="S460" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="461">
@@ -24088,7 +24068,7 @@
         <v>10</v>
       </c>
       <c r="S461" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="462">
@@ -24141,7 +24121,7 @@
         <v>10</v>
       </c>
       <c r="S462" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="463">
@@ -24194,7 +24174,7 @@
         <v>10</v>
       </c>
       <c r="S463" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="464">
@@ -24247,7 +24227,7 @@
         <v>10</v>
       </c>
       <c r="S464" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -24416,21 +24396,13 @@
           <t>스타렉스91주8839</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -24479,21 +24451,13 @@
           <t>스타렉스91주8839</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -24565,54 +24529,1561 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Material ID</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Site</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>MaterialID</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Site</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>EntryTime</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Entry Date</t>
+          <t>RTK_센터미스</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>MaterialID</t>
+          <t>RTK_농도</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>EntryDate</t>
-        </is>
+          <t>RTK_마킹미스</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>RTK_필름마크</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>RTK_취급부주의</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>RTK_고객불만</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>RTK_기타</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>장비명</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>검사량</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>단가</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>출장비</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>일식</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>검사비</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>검사방법</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>FilmCount</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>WorkTime</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>OT</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>User2</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>WorkTime2</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>OT2</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>User3</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>WorkTime3</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>OT3</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>User4</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>WorkTime4</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>OT4</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>User5</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>WorkTime5</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>OT5</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>User6</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>WorkTime6</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>OT6</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>User7</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>WorkTime7</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>OT7</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>User8</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>WorkTime8</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>OT8</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>User9</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>WorkTime9</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>OT9</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>User10</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>WorkTime10</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>OT10</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>NDT_형광자분</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>NDT_흑색자분</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>NDT_백색페인트</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>NDT_침투제</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>NDT_세척제</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>NDT_현상제</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>NDT_형광침투제</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>차량번호</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>주행거리</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>차량점검</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>차량비고</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>품목명</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>RTK_총계</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>회사코드</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>업체명</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>작업자</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>작업시간</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>OT시간</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>OT금액</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>입력시간</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>(Full작업자)</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>RTK_RTK총계</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>검사품명</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>적용코드</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>성적서번호</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>검사자</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>408</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="1" t="n">
+        <v>46146.72261083333</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>410</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="1" t="n">
+        <v>46146.7233049537</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>406</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" s="1" t="n">
+        <v>46146.72381587963</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>405</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" s="1" t="n">
+        <v>46147.20053241898</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>460</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="1" t="n">
+        <v>46147.2070821875</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>461</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" s="1" t="n">
+        <v>46147.2270262963</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -24626,1590 +26097,70 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Site</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Site</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>MaterialID</t>
+          <t>LaborCost</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>MaterialCost</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>OutsourceCost</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>EntryTime</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>RTK_센터미스</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>RTK_농도</t>
-        </is>
-      </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>RTK_마킹미스</t>
+          <t>LaborDetail</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>RTK_필름마크</t>
+          <t>MaterialDetail</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>RTK_취급부주의</t>
+          <t>ExpenseDetail</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>RTK_고객불만</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>RTK_기타</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>장비명</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>검사량</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>단가</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>출장비</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>일식</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>검사비</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>검사방법</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>FilmCount</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>WorkTime</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>OT</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>User2</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>WorkTime2</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>OT2</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>User3</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>WorkTime3</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>OT3</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>User4</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>WorkTime4</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>OT4</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>User5</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>WorkTime5</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>OT5</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>User6</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>WorkTime6</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>OT6</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>User7</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>WorkTime7</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>OT7</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>User8</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>WorkTime8</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>OT8</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>User9</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>WorkTime9</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>OT9</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>User10</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>WorkTime10</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>OT10</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>NDT_형광자분</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>NDT_흑색자분</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>NDT_백색페인트</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>NDT_침투제</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>NDT_세척제</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>NDT_현상제</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>NDT_형광침투제</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>차량번호</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>주행거리</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>차량점검</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>차량비고</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>품목명</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>RTK_총계</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
-        <is>
-          <t>회사코드</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>업체명</t>
-        </is>
-      </c>
-      <c r="BO1" t="inlineStr">
-        <is>
-          <t>작업자</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>작업시간</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>OT시간</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>OT금액</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>입력시간</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>(Full작업자)</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>RTK_RTK총계</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
-        <is>
-          <t>검사품명</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>적용코드</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>성적서번호</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>검사자</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>408</v>
-      </c>
-      <c r="D2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="1" t="n">
-        <v>46146.72261083333</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>R-RAY(Se-75)</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr"/>
-      <c r="BY2" t="inlineStr"/>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr"/>
-      <c r="CB2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>410</v>
-      </c>
-      <c r="D3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" s="1" t="n">
-        <v>46146.7233049537</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>R-RAY(Se-75)</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>406</v>
-      </c>
-      <c r="D4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" s="1" t="n">
-        <v>46146.72381587963</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>R-RAY(Se-75)</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr"/>
-      <c r="BY4" t="inlineStr"/>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>405</v>
-      </c>
-      <c r="D5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" s="1" t="n">
-        <v>46147.20053241898</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>R-RAY(Se-75)</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr"/>
-      <c r="BY5" t="inlineStr"/>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>460</v>
-      </c>
-      <c r="D6" t="n">
-        <v>100</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" s="1" t="n">
-        <v>46147.2070821875</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>R-RAY(Se-75)</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr"/>
-      <c r="BY6" t="inlineStr"/>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr"/>
-      <c r="CB6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>461</v>
-      </c>
-      <c r="D7" t="n">
-        <v>100</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>46147.22702630058</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>R-RAY(Se-75)</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr"/>
-      <c r="BR7" t="inlineStr"/>
-      <c r="BS7" t="inlineStr"/>
-      <c r="BT7" t="inlineStr"/>
-      <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr"/>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr"/>
-      <c r="CB7" t="inlineStr"/>
+          <t>UnitPrice</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26222,82 +26173,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>LaborCost</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>MaterialCost</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>OutsourceCost</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Profit</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>LaborDetail</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>MaterialDetail</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ExpenseDetail</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>UnitPrice</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/data/Material_Inventory.xlsx
+++ b/data/Material_Inventory.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21716,7 +21717,11 @@
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr">
         <is>
@@ -21806,7 +21811,11 @@
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr">
         <is>
@@ -23348,7 +23357,11 @@
         </is>
       </c>
       <c r="E447" t="inlineStr"/>
-      <c r="F447" t="inlineStr"/>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr"/>
       <c r="I447" t="inlineStr"/>
@@ -23389,7 +23402,11 @@
         </is>
       </c>
       <c r="E448" t="inlineStr"/>
-      <c r="F448" t="inlineStr"/>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr"/>
       <c r="I448" t="inlineStr"/>
@@ -24396,13 +24413,21 @@
           <t>스타렉스91주8839</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -24451,13 +24476,21 @@
           <t>스타렉스91주8839</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -24501,10 +24534,26 @@
           <t>K1-PJT</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -24529,1561 +24578,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>MaterialID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Site</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>MaterialID</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Usage</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>EntryTime</t>
-        </is>
-      </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>RTK_센터미스</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>RTK_농도</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>RTK_마킹미스</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>RTK_필름마크</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>RTK_취급부주의</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>RTK_고객불만</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>RTK_기타</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>장비명</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>검사량</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>단가</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>출장비</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>일식</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>검사비</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>검사방법</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>FilmCount</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>WorkTime</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>OT</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>User2</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>WorkTime2</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>OT2</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>User3</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>WorkTime3</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>OT3</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>User4</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>WorkTime4</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>OT4</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>User5</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>WorkTime5</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>OT5</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>User6</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>WorkTime6</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>OT6</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>User7</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>WorkTime7</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>OT7</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>User8</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>WorkTime8</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>OT8</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>User9</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>WorkTime9</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>OT9</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>User10</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>WorkTime10</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>OT10</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>NDT_형광자분</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>NDT_흑색자분</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>NDT_백색페인트</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>NDT_침투제</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>NDT_세척제</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>NDT_현상제</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>NDT_형광침투제</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>차량번호</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>주행거리</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>차량점검</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>차량비고</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>품목명</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>RTK_총계</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
-        <is>
-          <t>회사코드</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>업체명</t>
-        </is>
-      </c>
-      <c r="BO1" t="inlineStr">
-        <is>
-          <t>작업자</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>작업시간</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>OT시간</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>OT금액</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>입력시간</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>(Full작업자)</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>RTK_RTK총계</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
-        <is>
-          <t>검사품명</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>적용코드</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>성적서번호</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>검사자</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>408</v>
-      </c>
-      <c r="D2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="1" t="n">
-        <v>46146.72261083333</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>R-RAY(Se-75)</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr"/>
-      <c r="BY2" t="inlineStr"/>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr"/>
-      <c r="CB2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>410</v>
-      </c>
-      <c r="D3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" s="1" t="n">
-        <v>46146.7233049537</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>R-RAY(Se-75)</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>406</v>
-      </c>
-      <c r="D4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" s="1" t="n">
-        <v>46146.72381587963</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>R-RAY(Se-75)</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr"/>
-      <c r="BY4" t="inlineStr"/>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>405</v>
-      </c>
-      <c r="D5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" s="1" t="n">
-        <v>46147.20053241898</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>R-RAY(Se-75)</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr"/>
-      <c r="BY5" t="inlineStr"/>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>460</v>
-      </c>
-      <c r="D6" t="n">
-        <v>100</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" s="1" t="n">
-        <v>46147.2070821875</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>R-RAY(Se-75)</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr"/>
-      <c r="BY6" t="inlineStr"/>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr"/>
-      <c r="CB6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>461</v>
-      </c>
-      <c r="D7" t="n">
-        <v>100</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" s="1" t="n">
-        <v>46147.2270262963</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>R-RAY(Se-75)</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr"/>
-      <c r="BR7" t="inlineStr"/>
-      <c r="BS7" t="inlineStr"/>
-      <c r="BT7" t="inlineStr"/>
-      <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr"/>
-      <c r="BY7" t="inlineStr"/>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr"/>
-      <c r="CB7" t="n">
-        <v>0</v>
+          <t>EntryDate</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -26097,69 +24629,1669 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Site</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>LaborCost</t>
+          <t>MaterialID</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>MaterialCost</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>OutsourceCost</t>
+          <t>EntryTime</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Profit</t>
+          <t>RTK_센터미스</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>RTK_농도</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>LaborDetail</t>
+          <t>RTK_마킹미스</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>MaterialDetail</t>
+          <t>RTK_필름마크</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>ExpenseDetail</t>
+          <t>RTK_취급부주의</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>UnitPrice</t>
-        </is>
+          <t>RTK_고객불만</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>RTK_기타</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>장비명</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>검사량</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>단가</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>출장비</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>일식</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>검사비</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>검사방법</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>FilmCount</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>WorkTime</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>OT</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>User2</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>WorkTime2</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>OT2</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>User3</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>WorkTime3</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>OT3</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>User4</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>WorkTime4</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>OT4</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>User5</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>WorkTime5</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>OT5</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>User6</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>WorkTime6</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>OT6</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>User7</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>WorkTime7</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>OT7</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>User8</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>WorkTime8</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>OT8</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>User9</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>WorkTime9</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>OT9</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>User10</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>WorkTime10</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>OT10</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>NDT_형광자분</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>NDT_흑색자분</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>NDT_백색페인트</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>NDT_침투제</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>NDT_세척제</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>NDT_현상제</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>NDT_형광침투제</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>차량번호</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>주행거리</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>차량점검</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>차량비고</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>품목명</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>RTK_총계</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>회사코드</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>업체명</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>작업자</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>작업시간</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>OT시간</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>OT금액</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>입력시간</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>(Full작업자)</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>RTK_RTK총계</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>검사품명</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>적용코드</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>성적서번호</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>검사자</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>408</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="1" t="n">
+        <v>46146.72261083333</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>410</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="1" t="n">
+        <v>46146.7233049537</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>406</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" s="1" t="n">
+        <v>46146.72381587963</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>405</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" s="1" t="n">
+        <v>46147.20053241898</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>460</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="1" t="n">
+        <v>46147.2070821875</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>461</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" s="1" t="n">
+        <v>46147.2270262963</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -26173,6 +26305,82 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>LaborCost</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>MaterialCost</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>OutsourceCost</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>LaborDetail</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MaterialDetail</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ExpenseDetail</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>UnitPrice</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
